--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -9,11 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대표 정보" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구성 확인" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명령 출력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="패키지" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명령 출력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성 확인'!$A$5:$F$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성 확인'!$A$5:$F$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'구성 확인'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'패키지'!$A$3:$A$2003</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'패키지'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -325,6 +328,8 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -784,7 +789,7 @@
         </is>
       </c>
       <c r="C8" s="48">
-        <f>IF('구성 확인'!E17="","",IF(TRIM('구성 확인'!E17)="none","물리","가상 ("&amp;TRIM('구성 확인'!E17)&amp;")"))</f>
+        <f>IF('구성 확인'!E17="","",IFERROR(INDEX({"물리","VMware","Hyper-V","KVM","Xen"},MATCH(TRIM('구성 확인'!E17),{"none","vmware","microsoft","kvm","xen"},0)),TRIM('구성 확인'!E17)))</f>
         <v/>
       </c>
     </row>
@@ -989,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1362,7 +1367,7 @@
       <c r="E17" s="54" t="n"/>
       <c r="F17" s="55" t="inlineStr">
         <is>
-          <t>none이면 물리 서버</t>
+          <t>none = 물리, microsoft = Hyper-V</t>
         </is>
       </c>
     </row>
@@ -2545,18 +2550,18 @@
       </c>
       <c r="C65" s="52" t="inlineStr">
         <is>
-          <t>최근 패치일</t>
+          <t>주요 패키지</t>
         </is>
       </c>
       <c r="D65" s="53" t="inlineStr">
         <is>
-          <t>dnf history</t>
+          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
         </is>
       </c>
       <c r="E65" s="54" t="n"/>
       <c r="F65" s="55" t="inlineStr">
         <is>
-          <t>Action(s)에 U가 든 줄</t>
+          <t>없으면 is not installed</t>
         </is>
       </c>
     </row>
@@ -2572,18 +2577,18 @@
       </c>
       <c r="C66" s="52" t="inlineStr">
         <is>
-          <t>자동 업데이트 설정</t>
+          <t>전체 패키지</t>
         </is>
       </c>
       <c r="D66" s="53" t="inlineStr">
         <is>
-          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
+          <t>rpm -qa | sort</t>
         </is>
       </c>
       <c r="E66" s="54" t="n"/>
       <c r="F66" s="55" t="inlineStr">
         <is>
-          <t>파일 없으면 미설치</t>
+          <t>결과는 패키지 시트에</t>
         </is>
       </c>
     </row>
@@ -2599,18 +2604,18 @@
       </c>
       <c r="C67" s="52" t="inlineStr">
         <is>
-          <t>자동 업데이트 예약</t>
+          <t>최근 패치일</t>
         </is>
       </c>
       <c r="D67" s="53" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files 'dnf-automatic*'</t>
+          <t>dnf history</t>
         </is>
       </c>
       <c r="E67" s="54" t="n"/>
       <c r="F67" s="55" t="inlineStr">
         <is>
-          <t>enabled면 사용</t>
+          <t>Action(s)에 U가 든 줄</t>
         </is>
       </c>
     </row>
@@ -2626,18 +2631,18 @@
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>저장소 목록</t>
+          <t>자동 업데이트 설정</t>
         </is>
       </c>
       <c r="D68" s="53" t="inlineStr">
         <is>
-          <t>dnf repolist</t>
+          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
         </is>
       </c>
       <c r="E68" s="54" t="n"/>
       <c r="F68" s="55" t="inlineStr">
         <is>
-          <t>repo id·이름만 나옴 (패키지 수 없음)</t>
+          <t>파일 없으면 미설치</t>
         </is>
       </c>
     </row>
@@ -2653,16 +2658,20 @@
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>저장소 파일</t>
+          <t>자동 업데이트 예약</t>
         </is>
       </c>
       <c r="D69" s="53" t="inlineStr">
         <is>
-          <t>ls /etc/yum.repos.d/</t>
+          <t>systemctl list-unit-files 'dnf-automatic*'</t>
         </is>
       </c>
       <c r="E69" s="54" t="n"/>
-      <c r="F69" s="55" t="n"/>
+      <c r="F69" s="55" t="inlineStr">
+        <is>
+          <t>enabled면 사용</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="51">
@@ -2676,18 +2685,18 @@
       </c>
       <c r="C70" s="52" t="inlineStr">
         <is>
-          <t>구독 등록 여부</t>
+          <t>저장소 목록</t>
         </is>
       </c>
       <c r="D70" s="53" t="inlineStr">
         <is>
-          <t>ls /etc/pki/consumer/cert.pem</t>
+          <t>dnf repolist</t>
         </is>
       </c>
       <c r="E70" s="54" t="n"/>
       <c r="F70" s="55" t="inlineStr">
         <is>
-          <t>파일 없으면 미등록</t>
+          <t>repo id·이름만 나옴 (패키지 수 없음)</t>
         </is>
       </c>
     </row>
@@ -2703,20 +2712,16 @@
       </c>
       <c r="C71" s="52" t="inlineStr">
         <is>
-          <t>구독 (RHSM)</t>
+          <t>저장소 파일</t>
         </is>
       </c>
       <c r="D71" s="53" t="inlineStr">
         <is>
-          <t>subscription-manager status</t>
+          <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
       <c r="E71" s="54" t="n"/>
-      <c r="F71" s="55" t="inlineStr">
-        <is>
-          <t>RHEL</t>
-        </is>
-      </c>
+      <c r="F71" s="55" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="51">
@@ -2730,18 +2735,18 @@
       </c>
       <c r="C72" s="52" t="inlineStr">
         <is>
-          <t>릴리스 고정</t>
+          <t>구독 등록 여부</t>
         </is>
       </c>
       <c r="D72" s="53" t="inlineStr">
         <is>
-          <t>subscription-manager release --show</t>
+          <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
       <c r="E72" s="54" t="n"/>
       <c r="F72" s="55" t="inlineStr">
         <is>
-          <t>Release not set이면 미고정</t>
+          <t>파일 없으면 미등록</t>
         </is>
       </c>
     </row>
@@ -2752,23 +2757,23 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>커널 설정</t>
+          <t>업데이트·패키지</t>
         </is>
       </c>
       <c r="C73" s="52" t="inlineStr">
         <is>
-          <t>sysctl</t>
+          <t>구독 (RHSM)</t>
         </is>
       </c>
       <c r="D73" s="53" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+          <t>subscription-manager status</t>
         </is>
       </c>
       <c r="E73" s="54" t="n"/>
       <c r="F73" s="55" t="inlineStr">
         <is>
-          <t>99-sysctl.conf는 sysctl.conf와 같은 파일 (중복 표시)</t>
+          <t>RHEL</t>
         </is>
       </c>
     </row>
@@ -2779,23 +2784,23 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>커널 설정</t>
+          <t>업데이트·패키지</t>
         </is>
       </c>
       <c r="C74" s="52" t="inlineStr">
         <is>
-          <t>자원 제한 (limits)</t>
+          <t>릴리스 고정</t>
         </is>
       </c>
       <c r="D74" s="53" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
+          <t>subscription-manager release --show</t>
         </is>
       </c>
       <c r="E74" s="54" t="n"/>
       <c r="F74" s="55" t="inlineStr">
         <is>
-          <t>로그인 세션에만 적용 (systemd 서비스 제외)</t>
+          <t>Release not set이면 미고정</t>
         </is>
       </c>
     </row>
@@ -2811,16 +2816,20 @@
       </c>
       <c r="C75" s="52" t="inlineStr">
         <is>
-          <t>kdump 설정</t>
+          <t>sysctl</t>
         </is>
       </c>
       <c r="D75" s="53" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
+          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
         </is>
       </c>
       <c r="E75" s="54" t="n"/>
-      <c r="F75" s="55" t="n"/>
+      <c r="F75" s="55" t="inlineStr">
+        <is>
+          <t>99-sysctl.conf는 sysctl.conf와 같은 파일 (중복 표시)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="51">
@@ -2834,16 +2843,20 @@
       </c>
       <c r="C76" s="52" t="inlineStr">
         <is>
-          <t>kdump 실행</t>
+          <t>자원 제한 (limits)</t>
         </is>
       </c>
       <c r="D76" s="53" t="inlineStr">
         <is>
-          <t>systemctl is-active kdump</t>
+          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
       <c r="E76" s="54" t="n"/>
-      <c r="F76" s="55" t="n"/>
+      <c r="F76" s="55" t="inlineStr">
+        <is>
+          <t>로그인 세션에만 적용 (systemd 서비스 제외)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="51">
@@ -2857,12 +2870,12 @@
       </c>
       <c r="C77" s="52" t="inlineStr">
         <is>
-          <t>kdump 부팅 시 시작</t>
+          <t>kdump 설정</t>
         </is>
       </c>
       <c r="D77" s="53" t="inlineStr">
         <is>
-          <t>systemctl is-enabled kdump</t>
+          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
       <c r="E77" s="54" t="n"/>
@@ -2875,17 +2888,17 @@
       </c>
       <c r="B78" s="51" t="inlineStr">
         <is>
-          <t>서비스·예약</t>
+          <t>커널 설정</t>
         </is>
       </c>
       <c r="C78" s="52" t="inlineStr">
         <is>
-          <t>실행 중인 서비스</t>
+          <t>kdump 실행</t>
         </is>
       </c>
       <c r="D78" s="53" t="inlineStr">
         <is>
-          <t>systemctl list-units --type=service --state=running --no-pager</t>
+          <t>systemctl is-active kdump</t>
         </is>
       </c>
       <c r="E78" s="54" t="n"/>
@@ -2898,17 +2911,17 @@
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>서비스·예약</t>
+          <t>커널 설정</t>
         </is>
       </c>
       <c r="C79" s="52" t="inlineStr">
         <is>
-          <t>자동 시작 서비스</t>
+          <t>kdump 부팅 시 시작</t>
         </is>
       </c>
       <c r="D79" s="53" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
+          <t>systemctl is-enabled kdump</t>
         </is>
       </c>
       <c r="E79" s="54" t="n"/>
@@ -2926,20 +2939,16 @@
       </c>
       <c r="C80" s="52" t="inlineStr">
         <is>
-          <t>열린 포트</t>
+          <t>실행 중인 서비스</t>
         </is>
       </c>
       <c r="D80" s="53" t="inlineStr">
         <is>
-          <t>ss -tulnp</t>
+          <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
       <c r="E80" s="54" t="n"/>
-      <c r="F80" s="55" t="inlineStr">
-        <is>
-          <t>LISTEN 포트와 프로세스</t>
-        </is>
-      </c>
+      <c r="F80" s="55" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="51">
@@ -2953,12 +2962,12 @@
       </c>
       <c r="C81" s="52" t="inlineStr">
         <is>
-          <t>예약 작업 (타이머)</t>
+          <t>자동 시작 서비스</t>
         </is>
       </c>
       <c r="D81" s="53" t="inlineStr">
         <is>
-          <t>systemctl list-timers --all --no-pager</t>
+          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
       <c r="E81" s="54" t="n"/>
@@ -2976,18 +2985,18 @@
       </c>
       <c r="C82" s="52" t="inlineStr">
         <is>
-          <t>예약 작업 (crontab)</t>
+          <t>열린 포트</t>
         </is>
       </c>
       <c r="D82" s="53" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /var/spool/cron/*</t>
+          <t>ss -tulnp</t>
         </is>
       </c>
       <c r="E82" s="54" t="n"/>
       <c r="F82" s="55" t="inlineStr">
         <is>
-          <t>머리글 파일명 = 계정명</t>
+          <t>LISTEN 포트와 프로세스</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3012,12 @@
       </c>
       <c r="C83" s="52" t="inlineStr">
         <is>
-          <t>예약 작업 (cron.d)</t>
+          <t>예약 작업 (타이머)</t>
         </is>
       </c>
       <c r="D83" s="53" t="inlineStr">
         <is>
-          <t>ls /etc/cron.d</t>
+          <t>systemctl list-timers --all --no-pager</t>
         </is>
       </c>
       <c r="E83" s="54" t="n"/>
@@ -3021,23 +3030,23 @@
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>에이전트·백업</t>
+          <t>서비스·예약</t>
         </is>
       </c>
       <c r="C84" s="52" t="inlineStr">
         <is>
-          <t>모니터링 에이전트</t>
+          <t>예약 작업 (crontab)</t>
         </is>
       </c>
       <c r="D84" s="53" t="inlineStr">
         <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+          <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E84" s="54" t="n"/>
       <c r="F84" s="55" t="inlineStr">
         <is>
-          <t>출력 없으면 미실행</t>
+          <t>머리글 파일명 = 계정명</t>
         </is>
       </c>
     </row>
@@ -3048,25 +3057,21 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>에이전트·백업</t>
+          <t>서비스·예약</t>
         </is>
       </c>
       <c r="C85" s="52" t="inlineStr">
         <is>
-          <t>보안 에이전트</t>
+          <t>예약 작업 (cron.d)</t>
         </is>
       </c>
       <c r="D85" s="53" t="inlineStr">
         <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+          <t>ls /etc/cron.d</t>
         </is>
       </c>
       <c r="E85" s="54" t="n"/>
-      <c r="F85" s="55" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
+      <c r="F85" s="55" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="51">
@@ -3080,7 +3085,7 @@
       </c>
       <c r="C86" s="52" t="inlineStr">
         <is>
-          <t>백신</t>
+          <t>모니터링 에이전트</t>
         </is>
       </c>
       <c r="D86" s="53" t="inlineStr">
@@ -3107,23 +3112,77 @@
       </c>
       <c r="C87" s="52" t="inlineStr">
         <is>
-          <t>설정 백업</t>
+          <t>보안 에이전트</t>
         </is>
       </c>
       <c r="D87" s="53" t="inlineStr">
         <is>
-          <t>백업 위치, 마지막 백업 날짜</t>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
       <c r="E87" s="54" t="n"/>
       <c r="F87" s="55" t="inlineStr">
         <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C88" s="52" t="inlineStr">
+        <is>
+          <t>백신</t>
+        </is>
+      </c>
+      <c r="D88" s="53" t="inlineStr">
+        <is>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+        </is>
+      </c>
+      <c r="E88" s="54" t="n"/>
+      <c r="F88" s="55" t="inlineStr">
+        <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C89" s="52" t="inlineStr">
+        <is>
+          <t>설정 백업</t>
+        </is>
+      </c>
+      <c r="D89" s="53" t="inlineStr">
+        <is>
+          <t>백업 위치, 마지막 백업 날짜</t>
+        </is>
+      </c>
+      <c r="E89" s="54" t="n"/>
+      <c r="F89" s="55" t="inlineStr">
+        <is>
           <t>직접 입력</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F87"/>
+  <autoFilter ref="A5:F89"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.75" header="0.5" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -3143,6 +3202,6046 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:A2003"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>패키지</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>명령: rpm -qa | sort  →  결과를 A4부터 붙여 넣기</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>이름-버전-릴리스.아키텍처</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="62" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="62" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="62" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="62" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="62" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="62" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="62" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="62" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="62" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="62" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="62" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="62" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="62" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="62" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="62" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="62" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="62" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="62" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="62" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="62" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="62" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="62" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="62" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="62" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="62" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="62" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="62" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="62" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="62" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="62" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="62" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="62" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="62" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="62" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="62" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="62" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="62" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="62" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="62" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="62" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="62" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="62" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="62" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="62" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="62" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="62" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="62" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="62" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="62" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="62" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="62" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="62" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="62" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="62" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="62" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="62" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="62" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="62" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="62" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="62" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="62" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="62" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="62" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="62" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="62" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="62" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="62" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="62" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="62" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="62" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="62" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="62" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="62" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="62" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="62" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="62" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="62" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="62" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="62" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="62" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="62" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="62" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="62" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="62" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="62" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="62" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="62" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="62" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="62" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="62" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="62" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="62" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="62" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="62" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="62" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="62" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="62" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="62" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="62" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="62" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="62" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="62" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="62" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="62" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="62" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="62" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="62" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="62" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="62" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="62" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="62" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="62" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="62" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="62" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="62" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="62" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="62" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="62" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="62" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="62" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="62" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="62" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="62" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="62" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="62" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="62" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="62" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="62" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="62" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="62" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="62" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="62" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="62" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="62" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="62" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="62" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="62" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="62" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="62" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="62" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="62" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="62" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="62" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="62" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="62" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="62" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="62" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="62" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="62" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="62" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="62" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="62" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="62" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="62" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="62" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="62" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="62" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="62" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="62" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="62" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="62" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="62" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="62" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="62" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="62" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="62" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="62" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="62" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="62" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="62" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="62" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="62" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="62" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="62" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="62" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="62" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="62" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="62" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="62" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="62" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="62" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="62" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="62" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="62" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="62" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="62" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="62" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="62" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="62" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="62" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="62" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="62" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="62" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="62" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="62" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="62" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="62" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="62" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="62" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="62" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="62" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="62" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="62" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="62" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="62" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="62" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="62" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="62" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="62" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="62" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="62" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="62" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="62" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="62" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="62" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="62" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="62" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="62" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="62" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="62" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="62" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="62" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="62" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="62" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="62" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="62" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="62" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="62" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="62" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="62" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="62" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="62" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="62" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="62" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="62" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="62" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="62" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="62" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="62" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="62" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="62" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="62" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="62" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="62" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="62" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="62" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="62" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="62" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="62" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="62" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="62" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="62" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="62" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="62" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="62" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="62" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="62" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="62" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="62" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="62" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="62" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="62" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="62" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="62" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="62" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="62" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="62" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="62" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="62" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="62" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="62" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="62" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="62" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="62" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="62" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="62" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="62" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="62" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="62" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="62" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="62" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="62" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="62" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="62" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="62" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="62" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="62" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="62" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="62" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="62" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="62" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="62" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="62" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="62" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="62" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="62" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="62" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="62" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="62" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="62" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="62" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="62" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="62" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="62" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="62" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="62" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="62" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="62" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="62" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="62" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="62" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="62" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="62" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="62" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="62" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="62" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="62" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="62" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="62" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="62" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="62" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="62" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="62" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="62" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="62" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="62" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="62" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="62" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="62" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="62" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="62" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="62" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="62" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="62" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="62" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="62" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="62" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="62" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="62" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="62" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="62" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="62" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="62" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="62" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="62" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="62" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="62" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="62" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="62" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="62" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="62" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="62" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="62" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="62" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="62" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="62" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="62" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="62" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="62" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="62" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="62" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="62" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="62" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="62" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="62" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="62" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="62" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="62" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="62" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="62" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="62" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="62" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="62" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="62" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="62" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="62" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="62" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="62" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="62" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="62" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="62" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="62" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="62" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="62" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="62" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="62" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="62" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="62" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="62" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="62" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="62" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="62" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="62" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="62" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="62" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="62" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="62" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="62" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="62" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="62" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="62" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="62" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="62" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="62" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="62" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="62" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="62" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="62" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="62" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="62" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="62" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="62" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="62" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="62" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="62" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="62" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="62" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="62" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="62" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="62" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="62" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="62" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="62" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="62" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="62" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="62" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="62" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="62" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="62" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="62" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="62" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="62" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="62" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="62" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="62" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="62" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="62" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="62" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="62" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="62" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="62" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="62" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="62" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="62" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="62" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="62" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="62" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="62" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="62" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="62" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="62" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="62" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="62" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="62" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="62" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="62" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="62" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="62" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="62" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="62" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="62" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="62" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="62" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="62" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="62" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="62" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="62" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="62" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="62" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="62" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="62" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="62" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="62" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="62" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="62" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="62" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="62" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="62" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="62" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="62" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="62" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="62" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="62" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="62" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="62" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="62" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="62" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="62" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="62" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="62" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="62" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="62" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="62" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="62" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="62" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="62" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="62" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="62" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="62" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="62" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="62" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="62" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="62" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="62" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="62" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="62" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="62" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="62" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="62" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="62" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="62" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="62" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="62" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="62" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="62" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="62" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="62" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="62" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="62" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="62" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="62" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="62" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="62" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="62" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="62" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="62" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="62" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="62" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="62" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="62" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="62" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="62" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="62" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="62" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="62" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="62" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="62" t="n"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="62" t="n"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="62" t="n"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="62" t="n"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="62" t="n"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="62" t="n"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="62" t="n"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="62" t="n"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="62" t="n"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="62" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="62" t="n"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="62" t="n"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="62" t="n"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="62" t="n"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="62" t="n"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="62" t="n"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="62" t="n"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="62" t="n"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="62" t="n"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="62" t="n"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="62" t="n"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="62" t="n"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="62" t="n"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="62" t="n"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="62" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="62" t="n"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="62" t="n"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="62" t="n"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="62" t="n"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="62" t="n"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="62" t="n"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="62" t="n"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="62" t="n"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="62" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="62" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="62" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="62" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="62" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="62" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="62" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="62" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="62" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="62" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="62" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="62" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="62" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="62" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="62" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="62" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="62" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="62" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="62" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="62" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="62" t="n"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="62" t="n"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="62" t="n"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="62" t="n"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="62" t="n"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="62" t="n"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="62" t="n"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="62" t="n"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="62" t="n"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="62" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="62" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="62" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="62" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="62" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="62" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="62" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="62" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="62" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="62" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="62" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="62" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="62" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="62" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="62" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="62" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="62" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="62" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="62" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="62" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="62" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="62" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="62" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="62" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="62" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="62" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="62" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="62" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="62" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="62" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="62" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="62" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="62" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="62" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="62" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="62" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="62" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="62" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="62" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="62" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="62" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="62" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="62" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="62" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="62" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="62" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="62" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="62" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="62" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="62" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="62" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="62" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="62" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="62" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="62" t="n"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="62" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="62" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="62" t="n"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="62" t="n"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="62" t="n"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="62" t="n"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="62" t="n"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="62" t="n"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="62" t="n"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="62" t="n"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="62" t="n"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="62" t="n"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="62" t="n"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="62" t="n"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="62" t="n"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="62" t="n"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="62" t="n"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="62" t="n"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="62" t="n"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="62" t="n"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="62" t="n"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="62" t="n"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="62" t="n"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="62" t="n"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="62" t="n"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="62" t="n"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="62" t="n"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="62" t="n"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="62" t="n"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="62" t="n"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="62" t="n"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="62" t="n"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="62" t="n"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="62" t="n"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="62" t="n"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="62" t="n"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="62" t="n"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="62" t="n"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="62" t="n"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="62" t="n"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="62" t="n"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="62" t="n"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="62" t="n"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="62" t="n"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="62" t="n"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="62" t="n"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="62" t="n"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="62" t="n"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="62" t="n"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="62" t="n"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="62" t="n"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="62" t="n"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="62" t="n"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="62" t="n"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="62" t="n"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="62" t="n"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="62" t="n"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="62" t="n"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="62" t="n"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="62" t="n"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="62" t="n"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="62" t="n"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="62" t="n"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="62" t="n"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="62" t="n"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="62" t="n"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="62" t="n"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="62" t="n"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="62" t="n"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="62" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="62" t="n"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="62" t="n"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="62" t="n"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="62" t="n"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="62" t="n"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="62" t="n"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="62" t="n"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="62" t="n"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="62" t="n"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="62" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="62" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="62" t="n"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="62" t="n"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="62" t="n"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="62" t="n"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="62" t="n"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="62" t="n"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="62" t="n"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="62" t="n"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="62" t="n"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="62" t="n"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="62" t="n"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="62" t="n"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="62" t="n"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="62" t="n"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="62" t="n"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="62" t="n"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="62" t="n"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="62" t="n"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="62" t="n"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="62" t="n"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="62" t="n"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="62" t="n"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="62" t="n"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="62" t="n"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="62" t="n"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="62" t="n"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="62" t="n"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="62" t="n"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="62" t="n"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="62" t="n"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="62" t="n"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="62" t="n"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="62" t="n"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="62" t="n"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="62" t="n"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="62" t="n"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="62" t="n"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="62" t="n"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="62" t="n"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="62" t="n"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="62" t="n"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="62" t="n"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="62" t="n"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="62" t="n"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="62" t="n"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="62" t="n"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="62" t="n"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="62" t="n"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="62" t="n"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="62" t="n"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="62" t="n"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="62" t="n"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="62" t="n"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="62" t="n"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="62" t="n"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="62" t="n"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="62" t="n"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="62" t="n"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="62" t="n"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="62" t="n"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="62" t="n"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="62" t="n"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="62" t="n"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="62" t="n"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="62" t="n"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="62" t="n"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="62" t="n"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="62" t="n"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="62" t="n"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="62" t="n"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="62" t="n"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="62" t="n"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="62" t="n"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="62" t="n"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="62" t="n"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="62" t="n"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="62" t="n"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="62" t="n"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="62" t="n"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="62" t="n"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="62" t="n"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="62" t="n"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="62" t="n"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="62" t="n"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="62" t="n"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="62" t="n"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="62" t="n"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="62" t="n"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="62" t="n"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="62" t="n"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="62" t="n"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="62" t="n"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="62" t="n"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="62" t="n"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="62" t="n"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="62" t="n"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="62" t="n"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="62" t="n"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="62" t="n"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="62" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="62" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="62" t="n"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="62" t="n"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="62" t="n"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="62" t="n"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="62" t="n"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="62" t="n"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="62" t="n"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="62" t="n"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="62" t="n"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="62" t="n"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="62" t="n"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="62" t="n"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="62" t="n"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="62" t="n"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="62" t="n"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="62" t="n"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="62" t="n"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="62" t="n"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="62" t="n"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="62" t="n"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="62" t="n"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="62" t="n"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="62" t="n"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="62" t="n"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="62" t="n"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="62" t="n"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="62" t="n"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="62" t="n"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="62" t="n"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="62" t="n"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="62" t="n"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="62" t="n"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="62" t="n"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="62" t="n"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="62" t="n"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="62" t="n"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="62" t="n"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="62" t="n"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="62" t="n"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="62" t="n"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="62" t="n"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="62" t="n"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="62" t="n"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="62" t="n"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="62" t="n"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="62" t="n"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="62" t="n"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="62" t="n"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="62" t="n"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="62" t="n"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="62" t="n"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="62" t="n"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="62" t="n"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="62" t="n"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="62" t="n"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="62" t="n"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="62" t="n"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="62" t="n"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="62" t="n"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="62" t="n"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="62" t="n"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="62" t="n"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="62" t="n"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="62" t="n"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="62" t="n"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="62" t="n"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="62" t="n"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="62" t="n"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="62" t="n"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="62" t="n"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="62" t="n"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="62" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="62" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="62" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="62" t="n"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="62" t="n"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="62" t="n"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="62" t="n"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="62" t="n"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="62" t="n"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="62" t="n"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="62" t="n"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="62" t="n"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="62" t="n"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="62" t="n"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="62" t="n"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="62" t="n"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="62" t="n"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="62" t="n"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="62" t="n"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="62" t="n"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="62" t="n"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="62" t="n"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="62" t="n"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="62" t="n"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="62" t="n"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="62" t="n"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="62" t="n"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="62" t="n"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="62" t="n"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="62" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="62" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="62" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="62" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="62" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="62" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="62" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="62" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="62" t="n"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="62" t="n"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="62" t="n"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="62" t="n"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="62" t="n"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="62" t="n"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="62" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="62" t="n"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="62" t="n"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="62" t="n"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="62" t="n"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="62" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="62" t="n"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="62" t="n"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="62" t="n"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="62" t="n"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="62" t="n"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="62" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="62" t="n"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="62" t="n"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="62" t="n"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="62" t="n"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="62" t="n"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="62" t="n"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="62" t="n"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="62" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="62" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="62" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="62" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="62" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="62" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="62" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="62" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="62" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="62" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="62" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="62" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="62" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="62" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="62" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="62" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="62" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="62" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="62" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="62" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="62" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="62" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="62" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="62" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="62" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="62" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="62" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="62" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="62" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="62" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="62" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="62" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="62" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="62" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="62" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="62" t="n"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="62" t="n"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="62" t="n"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="62" t="n"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="62" t="n"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="62" t="n"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="62" t="n"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="62" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="62" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="62" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="62" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="62" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="62" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="62" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="62" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="62" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="62" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="62" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="62" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="62" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="62" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="62" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="62" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="62" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="62" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="62" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="62" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="62" t="n"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="62" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="62" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="62" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="62" t="n"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="62" t="n"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="62" t="n"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="62" t="n"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="62" t="n"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="62" t="n"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="62" t="n"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="62" t="n"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="62" t="n"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="62" t="n"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="62" t="n"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="62" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="62" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="62" t="n"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="62" t="n"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="62" t="n"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="62" t="n"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="62" t="n"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="62" t="n"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="62" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="62" t="n"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="62" t="n"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="62" t="n"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="62" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="62" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="62" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="62" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="62" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="62" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="62" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="62" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="62" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="62" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="62" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="62" t="n"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="62" t="n"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="62" t="n"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="62" t="n"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="62" t="n"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="62" t="n"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="62" t="n"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="62" t="n"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="62" t="n"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="62" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="62" t="n"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="62" t="n"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="62" t="n"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="62" t="n"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="62" t="n"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="62" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="62" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="62" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="62" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="62" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="62" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="62" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="62" t="n"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="62" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="62" t="n"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="62" t="n"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="62" t="n"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="62" t="n"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="62" t="n"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="62" t="n"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="62" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="62" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="62" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="62" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="62" t="n"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="62" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="62" t="n"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="62" t="n"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="62" t="n"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="62" t="n"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="62" t="n"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="62" t="n"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="62" t="n"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="62" t="n"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="62" t="n"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="62" t="n"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="62" t="n"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="62" t="n"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="62" t="n"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="62" t="n"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="62" t="n"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="62" t="n"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="62" t="n"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="62" t="n"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="62" t="n"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="62" t="n"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="62" t="n"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="62" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="62" t="n"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="62" t="n"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="62" t="n"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="62" t="n"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="62" t="n"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="62" t="n"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="62" t="n"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="62" t="n"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="62" t="n"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="62" t="n"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="62" t="n"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="62" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="62" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="62" t="n"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="62" t="n"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="62" t="n"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="62" t="n"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="62" t="n"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="62" t="n"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="62" t="n"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="62" t="n"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="62" t="n"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="62" t="n"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="62" t="n"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="62" t="n"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="62" t="n"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="62" t="n"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="62" t="n"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="62" t="n"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="62" t="n"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="62" t="n"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="62" t="n"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="62" t="n"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="62" t="n"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="62" t="n"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="62" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="62" t="n"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="62" t="n"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="62" t="n"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="62" t="n"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="62" t="n"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="62" t="n"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="62" t="n"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="62" t="n"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="62" t="n"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="62" t="n"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="62" t="n"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="62" t="n"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="62" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="62" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="62" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="62" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="62" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="62" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="62" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="62" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="62" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="62" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="62" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="62" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="62" t="n"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="62" t="n"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="62" t="n"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="62" t="n"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="62" t="n"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="62" t="n"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="62" t="n"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="62" t="n"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="62" t="n"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="62" t="n"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="62" t="n"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="62" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="62" t="n"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="62" t="n"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="62" t="n"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="62" t="n"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="62" t="n"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="62" t="n"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="62" t="n"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="62" t="n"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="62" t="n"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="62" t="n"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="62" t="n"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="62" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="62" t="n"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="62" t="n"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="62" t="n"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="62" t="n"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="62" t="n"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="62" t="n"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="62" t="n"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="62" t="n"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="62" t="n"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="62" t="n"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="62" t="n"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="62" t="n"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="62" t="n"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="62" t="n"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="62" t="n"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="62" t="n"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="62" t="n"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="62" t="n"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="62" t="n"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="62" t="n"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="62" t="n"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="62" t="n"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="62" t="n"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="62" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="62" t="n"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="62" t="n"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="62" t="n"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="62" t="n"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="62" t="n"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="62" t="n"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="62" t="n"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="62" t="n"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="62" t="n"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="62" t="n"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="62" t="n"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="62" t="n"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="62" t="n"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="62" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="62" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="62" t="n"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="62" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="62" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="62" t="n"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="62" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="62" t="n"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="62" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="62" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="62" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="62" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="62" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="62" t="n"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="62" t="n"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="62" t="n"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="62" t="n"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="62" t="n"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="62" t="n"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="62" t="n"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="62" t="n"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="62" t="n"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="62" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="62" t="n"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="62" t="n"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="62" t="n"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="62" t="n"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="62" t="n"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="62" t="n"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="62" t="n"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="62" t="n"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="62" t="n"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="62" t="n"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="62" t="n"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="62" t="n"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="62" t="n"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="62" t="n"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="62" t="n"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="62" t="n"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="62" t="n"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="62" t="n"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="62" t="n"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="62" t="n"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="62" t="n"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="62" t="n"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="62" t="n"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="62" t="n"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="62" t="n"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="62" t="n"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="62" t="n"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="62" t="n"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="62" t="n"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="62" t="n"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="62" t="n"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="62" t="n"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="62" t="n"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="62" t="n"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="62" t="n"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="62" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="62" t="n"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="62" t="n"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="62" t="n"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="62" t="n"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="62" t="n"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="62" t="n"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="62" t="n"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="62" t="n"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="62" t="n"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="62" t="n"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="62" t="n"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="62" t="n"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="62" t="n"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="62" t="n"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="62" t="n"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="62" t="n"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="62" t="n"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="62" t="n"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="62" t="n"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="62" t="n"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="62" t="n"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="62" t="n"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="62" t="n"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="62" t="n"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="62" t="n"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="62" t="n"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="62" t="n"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="62" t="n"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="62" t="n"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="62" t="n"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="62" t="n"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="62" t="n"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="62" t="n"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="62" t="n"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="62" t="n"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="62" t="n"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="62" t="n"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="62" t="n"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="62" t="n"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="62" t="n"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="62" t="n"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="62" t="n"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="62" t="n"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="62" t="n"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="62" t="n"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="62" t="n"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="62" t="n"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="62" t="n"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="62" t="n"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="62" t="n"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="62" t="n"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="62" t="n"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="62" t="n"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="62" t="n"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="62" t="n"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="62" t="n"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="62" t="n"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="62" t="n"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="62" t="n"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="62" t="n"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="62" t="n"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="62" t="n"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="62" t="n"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="62" t="n"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="62" t="n"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="62" t="n"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="62" t="n"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="62" t="n"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="62" t="n"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="62" t="n"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="62" t="n"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="62" t="n"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="62" t="n"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="62" t="n"/>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="62" t="n"/>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="62" t="n"/>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="62" t="n"/>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="62" t="n"/>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="62" t="n"/>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="62" t="n"/>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="62" t="n"/>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="62" t="n"/>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="62" t="n"/>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="62" t="n"/>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="62" t="n"/>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="62" t="n"/>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="62" t="n"/>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="62" t="n"/>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="62" t="n"/>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="62" t="n"/>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="62" t="n"/>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="62" t="n"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="62" t="n"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="62" t="n"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="62" t="n"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="62" t="n"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="62" t="n"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="62" t="n"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="62" t="n"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="62" t="n"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="62" t="n"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="62" t="n"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="62" t="n"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="62" t="n"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="62" t="n"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="62" t="n"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="62" t="n"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="62" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="62" t="n"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="62" t="n"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="62" t="n"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="62" t="n"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="62" t="n"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="62" t="n"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="62" t="n"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="62" t="n"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="62" t="n"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="62" t="n"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="62" t="n"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="62" t="n"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="62" t="n"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="62" t="n"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="62" t="n"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="62" t="n"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="62" t="n"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="62" t="n"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="62" t="n"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="62" t="n"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="62" t="n"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="62" t="n"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="62" t="n"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="62" t="n"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="62" t="n"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="62" t="n"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="62" t="n"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="62" t="n"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="62" t="n"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="62" t="n"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="62" t="n"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="62" t="n"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="62" t="n"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="62" t="n"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="62" t="n"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="62" t="n"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="62" t="n"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="62" t="n"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="62" t="n"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="62" t="n"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="62" t="n"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="62" t="n"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="62" t="n"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="62" t="n"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="62" t="n"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="62" t="n"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="62" t="n"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="62" t="n"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="62" t="n"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="62" t="n"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="62" t="n"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="62" t="n"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="62" t="n"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="62" t="n"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="62" t="n"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="62" t="n"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="62" t="n"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="62" t="n"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="62" t="n"/>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="62" t="n"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="62" t="n"/>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="62" t="n"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="62" t="n"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="62" t="n"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="62" t="n"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="62" t="n"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="62" t="n"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="62" t="n"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="62" t="n"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="62" t="n"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="62" t="n"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="62" t="n"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="62" t="n"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="62" t="n"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="62" t="n"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="62" t="n"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="62" t="n"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="62" t="n"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="62" t="n"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="62" t="n"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="62" t="n"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="62" t="n"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="62" t="n"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="62" t="n"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="62" t="n"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="62" t="n"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="62" t="n"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="62" t="n"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="62" t="n"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="62" t="n"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="62" t="n"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="62" t="n"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="62" t="n"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="62" t="n"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="62" t="n"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="62" t="n"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="62" t="n"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="62" t="n"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="62" t="n"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="62" t="n"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="62" t="n"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="62" t="n"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="62" t="n"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="62" t="n"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="62" t="n"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="62" t="n"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="62" t="n"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="62" t="n"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="62" t="n"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="62" t="n"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="62" t="n"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="62" t="n"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="62" t="n"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="62" t="n"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="62" t="n"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="62" t="n"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="62" t="n"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="62" t="n"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="62" t="n"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="62" t="n"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="62" t="n"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="62" t="n"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="62" t="n"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="62" t="n"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="62" t="n"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="62" t="n"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="62" t="n"/>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="62" t="n"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="62" t="n"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="62" t="n"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="62" t="n"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="62" t="n"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="62" t="n"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="62" t="n"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="62" t="n"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="62" t="n"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="62" t="n"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="62" t="n"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="62" t="n"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="62" t="n"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="62" t="n"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="62" t="n"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="62" t="n"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="62" t="n"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="62" t="n"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="62" t="n"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="62" t="n"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="62" t="n"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="62" t="n"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="62" t="n"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="62" t="n"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="62" t="n"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="62" t="n"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="62" t="n"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="62" t="n"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="62" t="n"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="62" t="n"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="62" t="n"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="62" t="n"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="62" t="n"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="62" t="n"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="62" t="n"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="62" t="n"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="62" t="n"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="62" t="n"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="62" t="n"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="62" t="n"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="62" t="n"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="62" t="n"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="62" t="n"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="62" t="n"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="62" t="n"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="62" t="n"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="62" t="n"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="62" t="n"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="62" t="n"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="62" t="n"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="62" t="n"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="62" t="n"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="62" t="n"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="62" t="n"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="62" t="n"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="62" t="n"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="62" t="n"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="62" t="n"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="62" t="n"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="62" t="n"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="62" t="n"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="62" t="n"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="62" t="n"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="62" t="n"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="62" t="n"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="62" t="n"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="62" t="n"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="62" t="n"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="62" t="n"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="62" t="n"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="62" t="n"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="62" t="n"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="62" t="n"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="62" t="n"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="62" t="n"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="62" t="n"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="62" t="n"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="62" t="n"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="62" t="n"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="62" t="n"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="62" t="n"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="62" t="n"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="62" t="n"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="62" t="n"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="62" t="n"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="62" t="n"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="62" t="n"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="62" t="n"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="62" t="n"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="62" t="n"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="62" t="n"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="62" t="n"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="62" t="n"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="62" t="n"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="62" t="n"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="62" t="n"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="62" t="n"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="62" t="n"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="62" t="n"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="62" t="n"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="62" t="n"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="62" t="n"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="62" t="n"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="62" t="n"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="62" t="n"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="62" t="n"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="62" t="n"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="62" t="n"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="62" t="n"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="62" t="n"/>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="62" t="n"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="62" t="n"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="62" t="n"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="62" t="n"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="62" t="n"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="62" t="n"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="62" t="n"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="62" t="n"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="62" t="n"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="62" t="n"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="62" t="n"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="62" t="n"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="62" t="n"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="62" t="n"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="62" t="n"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="62" t="n"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="62" t="n"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="62" t="n"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="62" t="n"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="62" t="n"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="62" t="n"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="62" t="n"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="62" t="n"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="62" t="n"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="62" t="n"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="62" t="n"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="62" t="n"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="62" t="n"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="62" t="n"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="62" t="n"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="62" t="n"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="62" t="n"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="62" t="n"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="62" t="n"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="62" t="n"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="62" t="n"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="62" t="n"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="62" t="n"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="62" t="n"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="62" t="n"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="62" t="n"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="62" t="n"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="62" t="n"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="62" t="n"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="62" t="n"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="62" t="n"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="62" t="n"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="62" t="n"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="62" t="n"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="62" t="n"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="62" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="62" t="n"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="62" t="n"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="62" t="n"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="62" t="n"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="62" t="n"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="62" t="n"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="62" t="n"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="62" t="n"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="62" t="n"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="62" t="n"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="62" t="n"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="62" t="n"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="62" t="n"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="62" t="n"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="62" t="n"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="62" t="n"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="62" t="n"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="62" t="n"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="62" t="n"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="62" t="n"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="62" t="n"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="62" t="n"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="62" t="n"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="62" t="n"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="62" t="n"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="62" t="n"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="62" t="n"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="62" t="n"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="62" t="n"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="62" t="n"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="62" t="n"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="62" t="n"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="62" t="n"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="62" t="n"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="62" t="n"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="62" t="n"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="62" t="n"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="62" t="n"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="62" t="n"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="62" t="n"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="62" t="n"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="62" t="n"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="62" t="n"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="62" t="n"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="62" t="n"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="62" t="n"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="62" t="n"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="62" t="n"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="62" t="n"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="62" t="n"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="62" t="n"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="62" t="n"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="62" t="n"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="62" t="n"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="62" t="n"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="62" t="n"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="62" t="n"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="62" t="n"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="62" t="n"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="62" t="n"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="62" t="n"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="62" t="n"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="62" t="n"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="62" t="n"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="62" t="n"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="62" t="n"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="62" t="n"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="62" t="n"/>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="62" t="n"/>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="62" t="n"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="62" t="n"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="62" t="n"/>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="62" t="n"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="62" t="n"/>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="62" t="n"/>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="62" t="n"/>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="62" t="n"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="62" t="n"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="62" t="n"/>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="62" t="n"/>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="62" t="n"/>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="62" t="n"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="62" t="n"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="62" t="n"/>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="62" t="n"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="62" t="n"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="62" t="n"/>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="62" t="n"/>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="62" t="n"/>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="62" t="n"/>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="62" t="n"/>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="62" t="n"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="62" t="n"/>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="62" t="n"/>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="62" t="n"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="62" t="n"/>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="62" t="n"/>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="62" t="n"/>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="62" t="n"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="62" t="n"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="62" t="n"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="62" t="n"/>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="62" t="n"/>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="62" t="n"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="62" t="n"/>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="62" t="n"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="62" t="n"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="62" t="n"/>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="62" t="n"/>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="62" t="n"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="62" t="n"/>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="62" t="n"/>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="62" t="n"/>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="62" t="n"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="62" t="n"/>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="62" t="n"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="62" t="n"/>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="62" t="n"/>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="62" t="n"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="62" t="n"/>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="62" t="n"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="62" t="n"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="62" t="n"/>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="62" t="n"/>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="62" t="n"/>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="62" t="n"/>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="62" t="n"/>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="62" t="n"/>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="62" t="n"/>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="62" t="n"/>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="62" t="n"/>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="62" t="n"/>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="62" t="n"/>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="62" t="n"/>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="62" t="n"/>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="62" t="n"/>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="62" t="n"/>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="62" t="n"/>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="62" t="n"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="62" t="n"/>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="62" t="n"/>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="62" t="n"/>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="62" t="n"/>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="62" t="n"/>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="62" t="n"/>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="62" t="n"/>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="62" t="n"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="62" t="n"/>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="62" t="n"/>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="62" t="n"/>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="62" t="n"/>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="62" t="n"/>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="62" t="n"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="62" t="n"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="62" t="n"/>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="62" t="n"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="62" t="n"/>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="62" t="n"/>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="62" t="n"/>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="62" t="n"/>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="62" t="n"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="62" t="n"/>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="62" t="n"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="62" t="n"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="62" t="n"/>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="62" t="n"/>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="62" t="n"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="62" t="n"/>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="62" t="n"/>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="62" t="n"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="62" t="n"/>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="62" t="n"/>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="62" t="n"/>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="62" t="n"/>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="62" t="n"/>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="62" t="n"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="62" t="n"/>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="62" t="n"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="62" t="n"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="62" t="n"/>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="62" t="n"/>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="62" t="n"/>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="62" t="n"/>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="62" t="n"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="62" t="n"/>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="62" t="n"/>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="62" t="n"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="62" t="n"/>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="62" t="n"/>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="62" t="n"/>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="62" t="n"/>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="62" t="n"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="62" t="n"/>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="62" t="n"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="62" t="n"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="62" t="n"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="62" t="n"/>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="62" t="n"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="62" t="n"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="62" t="n"/>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="62" t="n"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="62" t="n"/>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="62" t="n"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="62" t="n"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="62" t="n"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="62" t="n"/>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="62" t="n"/>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="62" t="n"/>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="62" t="n"/>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="62" t="n"/>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="62" t="n"/>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="62" t="n"/>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="62" t="n"/>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="62" t="n"/>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="62" t="n"/>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="62" t="n"/>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="62" t="n"/>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="62" t="n"/>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="62" t="n"/>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="62" t="n"/>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="62" t="n"/>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="62" t="n"/>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="62" t="n"/>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="62" t="n"/>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="62" t="n"/>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="62" t="n"/>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="62" t="n"/>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="62" t="n"/>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="62" t="n"/>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="62" t="n"/>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="62" t="n"/>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="62" t="n"/>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="62" t="n"/>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="62" t="n"/>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="62" t="n"/>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="62" t="n"/>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="62" t="n"/>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="62" t="n"/>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="62" t="n"/>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="62" t="n"/>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="62" t="n"/>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="62" t="n"/>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="62" t="n"/>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="62" t="n"/>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="62" t="n"/>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="62" t="n"/>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="62" t="n"/>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="62" t="n"/>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="62" t="n"/>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="62" t="n"/>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="62" t="n"/>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="62" t="n"/>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="62" t="n"/>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="62" t="n"/>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="62" t="n"/>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="62" t="n"/>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="62" t="n"/>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="62" t="n"/>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="62" t="n"/>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="62" t="n"/>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="62" t="n"/>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="62" t="n"/>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="62" t="n"/>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="62" t="n"/>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="62" t="n"/>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="62" t="n"/>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="62" t="n"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="62" t="n"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="62" t="n"/>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="62" t="n"/>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:A2003"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:A2002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -324,10 +324,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -336,7 +339,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -347,11 +350,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -363,12 +372,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <border>
         <left style="thin">
@@ -412,6 +422,13 @@
         <name val="Consolas"/>
         <sz val="9"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="49" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -532,7 +549,7 @@
     <tableColumn id="1" name="No" dataDxfId="2">
       <calculatedColumnFormula>IF(Packages[[#This Row],[원문]]="","",ROW()-3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="원문" dataDxfId="2"/>
+    <tableColumn id="2" name="원문" dataDxfId="3"/>
     <tableColumn id="3" name="이름" dataDxfId="2">
       <calculatedColumnFormula>IF(Packages[[#This Row],[원문]]="","",IFERROR(LEFT(Packages[[#This Row],[원문]],FIND(" ",Packages[[#This Row],[원문]])-1),""))</calculatedColumnFormula>
     </tableColumn>
@@ -545,7 +562,7 @@
     <tableColumn id="6" name="아키텍처" dataDxfId="2">
       <calculatedColumnFormula>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-1),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="설치 일시" dataDxfId="3">
+    <tableColumn id="7" name="설치 일시" dataDxfId="4">
       <calculatedColumnFormula>IF(Packages[[#This Row],[이름]]="","",IFERROR(VALUE(TRIM(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))+1,20)))/86400+25569+9/24,""))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1127,7 +1144,7 @@
           <t>참고</t>
         </is>
       </c>
-      <c r="C21" s="49" t="n"/>
+      <c r="C21" s="51" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1161,7 +1178,7 @@
           <t>RHEL 계열 9 구성 확인</t>
         </is>
       </c>
-      <c r="F1" s="51" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
@@ -1177,7 +1194,7 @@
         <f>IF(E6="","",E6)</f>
         <v/>
       </c>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
@@ -1189,8 +1206,8 @@
           <t>확인일</t>
         </is>
       </c>
-      <c r="C3" s="53" t="n"/>
-      <c r="F3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="F3" s="55" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="46" t="inlineStr">
@@ -1225,2086 +1242,2086 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55">
+      <c r="A6" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>호스트명</t>
         </is>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>hostname</t>
         </is>
       </c>
-      <c r="E6" s="58" t="n"/>
-      <c r="F6" s="59" t="n"/>
+      <c r="E6" s="59" t="n"/>
+      <c r="F6" s="60" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="55">
+      <c r="A7" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>OS 버전</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>cat /etc/redhat-release</t>
         </is>
       </c>
-      <c r="E7" s="58" t="n"/>
-      <c r="F7" s="59" t="n"/>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="60" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="55">
+      <c r="A8" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="57" t="inlineStr">
         <is>
           <t>OS 설치일</t>
         </is>
       </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>stat -c %w /</t>
         </is>
       </c>
-      <c r="E8" s="58" t="n"/>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="E8" s="59" t="n"/>
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>VM 템플릿 배포는 템플릿 생성일</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55">
+      <c r="A9" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C9" s="56" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>실행 커널</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>uname -r</t>
         </is>
       </c>
-      <c r="E9" s="58" t="n"/>
-      <c r="F9" s="59" t="n"/>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="60" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="55">
+      <c r="A10" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>설치된 커널</t>
         </is>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="58" t="inlineStr">
         <is>
           <t>rpm -q kernel</t>
         </is>
       </c>
-      <c r="E10" s="58" t="n"/>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>실행 커널보다 최신이면 재부팅 필요</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55">
+      <c r="A11" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C11" s="56" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>uname -m</t>
         </is>
       </c>
-      <c r="E11" s="58" t="n"/>
-      <c r="F11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="55">
+      <c r="A12" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C12" s="56" t="inlineStr">
+      <c r="C12" s="57" t="inlineStr">
         <is>
           <t>부팅 방식</t>
         </is>
       </c>
-      <c r="D12" s="57" t="inlineStr">
+      <c r="D12" s="58" t="inlineStr">
         <is>
           <t>ls /sys/firmware/efi</t>
         </is>
       </c>
-      <c r="E12" s="58" t="n"/>
-      <c r="F12" s="59" t="inlineStr">
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="inlineStr">
         <is>
           <t>경로가 있으면 UEFI</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55">
+      <c r="A13" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="57" t="inlineStr">
         <is>
           <t>부팅 옵션</t>
         </is>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>cat /proc/cmdline</t>
         </is>
       </c>
-      <c r="E13" s="58" t="n"/>
-      <c r="F13" s="59" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="55">
+      <c r="A14" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C14" s="56" t="inlineStr">
+      <c r="C14" s="57" t="inlineStr">
         <is>
           <t>마지막 부팅</t>
         </is>
       </c>
-      <c r="D14" s="57" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>who -b</t>
         </is>
       </c>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="59" t="n"/>
+      <c r="E14" s="62" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="55">
+      <c r="A15" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C15" s="56" t="inlineStr">
+      <c r="C15" s="57" t="inlineStr">
         <is>
           <t>장비 모델</t>
         </is>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>cat /sys/class/dmi/id/product_name</t>
         </is>
       </c>
-      <c r="E15" s="58" t="n"/>
-      <c r="F15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="55">
+      <c r="A16" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C16" s="56" t="inlineStr">
+      <c r="C16" s="57" t="inlineStr">
         <is>
           <t>시리얼번호</t>
         </is>
       </c>
-      <c r="D16" s="57" t="inlineStr">
+      <c r="D16" s="58" t="inlineStr">
         <is>
           <t>cat /sys/class/dmi/id/product_serial</t>
         </is>
       </c>
-      <c r="E16" s="58" t="n"/>
-      <c r="F16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="55">
+      <c r="A17" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B17" s="55" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C17" s="56" t="inlineStr">
+      <c r="C17" s="57" t="inlineStr">
         <is>
           <t>가상화</t>
         </is>
       </c>
-      <c r="D17" s="57" t="inlineStr">
+      <c r="D17" s="58" t="inlineStr">
         <is>
           <t>systemd-detect-virt</t>
         </is>
       </c>
-      <c r="E17" s="58" t="n"/>
-      <c r="F17" s="59" t="inlineStr">
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>none이면 물리</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55">
+      <c r="A18" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C18" s="56" t="inlineStr">
+      <c r="C18" s="57" t="inlineStr">
         <is>
           <t>CPU 모델</t>
         </is>
       </c>
-      <c r="D18" s="57" t="inlineStr">
+      <c r="D18" s="58" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i 'model name' | uniq</t>
         </is>
       </c>
-      <c r="E18" s="58" t="n"/>
-      <c r="F18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="55">
+      <c r="A19" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B19" s="55" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C19" s="56" t="inlineStr">
+      <c r="C19" s="57" t="inlineStr">
         <is>
           <t>CPU 소켓 수</t>
         </is>
       </c>
-      <c r="D19" s="57" t="inlineStr">
+      <c r="D19" s="58" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep 'physical id' | sort -u | wc -l</t>
         </is>
       </c>
-      <c r="E19" s="58" t="n"/>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="E19" s="61" t="n"/>
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55">
+      <c r="A20" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C20" s="56" t="inlineStr">
+      <c r="C20" s="57" t="inlineStr">
         <is>
           <t>소켓당 코어 수</t>
         </is>
       </c>
-      <c r="D20" s="57" t="inlineStr">
+      <c r="D20" s="58" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i 'cpu cores' | uniq</t>
         </is>
       </c>
-      <c r="E20" s="58" t="n"/>
-      <c r="F20" s="59" t="inlineStr">
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55">
+      <c r="A21" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B21" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C21" s="56" t="inlineStr">
+      <c r="C21" s="57" t="inlineStr">
         <is>
           <t>물리 코어 수</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="63" t="inlineStr">
         <is>
           <t>CPU 소켓 수 × 소켓당 코어 수</t>
         </is>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="64">
         <f>IF(COUNT(E19,E20)=2,E19*E20,"")</f>
         <v/>
       </c>
-      <c r="F21" s="59" t="inlineStr">
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55">
+      <c r="A22" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C22" s="56" t="inlineStr">
+      <c r="C22" s="57" t="inlineStr">
         <is>
           <t>논리 CPU 수</t>
         </is>
       </c>
-      <c r="D22" s="57" t="inlineStr">
+      <c r="D22" s="58" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i '^processor' | wc -l</t>
         </is>
       </c>
-      <c r="E22" s="58" t="n"/>
-      <c r="F22" s="59" t="inlineStr">
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="60" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55">
+      <c r="A23" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B23" s="55" t="inlineStr">
+      <c r="B23" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C23" s="56" t="inlineStr">
+      <c r="C23" s="57" t="inlineStr">
         <is>
           <t>하이퍼스레딩</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="D23" s="63" t="inlineStr">
         <is>
           <t>논리 CPU 수 = 물리 코어 수 × 2</t>
         </is>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="64">
         <f>IF(COUNT(E21,E22)=2,IF(E22=E21*2,"사용","미사용"),"")</f>
         <v/>
       </c>
-      <c r="F23" s="59" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55">
+      <c r="A24" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C24" s="56" t="inlineStr">
+      <c r="C24" s="57" t="inlineStr">
         <is>
           <t>OS 인식 메모리 (MiB)</t>
         </is>
       </c>
-      <c r="D24" s="57" t="inlineStr">
+      <c r="D24" s="58" t="inlineStr">
         <is>
           <t>free -m</t>
         </is>
       </c>
-      <c r="E24" s="58" t="n"/>
-      <c r="F24" s="59" t="inlineStr">
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="60" t="inlineStr">
         <is>
           <t>Mem total, 숫자만</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55">
+      <c r="A25" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B25" s="55" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C25" s="56" t="inlineStr">
+      <c r="C25" s="57" t="inlineStr">
         <is>
           <t>물리 메모리</t>
         </is>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D25" s="58" t="inlineStr">
         <is>
           <t>dmidecode -t memory | grep -i size | egrep -v 'No Module|Cache|Logical|Volatile'</t>
         </is>
       </c>
-      <c r="E25" s="58" t="n"/>
-      <c r="F25" s="59" t="inlineStr">
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="60" t="inlineStr">
         <is>
           <t>물리 서버</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55">
+      <c r="A26" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C26" s="56" t="inlineStr">
+      <c r="C26" s="57" t="inlineStr">
         <is>
           <t>GPU</t>
         </is>
       </c>
-      <c r="D26" s="57" t="inlineStr">
+      <c r="D26" s="58" t="inlineStr">
         <is>
           <t>nvidia-smi -L</t>
         </is>
       </c>
-      <c r="E26" s="58" t="n"/>
-      <c r="F26" s="59" t="inlineStr">
+      <c r="E26" s="61" t="n"/>
+      <c r="F26" s="60" t="inlineStr">
         <is>
           <t>GPU 서버</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55">
+      <c r="A27" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B27" s="55" t="inlineStr">
+      <c r="B27" s="56" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C27" s="56" t="inlineStr">
+      <c r="C27" s="57" t="inlineStr">
         <is>
           <t>시간대</t>
         </is>
       </c>
-      <c r="D27" s="57" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>timedatectl | grep 'Time zone'</t>
         </is>
       </c>
-      <c r="E27" s="58" t="n"/>
-      <c r="F27" s="59" t="n"/>
+      <c r="E27" s="59" t="n"/>
+      <c r="F27" s="60" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="55">
+      <c r="A28" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B28" s="55" t="inlineStr">
+      <c r="B28" s="56" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C28" s="56" t="inlineStr">
+      <c r="C28" s="57" t="inlineStr">
         <is>
           <t>시간 동기화 여부</t>
         </is>
       </c>
-      <c r="D28" s="57" t="inlineStr">
+      <c r="D28" s="58" t="inlineStr">
         <is>
           <t>timedatectl | egrep 'synchronized|NTP'</t>
         </is>
       </c>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="59" t="n"/>
+      <c r="E28" s="59" t="n"/>
+      <c r="F28" s="60" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="55">
+      <c r="A29" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B29" s="55" t="inlineStr">
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C29" s="56" t="inlineStr">
+      <c r="C29" s="57" t="inlineStr">
         <is>
           <t>타임 서버 (chrony)</t>
         </is>
       </c>
-      <c r="D29" s="57" t="inlineStr">
+      <c r="D29" s="58" t="inlineStr">
         <is>
           <t>chronyc sources -v</t>
         </is>
       </c>
-      <c r="E29" s="58" t="n"/>
-      <c r="F29" s="59" t="inlineStr">
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="60" t="inlineStr">
         <is>
           <t>* 표시가 동기 서버</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55">
+      <c r="A30" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B30" s="55" t="inlineStr">
+      <c r="B30" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C30" s="56" t="inlineStr">
+      <c r="C30" s="57" t="inlineStr">
         <is>
           <t>IP 주소</t>
         </is>
       </c>
-      <c r="D30" s="57" t="inlineStr">
+      <c r="D30" s="58" t="inlineStr">
         <is>
           <t>ip -br addr</t>
         </is>
       </c>
-      <c r="E30" s="58" t="n"/>
-      <c r="F30" s="59" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="60" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="55">
+      <c r="A31" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B31" s="55" t="inlineStr">
+      <c r="B31" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C31" s="56" t="inlineStr">
+      <c r="C31" s="57" t="inlineStr">
         <is>
           <t>MAC 주소</t>
         </is>
       </c>
-      <c r="D31" s="57" t="inlineStr">
+      <c r="D31" s="58" t="inlineStr">
         <is>
           <t>ip -br link</t>
         </is>
       </c>
-      <c r="E31" s="58" t="n"/>
-      <c r="F31" s="59" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="60" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="55">
+      <c r="A32" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B32" s="55" t="inlineStr">
+      <c r="B32" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C32" s="56" t="inlineStr">
+      <c r="C32" s="57" t="inlineStr">
         <is>
           <t>MTU</t>
         </is>
       </c>
-      <c r="D32" s="57" t="inlineStr">
+      <c r="D32" s="58" t="inlineStr">
         <is>
           <t>ip link | grep mtu</t>
         </is>
       </c>
-      <c r="E32" s="58" t="n"/>
-      <c r="F32" s="59" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="60" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="55">
+      <c r="A33" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B33" s="55" t="inlineStr">
+      <c r="B33" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C33" s="56" t="inlineStr">
+      <c r="C33" s="57" t="inlineStr">
         <is>
           <t>본딩 상태</t>
         </is>
       </c>
-      <c r="D33" s="57" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>tail -v -n +1 /proc/net/bonding/*</t>
         </is>
       </c>
-      <c r="E33" s="58" t="n"/>
-      <c r="F33" s="59" t="inlineStr">
+      <c r="E33" s="61" t="n"/>
+      <c r="F33" s="60" t="inlineStr">
         <is>
           <t>본딩 사용 시</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="55">
+      <c r="A34" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B34" s="55" t="inlineStr">
+      <c r="B34" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C34" s="56" t="inlineStr">
+      <c r="C34" s="57" t="inlineStr">
         <is>
           <t>IPv4 경로</t>
         </is>
       </c>
-      <c r="D34" s="57" t="inlineStr">
+      <c r="D34" s="58" t="inlineStr">
         <is>
           <t>ip route</t>
         </is>
       </c>
-      <c r="E34" s="58" t="n"/>
-      <c r="F34" s="59" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="60" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="55">
+      <c r="A35" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B35" s="55" t="inlineStr">
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C35" s="56" t="inlineStr">
+      <c r="C35" s="57" t="inlineStr">
         <is>
           <t>DNS 서버·도메인</t>
         </is>
       </c>
-      <c r="D35" s="57" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>cat /etc/resolv.conf</t>
         </is>
       </c>
-      <c r="E35" s="58" t="n"/>
-      <c r="F35" s="59" t="n"/>
+      <c r="E35" s="61" t="n"/>
+      <c r="F35" s="60" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="55">
+      <c r="A36" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B36" s="55" t="inlineStr">
+      <c r="B36" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C36" s="56" t="inlineStr">
+      <c r="C36" s="57" t="inlineStr">
         <is>
           <t>호스트 파일</t>
         </is>
       </c>
-      <c r="D36" s="57" t="inlineStr">
+      <c r="D36" s="58" t="inlineStr">
         <is>
           <t>cat /etc/hosts</t>
         </is>
       </c>
-      <c r="E36" s="58" t="n"/>
-      <c r="F36" s="59" t="n"/>
+      <c r="E36" s="61" t="n"/>
+      <c r="F36" s="60" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="55">
+      <c r="A37" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B37" s="55" t="inlineStr">
+      <c r="B37" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C37" s="56" t="inlineStr">
+      <c r="C37" s="57" t="inlineStr">
         <is>
           <t>네트워크 연결</t>
         </is>
       </c>
-      <c r="D37" s="57" t="inlineStr">
+      <c r="D37" s="58" t="inlineStr">
         <is>
           <t>nmcli connection show</t>
         </is>
       </c>
-      <c r="E37" s="58" t="n"/>
-      <c r="F37" s="59" t="n"/>
+      <c r="E37" s="61" t="n"/>
+      <c r="F37" s="60" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="55">
+      <c r="A38" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B38" s="55" t="inlineStr">
+      <c r="B38" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C38" s="56" t="inlineStr">
+      <c r="C38" s="57" t="inlineStr">
         <is>
           <t>저장된 네트워크 설정</t>
         </is>
       </c>
-      <c r="D38" s="57" t="inlineStr">
+      <c r="D38" s="58" t="inlineStr">
         <is>
           <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
-      <c r="E38" s="58" t="n"/>
-      <c r="F38" s="59" t="inlineStr">
+      <c r="E38" s="61" t="n"/>
+      <c r="F38" s="60" t="inlineStr">
         <is>
           <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55">
+      <c r="A39" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B39" s="55" t="inlineStr">
+      <c r="B39" s="56" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C39" s="56" t="inlineStr">
+      <c r="C39" s="57" t="inlineStr">
         <is>
           <t>링 버퍼 (RX/TX)</t>
         </is>
       </c>
-      <c r="D39" s="57" t="inlineStr">
+      <c r="D39" s="58" t="inlineStr">
         <is>
           <t>ethtool -g &lt;인터페이스&gt;</t>
         </is>
       </c>
-      <c r="E39" s="58" t="n"/>
-      <c r="F39" s="59" t="inlineStr">
+      <c r="E39" s="61" t="n"/>
+      <c r="F39" s="60" t="inlineStr">
         <is>
           <t>조정한 경우</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55">
+      <c r="A40" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B40" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C40" s="56" t="inlineStr">
+      <c r="C40" s="57" t="inlineStr">
         <is>
           <t>장치와 파일시스템</t>
         </is>
       </c>
-      <c r="D40" s="57" t="inlineStr">
+      <c r="D40" s="58" t="inlineStr">
         <is>
           <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
         </is>
       </c>
-      <c r="E40" s="58" t="n"/>
-      <c r="F40" s="59" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="60" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="55">
+      <c r="A41" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B41" s="55" t="inlineStr">
+      <c r="B41" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C41" s="56" t="inlineStr">
+      <c r="C41" s="57" t="inlineStr">
         <is>
           <t>파일시스템 사용량</t>
         </is>
       </c>
-      <c r="D41" s="57" t="inlineStr">
+      <c r="D41" s="58" t="inlineStr">
         <is>
           <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
         </is>
       </c>
-      <c r="E41" s="58" t="n"/>
-      <c r="F41" s="59" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="60" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="55">
+      <c r="A42" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B42" s="55" t="inlineStr">
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C42" s="56" t="inlineStr">
+      <c r="C42" s="57" t="inlineStr">
         <is>
           <t>현재 마운트</t>
         </is>
       </c>
-      <c r="D42" s="57" t="inlineStr">
+      <c r="D42" s="58" t="inlineStr">
         <is>
           <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
         </is>
       </c>
-      <c r="E42" s="58" t="n"/>
-      <c r="F42" s="59" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="60" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="55">
+      <c r="A43" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B43" s="55" t="inlineStr">
+      <c r="B43" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C43" s="56" t="inlineStr">
+      <c r="C43" s="57" t="inlineStr">
         <is>
           <t>저장된 마운트</t>
         </is>
       </c>
-      <c r="D43" s="57" t="inlineStr">
+      <c r="D43" s="58" t="inlineStr">
         <is>
           <t>cat /etc/fstab</t>
         </is>
       </c>
-      <c r="E43" s="58" t="n"/>
-      <c r="F43" s="59" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="60" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="55">
+      <c r="A44" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B44" s="55" t="inlineStr">
+      <c r="B44" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C44" s="56" t="inlineStr">
+      <c r="C44" s="57" t="inlineStr">
         <is>
           <t>스왑</t>
         </is>
       </c>
-      <c r="D44" s="57" t="inlineStr">
+      <c r="D44" s="58" t="inlineStr">
         <is>
           <t>cat /proc/swaps</t>
         </is>
       </c>
-      <c r="E44" s="58" t="n"/>
-      <c r="F44" s="59" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="60" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="55">
+      <c r="A45" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B45" s="55" t="inlineStr">
+      <c r="B45" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C45" s="56" t="inlineStr">
+      <c r="C45" s="57" t="inlineStr">
         <is>
           <t>LVM-PV</t>
         </is>
       </c>
-      <c r="D45" s="57" t="inlineStr">
+      <c r="D45" s="58" t="inlineStr">
         <is>
           <t>pvs</t>
         </is>
       </c>
-      <c r="E45" s="58" t="n"/>
-      <c r="F45" s="59" t="inlineStr">
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="60" t="inlineStr">
         <is>
           <t>LVM 사용 시</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55">
+      <c r="A46" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B46" s="55" t="inlineStr">
+      <c r="B46" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C46" s="56" t="inlineStr">
+      <c r="C46" s="57" t="inlineStr">
         <is>
           <t>LVM-VG</t>
         </is>
       </c>
-      <c r="D46" s="57" t="inlineStr">
+      <c r="D46" s="58" t="inlineStr">
         <is>
           <t>vgs</t>
         </is>
       </c>
-      <c r="E46" s="58" t="n"/>
-      <c r="F46" s="59" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="60" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="55">
+      <c r="A47" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B47" s="55" t="inlineStr">
+      <c r="B47" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C47" s="56" t="inlineStr">
+      <c r="C47" s="57" t="inlineStr">
         <is>
           <t>LVM-LV</t>
         </is>
       </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D47" s="58" t="inlineStr">
         <is>
           <t>lvs -a -o +devices</t>
         </is>
       </c>
-      <c r="E47" s="58" t="n"/>
-      <c r="F47" s="59" t="n"/>
+      <c r="E47" s="61" t="n"/>
+      <c r="F47" s="60" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="55">
+      <c r="A48" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B48" s="55" t="inlineStr">
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C48" s="56" t="inlineStr">
+      <c r="C48" s="57" t="inlineStr">
         <is>
           <t>SCSI 호스트</t>
         </is>
       </c>
-      <c r="D48" s="57" t="inlineStr">
+      <c r="D48" s="58" t="inlineStr">
         <is>
           <t>lsscsi -H</t>
         </is>
       </c>
-      <c r="E48" s="58" t="n"/>
-      <c r="F48" s="59" t="inlineStr">
+      <c r="E48" s="61" t="n"/>
+      <c r="F48" s="60" t="inlineStr">
         <is>
           <t>lsscsi 패키지</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55">
+      <c r="A49" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B49" s="55" t="inlineStr">
+      <c r="B49" s="56" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C49" s="56" t="inlineStr">
+      <c r="C49" s="57" t="inlineStr">
         <is>
           <t>SCSI 장치</t>
         </is>
       </c>
-      <c r="D49" s="57" t="inlineStr">
+      <c r="D49" s="58" t="inlineStr">
         <is>
           <t>lsscsi -is</t>
         </is>
       </c>
-      <c r="E49" s="58" t="n"/>
-      <c r="F49" s="59" t="inlineStr">
+      <c r="E49" s="61" t="n"/>
+      <c r="F49" s="60" t="inlineStr">
         <is>
           <t>lsscsi 패키지</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55">
+      <c r="A50" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B50" s="55" t="inlineStr">
+      <c r="B50" s="56" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C50" s="56" t="inlineStr">
+      <c r="C50" s="57" t="inlineStr">
         <is>
           <t>HBA 포트 (WWPN·상태·유형)</t>
         </is>
       </c>
-      <c r="D50" s="57" t="inlineStr">
+      <c r="D50" s="58" t="inlineStr">
         <is>
           <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
         </is>
       </c>
-      <c r="E50" s="58" t="n"/>
-      <c r="F50" s="59" t="inlineStr">
+      <c r="E50" s="61" t="n"/>
+      <c r="F50" s="60" t="inlineStr">
         <is>
           <t>SAN 사용 시</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="55">
+      <c r="A51" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B51" s="55" t="inlineStr">
+      <c r="B51" s="56" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C51" s="56" t="inlineStr">
+      <c r="C51" s="57" t="inlineStr">
         <is>
           <t>멀티패스 상태</t>
         </is>
       </c>
-      <c r="D51" s="57" t="inlineStr">
+      <c r="D51" s="58" t="inlineStr">
         <is>
           <t>multipath -ll</t>
         </is>
       </c>
-      <c r="E51" s="58" t="n"/>
-      <c r="F51" s="59" t="n"/>
+      <c r="E51" s="61" t="n"/>
+      <c r="F51" s="60" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="55">
+      <c r="A52" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B52" s="55" t="inlineStr">
+      <c r="B52" s="56" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C52" s="56" t="inlineStr">
+      <c r="C52" s="57" t="inlineStr">
         <is>
           <t>멀티패스 설정</t>
         </is>
       </c>
-      <c r="D52" s="57" t="inlineStr">
+      <c r="D52" s="58" t="inlineStr">
         <is>
           <t>cat /etc/multipath.conf</t>
         </is>
       </c>
-      <c r="E52" s="58" t="n"/>
-      <c r="F52" s="59" t="n"/>
+      <c r="E52" s="61" t="n"/>
+      <c r="F52" s="60" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="55">
+      <c r="A53" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B53" s="55" t="inlineStr">
+      <c r="B53" s="56" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C53" s="56" t="inlineStr">
+      <c r="C53" s="57" t="inlineStr">
         <is>
           <t>멀티패스 이름 매핑</t>
         </is>
       </c>
-      <c r="D53" s="57" t="inlineStr">
+      <c r="D53" s="58" t="inlineStr">
         <is>
           <t>cat /etc/multipath/bindings</t>
         </is>
       </c>
-      <c r="E53" s="58" t="n"/>
-      <c r="F53" s="59" t="n"/>
+      <c r="E53" s="61" t="n"/>
+      <c r="F53" s="60" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="55">
+      <c r="A54" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B54" s="55" t="inlineStr">
+      <c r="B54" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C54" s="56" t="inlineStr">
+      <c r="C54" s="57" t="inlineStr">
         <is>
           <t>로그인 가능 계정</t>
         </is>
       </c>
-      <c r="D54" s="57" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
         </is>
       </c>
-      <c r="E54" s="58" t="n"/>
-      <c r="F54" s="59" t="n"/>
+      <c r="E54" s="61" t="n"/>
+      <c r="F54" s="60" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="55">
+      <c r="A55" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B55" s="55" t="inlineStr">
+      <c r="B55" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C55" s="56" t="inlineStr">
+      <c r="C55" s="57" t="inlineStr">
         <is>
           <t>관리자 그룹</t>
         </is>
       </c>
-      <c r="D55" s="57" t="inlineStr">
+      <c r="D55" s="58" t="inlineStr">
         <is>
           <t>getent group wheel</t>
         </is>
       </c>
-      <c r="E55" s="58" t="n"/>
-      <c r="F55" s="59" t="n"/>
+      <c r="E55" s="59" t="n"/>
+      <c r="F55" s="60" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="55">
+      <c r="A56" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B56" s="55" t="inlineStr">
+      <c r="B56" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C56" s="56" t="inlineStr">
+      <c r="C56" s="57" t="inlineStr">
         <is>
           <t>SSH 설정</t>
         </is>
       </c>
-      <c r="D56" s="57" t="inlineStr">
+      <c r="D56" s="58" t="inlineStr">
         <is>
           <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
         </is>
       </c>
-      <c r="E56" s="58" t="n"/>
-      <c r="F56" s="59" t="inlineStr">
+      <c r="E56" s="59" t="n"/>
+      <c r="F56" s="60" t="inlineStr">
         <is>
           <t>allowusers 없으면 미설정</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55">
+      <c r="A57" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B57" s="55" t="inlineStr">
+      <c r="B57" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C57" s="56" t="inlineStr">
+      <c r="C57" s="57" t="inlineStr">
         <is>
           <t>방화벽 실행</t>
         </is>
       </c>
-      <c r="D57" s="57" t="inlineStr">
+      <c r="D57" s="58" t="inlineStr">
         <is>
           <t>systemctl is-active firewalld</t>
         </is>
       </c>
-      <c r="E57" s="58" t="n"/>
-      <c r="F57" s="59" t="n"/>
+      <c r="E57" s="59" t="n"/>
+      <c r="F57" s="60" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="55">
+      <c r="A58" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B58" s="55" t="inlineStr">
+      <c r="B58" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C58" s="56" t="inlineStr">
+      <c r="C58" s="57" t="inlineStr">
         <is>
           <t>방화벽 부팅 시 시작</t>
         </is>
       </c>
-      <c r="D58" s="57" t="inlineStr">
+      <c r="D58" s="58" t="inlineStr">
         <is>
           <t>systemctl is-enabled firewalld</t>
         </is>
       </c>
-      <c r="E58" s="58" t="n"/>
-      <c r="F58" s="59" t="n"/>
+      <c r="E58" s="59" t="n"/>
+      <c r="F58" s="60" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="55">
+      <c r="A59" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B59" s="55" t="inlineStr">
+      <c r="B59" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C59" s="56" t="inlineStr">
+      <c r="C59" s="57" t="inlineStr">
         <is>
           <t>방화벽 응답</t>
         </is>
       </c>
-      <c r="D59" s="57" t="inlineStr">
+      <c r="D59" s="58" t="inlineStr">
         <is>
           <t>firewall-cmd --state</t>
         </is>
       </c>
-      <c r="E59" s="58" t="n"/>
-      <c r="F59" s="59" t="inlineStr">
+      <c r="E59" s="59" t="n"/>
+      <c r="F59" s="60" t="inlineStr">
         <is>
           <t>not running이면 미사용</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="55">
+      <c r="A60" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B60" s="55" t="inlineStr">
+      <c r="B60" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C60" s="56" t="inlineStr">
+      <c r="C60" s="57" t="inlineStr">
         <is>
           <t>방화벽 영역</t>
         </is>
       </c>
-      <c r="D60" s="57" t="inlineStr">
+      <c r="D60" s="58" t="inlineStr">
         <is>
           <t>firewall-cmd --get-active-zones</t>
         </is>
       </c>
-      <c r="E60" s="58" t="n"/>
-      <c r="F60" s="59" t="n"/>
+      <c r="E60" s="59" t="n"/>
+      <c r="F60" s="60" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="55">
+      <c r="A61" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B61" s="55" t="inlineStr">
+      <c r="B61" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C61" s="56" t="inlineStr">
+      <c r="C61" s="57" t="inlineStr">
         <is>
           <t>방화벽 규칙</t>
         </is>
       </c>
-      <c r="D61" s="57" t="inlineStr">
+      <c r="D61" s="58" t="inlineStr">
         <is>
           <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
-      <c r="E61" s="58" t="n"/>
-      <c r="F61" s="59" t="inlineStr">
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="60" t="inlineStr">
         <is>
           <t>활성 영역마다</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55">
+      <c r="A62" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B62" s="55" t="inlineStr">
+      <c r="B62" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C62" s="56" t="inlineStr">
+      <c r="C62" s="57" t="inlineStr">
         <is>
           <t>방화벽 저장 규칙</t>
         </is>
       </c>
-      <c r="D62" s="57" t="inlineStr">
+      <c r="D62" s="58" t="inlineStr">
         <is>
           <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
-      <c r="E62" s="58" t="n"/>
-      <c r="F62" s="59" t="inlineStr">
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="60" t="inlineStr">
         <is>
           <t>규칙과 다르면 표시</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55">
+      <c r="A63" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B63" s="55" t="inlineStr">
+      <c r="B63" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C63" s="56" t="inlineStr">
+      <c r="C63" s="57" t="inlineStr">
         <is>
           <t>보안 모듈 (SELinux)</t>
         </is>
       </c>
-      <c r="D63" s="57" t="inlineStr">
+      <c r="D63" s="58" t="inlineStr">
         <is>
           <t>getenforce</t>
         </is>
       </c>
-      <c r="E63" s="58" t="n"/>
-      <c r="F63" s="59" t="n"/>
+      <c r="E63" s="59" t="n"/>
+      <c r="F63" s="60" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="55">
+      <c r="A64" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B64" s="55" t="inlineStr">
+      <c r="B64" s="56" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C64" s="56" t="inlineStr">
+      <c r="C64" s="57" t="inlineStr">
         <is>
           <t>보안 모듈 부팅 설정</t>
         </is>
       </c>
-      <c r="D64" s="57" t="inlineStr">
+      <c r="D64" s="58" t="inlineStr">
         <is>
           <t>grep ^SELINUX= /etc/selinux/config</t>
         </is>
       </c>
-      <c r="E64" s="58" t="n"/>
-      <c r="F64" s="59" t="n"/>
+      <c r="E64" s="59" t="n"/>
+      <c r="F64" s="60" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="55">
+      <c r="A65" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B65" s="55" t="inlineStr">
+      <c r="B65" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C65" s="56" t="inlineStr">
+      <c r="C65" s="57" t="inlineStr">
         <is>
           <t>주요 패키지</t>
         </is>
       </c>
-      <c r="D65" s="57" t="inlineStr">
+      <c r="D65" s="58" t="inlineStr">
         <is>
           <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
         </is>
       </c>
-      <c r="E65" s="58" t="n"/>
-      <c r="F65" s="59" t="n"/>
+      <c r="E65" s="61" t="n"/>
+      <c r="F65" s="60" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="55">
+      <c r="A66" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B66" s="55" t="inlineStr">
+      <c r="B66" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C66" s="56" t="inlineStr">
+      <c r="C66" s="57" t="inlineStr">
         <is>
           <t>전체 패키지</t>
         </is>
       </c>
-      <c r="D66" s="57" t="inlineStr">
+      <c r="D66" s="58" t="inlineStr">
         <is>
           <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
         </is>
       </c>
-      <c r="E66" s="58" t="inlineStr">
+      <c r="E66" s="59" t="inlineStr">
         <is>
           <t>패키지 시트 참고</t>
         </is>
       </c>
-      <c r="F66" s="59" t="n"/>
+      <c r="F66" s="60" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="55">
+      <c r="A67" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B67" s="55" t="inlineStr">
+      <c r="B67" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C67" s="56" t="inlineStr">
+      <c r="C67" s="57" t="inlineStr">
         <is>
           <t>최근 패치일</t>
         </is>
       </c>
-      <c r="D67" s="57" t="inlineStr">
+      <c r="D67" s="58" t="inlineStr">
         <is>
           <t>dnf history</t>
         </is>
       </c>
-      <c r="E67" s="58" t="n"/>
-      <c r="F67" s="59" t="inlineStr">
+      <c r="E67" s="61" t="n"/>
+      <c r="F67" s="60" t="inlineStr">
         <is>
           <t>Action(s)에 U가 든 줄</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="55">
+      <c r="A68" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B68" s="55" t="inlineStr">
+      <c r="B68" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C68" s="56" t="inlineStr">
+      <c r="C68" s="57" t="inlineStr">
         <is>
           <t>자동 업데이트 설정</t>
         </is>
       </c>
-      <c r="D68" s="57" t="inlineStr">
+      <c r="D68" s="58" t="inlineStr">
         <is>
           <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
         </is>
       </c>
-      <c r="E68" s="58" t="n"/>
-      <c r="F68" s="59" t="inlineStr">
+      <c r="E68" s="61" t="n"/>
+      <c r="F68" s="60" t="inlineStr">
         <is>
           <t>파일 없으면 미설치</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="55">
+      <c r="A69" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B69" s="55" t="inlineStr">
+      <c r="B69" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C69" s="56" t="inlineStr">
+      <c r="C69" s="57" t="inlineStr">
         <is>
           <t>자동 업데이트 예약</t>
         </is>
       </c>
-      <c r="D69" s="57" t="inlineStr">
+      <c r="D69" s="58" t="inlineStr">
         <is>
           <t>systemctl list-unit-files 'dnf-automatic*'</t>
         </is>
       </c>
-      <c r="E69" s="58" t="n"/>
-      <c r="F69" s="59" t="inlineStr">
+      <c r="E69" s="61" t="n"/>
+      <c r="F69" s="60" t="inlineStr">
         <is>
           <t>enabled면 사용</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55">
+      <c r="A70" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B70" s="55" t="inlineStr">
+      <c r="B70" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C70" s="56" t="inlineStr">
+      <c r="C70" s="57" t="inlineStr">
         <is>
           <t>저장소 목록</t>
         </is>
       </c>
-      <c r="D70" s="57" t="inlineStr">
+      <c r="D70" s="58" t="inlineStr">
         <is>
           <t>dnf repolist</t>
         </is>
       </c>
-      <c r="E70" s="58" t="n"/>
-      <c r="F70" s="59" t="n"/>
+      <c r="E70" s="61" t="n"/>
+      <c r="F70" s="60" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="55">
+      <c r="A71" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B71" s="55" t="inlineStr">
+      <c r="B71" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C71" s="56" t="inlineStr">
+      <c r="C71" s="57" t="inlineStr">
         <is>
           <t>저장소 파일</t>
         </is>
       </c>
-      <c r="D71" s="57" t="inlineStr">
+      <c r="D71" s="58" t="inlineStr">
         <is>
           <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
-      <c r="E71" s="58" t="n"/>
-      <c r="F71" s="59" t="n"/>
+      <c r="E71" s="61" t="n"/>
+      <c r="F71" s="60" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="55">
+      <c r="A72" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B72" s="55" t="inlineStr">
+      <c r="B72" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C72" s="56" t="inlineStr">
+      <c r="C72" s="57" t="inlineStr">
         <is>
           <t>구독 등록 여부</t>
         </is>
       </c>
-      <c r="D72" s="57" t="inlineStr">
+      <c r="D72" s="58" t="inlineStr">
         <is>
           <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
-      <c r="E72" s="58" t="n"/>
-      <c r="F72" s="59" t="inlineStr">
+      <c r="E72" s="59" t="n"/>
+      <c r="F72" s="60" t="inlineStr">
         <is>
           <t>파일 없으면 미등록</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="55">
+      <c r="A73" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B73" s="55" t="inlineStr">
+      <c r="B73" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C73" s="56" t="inlineStr">
+      <c r="C73" s="57" t="inlineStr">
         <is>
           <t>구독 (RHSM)</t>
         </is>
       </c>
-      <c r="D73" s="57" t="inlineStr">
+      <c r="D73" s="58" t="inlineStr">
         <is>
           <t>subscription-manager status</t>
         </is>
       </c>
-      <c r="E73" s="58" t="n"/>
-      <c r="F73" s="59" t="inlineStr">
+      <c r="E73" s="61" t="n"/>
+      <c r="F73" s="60" t="inlineStr">
         <is>
           <t>RHEL</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="55">
+      <c r="A74" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B74" s="55" t="inlineStr">
+      <c r="B74" s="56" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C74" s="56" t="inlineStr">
+      <c r="C74" s="57" t="inlineStr">
         <is>
           <t>릴리스 고정</t>
         </is>
       </c>
-      <c r="D74" s="57" t="inlineStr">
+      <c r="D74" s="58" t="inlineStr">
         <is>
           <t>subscription-manager release --show</t>
         </is>
       </c>
-      <c r="E74" s="58" t="n"/>
-      <c r="F74" s="59" t="inlineStr">
+      <c r="E74" s="59" t="n"/>
+      <c r="F74" s="60" t="inlineStr">
         <is>
           <t>Release not set이면 미고정</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="55">
+      <c r="A75" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B75" s="55" t="inlineStr">
+      <c r="B75" s="56" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C75" s="56" t="inlineStr">
+      <c r="C75" s="57" t="inlineStr">
         <is>
           <t>sysctl</t>
         </is>
       </c>
-      <c r="D75" s="57" t="inlineStr">
+      <c r="D75" s="58" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
         </is>
       </c>
-      <c r="E75" s="58" t="n"/>
-      <c r="F75" s="59" t="inlineStr">
+      <c r="E75" s="61" t="n"/>
+      <c r="F75" s="60" t="inlineStr">
         <is>
           <t>99-sysctl.conf 줄은 중복</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55">
+      <c r="A76" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B76" s="55" t="inlineStr">
+      <c r="B76" s="56" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C76" s="56" t="inlineStr">
+      <c r="C76" s="57" t="inlineStr">
         <is>
           <t>자원 제한 (limits)</t>
         </is>
       </c>
-      <c r="D76" s="57" t="inlineStr">
+      <c r="D76" s="58" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
-      <c r="E76" s="58" t="n"/>
-      <c r="F76" s="59" t="n"/>
+      <c r="E76" s="61" t="n"/>
+      <c r="F76" s="60" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="55">
+      <c r="A77" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B77" s="55" t="inlineStr">
+      <c r="B77" s="56" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C77" s="56" t="inlineStr">
+      <c r="C77" s="57" t="inlineStr">
         <is>
           <t>kdump 설정</t>
         </is>
       </c>
-      <c r="D77" s="57" t="inlineStr">
+      <c r="D77" s="58" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
-      <c r="E77" s="58" t="n"/>
-      <c r="F77" s="59" t="n"/>
+      <c r="E77" s="61" t="n"/>
+      <c r="F77" s="60" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="55">
+      <c r="A78" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B78" s="55" t="inlineStr">
+      <c r="B78" s="56" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C78" s="56" t="inlineStr">
+      <c r="C78" s="57" t="inlineStr">
         <is>
           <t>kdump 실행</t>
         </is>
       </c>
-      <c r="D78" s="57" t="inlineStr">
+      <c r="D78" s="58" t="inlineStr">
         <is>
           <t>systemctl is-active kdump</t>
         </is>
       </c>
-      <c r="E78" s="58" t="n"/>
-      <c r="F78" s="59" t="n"/>
+      <c r="E78" s="59" t="n"/>
+      <c r="F78" s="60" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="55">
+      <c r="A79" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B79" s="55" t="inlineStr">
+      <c r="B79" s="56" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C79" s="56" t="inlineStr">
+      <c r="C79" s="57" t="inlineStr">
         <is>
           <t>kdump 부팅 시 시작</t>
         </is>
       </c>
-      <c r="D79" s="57" t="inlineStr">
+      <c r="D79" s="58" t="inlineStr">
         <is>
           <t>systemctl is-enabled kdump</t>
         </is>
       </c>
-      <c r="E79" s="58" t="n"/>
-      <c r="F79" s="59" t="n"/>
+      <c r="E79" s="59" t="n"/>
+      <c r="F79" s="60" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="55">
+      <c r="A80" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B80" s="55" t="inlineStr">
+      <c r="B80" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C80" s="56" t="inlineStr">
+      <c r="C80" s="57" t="inlineStr">
         <is>
           <t>실행 중인 서비스</t>
         </is>
       </c>
-      <c r="D80" s="57" t="inlineStr">
+      <c r="D80" s="58" t="inlineStr">
         <is>
           <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
-      <c r="E80" s="58" t="n"/>
-      <c r="F80" s="59" t="n"/>
+      <c r="E80" s="61" t="n"/>
+      <c r="F80" s="60" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="55">
+      <c r="A81" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B81" s="55" t="inlineStr">
+      <c r="B81" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C81" s="56" t="inlineStr">
+      <c r="C81" s="57" t="inlineStr">
         <is>
           <t>자동 시작 서비스</t>
         </is>
       </c>
-      <c r="D81" s="57" t="inlineStr">
+      <c r="D81" s="58" t="inlineStr">
         <is>
           <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
-      <c r="E81" s="58" t="n"/>
-      <c r="F81" s="59" t="n"/>
+      <c r="E81" s="61" t="n"/>
+      <c r="F81" s="60" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="55">
+      <c r="A82" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B82" s="55" t="inlineStr">
+      <c r="B82" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C82" s="56" t="inlineStr">
+      <c r="C82" s="57" t="inlineStr">
         <is>
           <t>열린 포트</t>
         </is>
       </c>
-      <c r="D82" s="57" t="inlineStr">
+      <c r="D82" s="58" t="inlineStr">
         <is>
           <t>ss -tulnp</t>
         </is>
       </c>
-      <c r="E82" s="58" t="n"/>
-      <c r="F82" s="59" t="n"/>
+      <c r="E82" s="61" t="n"/>
+      <c r="F82" s="60" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="55">
+      <c r="A83" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B83" s="55" t="inlineStr">
+      <c r="B83" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C83" s="56" t="inlineStr">
+      <c r="C83" s="57" t="inlineStr">
         <is>
           <t>예약 작업 (타이머)</t>
         </is>
       </c>
-      <c r="D83" s="57" t="inlineStr">
+      <c r="D83" s="58" t="inlineStr">
         <is>
           <t>systemctl list-timers --all --no-pager</t>
         </is>
       </c>
-      <c r="E83" s="58" t="n"/>
-      <c r="F83" s="59" t="n"/>
+      <c r="E83" s="61" t="n"/>
+      <c r="F83" s="60" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="55">
+      <c r="A84" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B84" s="55" t="inlineStr">
+      <c r="B84" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C84" s="56" t="inlineStr">
+      <c r="C84" s="57" t="inlineStr">
         <is>
           <t>예약 작업 (crontab)</t>
         </is>
       </c>
-      <c r="D84" s="57" t="inlineStr">
+      <c r="D84" s="58" t="inlineStr">
         <is>
           <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
-      <c r="E84" s="58" t="n"/>
-      <c r="F84" s="59" t="inlineStr">
+      <c r="E84" s="61" t="n"/>
+      <c r="F84" s="60" t="inlineStr">
         <is>
           <t>파일명이 계정명</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="55">
+      <c r="A85" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B85" s="55" t="inlineStr">
+      <c r="B85" s="56" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C85" s="56" t="inlineStr">
+      <c r="C85" s="57" t="inlineStr">
         <is>
           <t>예약 작업 (cron.d)</t>
         </is>
       </c>
-      <c r="D85" s="57" t="inlineStr">
+      <c r="D85" s="58" t="inlineStr">
         <is>
           <t>ls /etc/cron.d</t>
         </is>
       </c>
-      <c r="E85" s="58" t="n"/>
-      <c r="F85" s="59" t="n"/>
+      <c r="E85" s="61" t="n"/>
+      <c r="F85" s="60" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="55">
+      <c r="A86" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B86" s="55" t="inlineStr">
+      <c r="B86" s="56" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C86" s="56" t="inlineStr">
+      <c r="C86" s="57" t="inlineStr">
         <is>
           <t>모니터링 에이전트</t>
         </is>
       </c>
-      <c r="D86" s="57" t="inlineStr">
+      <c r="D86" s="58" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E86" s="58" t="n"/>
-      <c r="F86" s="59" t="inlineStr">
+      <c r="E86" s="61" t="n"/>
+      <c r="F86" s="60" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="55">
+      <c r="A87" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B87" s="55" t="inlineStr">
+      <c r="B87" s="56" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C87" s="56" t="inlineStr">
+      <c r="C87" s="57" t="inlineStr">
         <is>
           <t>보안 에이전트</t>
         </is>
       </c>
-      <c r="D87" s="57" t="inlineStr">
+      <c r="D87" s="58" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E87" s="58" t="n"/>
-      <c r="F87" s="59" t="inlineStr">
+      <c r="E87" s="61" t="n"/>
+      <c r="F87" s="60" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="55">
+      <c r="A88" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B88" s="55" t="inlineStr">
+      <c r="B88" s="56" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C88" s="56" t="inlineStr">
+      <c r="C88" s="57" t="inlineStr">
         <is>
           <t>백신</t>
         </is>
       </c>
-      <c r="D88" s="57" t="inlineStr">
+      <c r="D88" s="58" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E88" s="58" t="n"/>
-      <c r="F88" s="59" t="inlineStr">
+      <c r="E88" s="61" t="n"/>
+      <c r="F88" s="60" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="55">
+      <c r="A89" s="56">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B89" s="55" t="inlineStr">
+      <c r="B89" s="56" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C89" s="56" t="inlineStr">
+      <c r="C89" s="57" t="inlineStr">
         <is>
           <t>설정 백업</t>
         </is>
       </c>
-      <c r="D89" s="57" t="inlineStr">
+      <c r="D89" s="58" t="inlineStr">
         <is>
           <t>백업 위치, 마지막 백업 날짜</t>
         </is>
       </c>
-      <c r="E89" s="58" t="n"/>
-      <c r="F89" s="59" t="inlineStr">
+      <c r="E89" s="59" t="n"/>
+      <c r="F89" s="60" t="inlineStr">
         <is>
           <t>직접 입력</t>
         </is>
@@ -3353,7 +3370,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3363,55 +3380,55 @@
           <t>원문</t>
         </is>
       </c>
-      <c r="C3" s="62" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="62" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="E3" s="62" t="inlineStr">
+      <c r="E3" s="65" t="inlineStr">
         <is>
           <t>릴리스</t>
         </is>
       </c>
-      <c r="F3" s="62" t="inlineStr">
+      <c r="F3" s="65" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="G3" s="62" t="inlineStr">
+      <c r="G3" s="65" t="inlineStr">
         <is>
           <t>설치 일시</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63">
+      <c r="A4" s="66">
         <f>IF(Packages[[#This Row],[원문]]="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B4" s="63" t="n"/>
-      <c r="C4" s="63">
+      <c r="B4" s="67" t="n"/>
+      <c r="C4" s="66">
         <f>IF(Packages[[#This Row],[원문]]="","",IFERROR(LEFT(Packages[[#This Row],[원문]],FIND(" ",Packages[[#This Row],[원문]])-1),""))</f>
         <v/>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="66">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))-1),""))</f>
         <v/>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="66">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-1),""))</f>
         <v/>
       </c>
-      <c r="F4" s="63">
+      <c r="F4" s="66">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-1),""))</f>
         <v/>
       </c>
-      <c r="G4" s="64">
+      <c r="G4" s="68">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(VALUE(TRIM(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))+1,20)))/86400+25569+9/24,""))</f>
         <v/>
       </c>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D52" s="58" t="inlineStr">
         <is>
-          <t>cat /etc/multipath.conf</t>
+          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
         </is>
       </c>
       <c r="E52" s="61" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D33" s="58" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /proc/net/bonding/*</t>
+          <t>grep -H . /proc/net/bonding/*</t>
         </is>
       </c>
       <c r="E33" s="61" t="n"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D38" s="58" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
+          <t>grep -H . /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
       <c r="E38" s="61" t="n"/>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="D73" s="58" t="inlineStr">
         <is>
-          <t>subscription-manager status</t>
+          <t>subscription-manager status | grep :</t>
         </is>
       </c>
       <c r="E73" s="61" t="n"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D84" s="58" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /var/spool/cron/*</t>
+          <t>grep -H . /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E84" s="61" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D33" s="58" t="inlineStr">
         <is>
-          <t>grep -H . /proc/net/bonding/*</t>
+          <t>awk 'FNR==1{print "["FILENAME"]"}1' /proc/net/bonding/*</t>
         </is>
       </c>
       <c r="E33" s="61" t="n"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D38" s="58" t="inlineStr">
         <is>
-          <t>grep -H . /etc/NetworkManager/system-connections/*.nmconnection</t>
+          <t>awk 'FNR==1{print "["FILENAME"]"}1' /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
       <c r="E38" s="61" t="n"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D84" s="58" t="inlineStr">
         <is>
-          <t>grep -H . /var/spool/cron/*</t>
+          <t>awk 'FNR==1{print "["FILENAME"]"}1' /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E84" s="61" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D33" s="58" t="inlineStr">
         <is>
-          <t>awk 'FNR==1{print "["FILENAME"]"}1' /proc/net/bonding/*</t>
+          <t>tail -v -n +1 /proc/net/bonding/*</t>
         </is>
       </c>
       <c r="E33" s="61" t="n"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D38" s="58" t="inlineStr">
         <is>
-          <t>awk 'FNR==1{print "["FILENAME"]"}1' /etc/NetworkManager/system-connections/*.nmconnection</t>
+          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
       <c r="E38" s="61" t="n"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D84" s="58" t="inlineStr">
         <is>
-          <t>awk 'FNR==1{print "["FILENAME"]"}1' /var/spool/cron/*</t>
+          <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E84" s="61" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,9 +330,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -355,12 +352,6 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1144,7 +1135,7 @@
           <t>참고</t>
         </is>
       </c>
-      <c r="C21" s="51" t="n"/>
+      <c r="C21" s="49" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1178,7 +1169,7 @@
           <t>RHEL 계열 9 구성 확인</t>
         </is>
       </c>
-      <c r="F1" s="52" t="inlineStr">
+      <c r="F1" s="51" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
@@ -1194,7 +1185,7 @@
         <f>IF(E6="","",E6)</f>
         <v/>
       </c>
-      <c r="F2" s="53" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
@@ -1206,8 +1197,8 @@
           <t>확인일</t>
         </is>
       </c>
-      <c r="C3" s="54" t="n"/>
-      <c r="F3" s="55" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="F3" s="54" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="46" t="inlineStr">
@@ -1242,2086 +1233,2086 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56">
+      <c r="A6" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>호스트명</t>
         </is>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>hostname</t>
         </is>
       </c>
-      <c r="E6" s="59" t="n"/>
-      <c r="F6" s="60" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="59" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="56">
+      <c r="A7" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C7" s="57" t="inlineStr">
+      <c r="C7" s="56" t="inlineStr">
         <is>
           <t>OS 버전</t>
         </is>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>cat /etc/redhat-release</t>
         </is>
       </c>
-      <c r="E7" s="59" t="n"/>
-      <c r="F7" s="60" t="n"/>
+      <c r="E7" s="58" t="n"/>
+      <c r="F7" s="59" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="56">
+      <c r="A8" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>OS 설치일</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>stat -c %w /</t>
         </is>
       </c>
-      <c r="E8" s="59" t="n"/>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="E8" s="58" t="n"/>
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>VM 템플릿 배포는 템플릿 생성일</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="56">
+      <c r="A9" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C9" s="56" t="inlineStr">
         <is>
           <t>실행 커널</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>uname -r</t>
         </is>
       </c>
-      <c r="E9" s="59" t="n"/>
-      <c r="F9" s="60" t="n"/>
+      <c r="E9" s="58" t="n"/>
+      <c r="F9" s="59" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="56">
+      <c r="A10" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C10" s="57" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>설치된 커널</t>
         </is>
       </c>
-      <c r="D10" s="58" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>rpm -q kernel</t>
         </is>
       </c>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="E10" s="58" t="n"/>
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>실행 커널보다 최신이면 재부팅 필요</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="56">
+      <c r="A11" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C11" s="57" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="D11" s="58" t="inlineStr">
+      <c r="D11" s="57" t="inlineStr">
         <is>
           <t>uname -m</t>
         </is>
       </c>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="60" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="59" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="56">
+      <c r="A12" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C12" s="57" t="inlineStr">
+      <c r="C12" s="56" t="inlineStr">
         <is>
           <t>부팅 방식</t>
         </is>
       </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>ls /sys/firmware/efi</t>
         </is>
       </c>
-      <c r="E12" s="59" t="n"/>
-      <c r="F12" s="60" t="inlineStr">
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>경로가 있으면 UEFI</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="56">
+      <c r="A13" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C13" s="57" t="inlineStr">
+      <c r="C13" s="56" t="inlineStr">
         <is>
           <t>부팅 옵션</t>
         </is>
       </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>cat /proc/cmdline</t>
         </is>
       </c>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="60" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="59" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="56">
+      <c r="A14" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="56" t="inlineStr">
         <is>
           <t>마지막 부팅</t>
         </is>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="57" t="inlineStr">
         <is>
           <t>who -b</t>
         </is>
       </c>
-      <c r="E14" s="62" t="n"/>
-      <c r="F14" s="60" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="59" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="56">
+      <c r="A15" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C15" s="57" t="inlineStr">
+      <c r="C15" s="56" t="inlineStr">
         <is>
           <t>장비 모델</t>
         </is>
       </c>
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="57" t="inlineStr">
         <is>
           <t>cat /sys/class/dmi/id/product_name</t>
         </is>
       </c>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="60" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="59" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="56">
+      <c r="A16" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B16" s="56" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C16" s="57" t="inlineStr">
+      <c r="C16" s="56" t="inlineStr">
         <is>
           <t>시리얼번호</t>
         </is>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="57" t="inlineStr">
         <is>
           <t>cat /sys/class/dmi/id/product_serial</t>
         </is>
       </c>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="60" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="59" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="56">
+      <c r="A17" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="C17" s="57" t="inlineStr">
+      <c r="C17" s="56" t="inlineStr">
         <is>
           <t>가상화</t>
         </is>
       </c>
-      <c r="D17" s="58" t="inlineStr">
+      <c r="D17" s="57" t="inlineStr">
         <is>
           <t>systemd-detect-virt</t>
         </is>
       </c>
-      <c r="E17" s="59" t="n"/>
-      <c r="F17" s="60" t="inlineStr">
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="59" t="inlineStr">
         <is>
           <t>none이면 물리</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="56">
+      <c r="A18" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C18" s="57" t="inlineStr">
+      <c r="C18" s="56" t="inlineStr">
         <is>
           <t>CPU 모델</t>
         </is>
       </c>
-      <c r="D18" s="58" t="inlineStr">
+      <c r="D18" s="57" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i 'model name' | uniq</t>
         </is>
       </c>
-      <c r="E18" s="59" t="n"/>
-      <c r="F18" s="60" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="59" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="56">
+      <c r="A19" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C19" s="57" t="inlineStr">
+      <c r="C19" s="56" t="inlineStr">
         <is>
           <t>CPU 소켓 수</t>
         </is>
       </c>
-      <c r="D19" s="58" t="inlineStr">
+      <c r="D19" s="57" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep 'physical id' | sort -u | wc -l</t>
         </is>
       </c>
-      <c r="E19" s="61" t="n"/>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="56">
+      <c r="A20" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C20" s="57" t="inlineStr">
+      <c r="C20" s="56" t="inlineStr">
         <is>
           <t>소켓당 코어 수</t>
         </is>
       </c>
-      <c r="D20" s="58" t="inlineStr">
+      <c r="D20" s="57" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i 'cpu cores' | uniq</t>
         </is>
       </c>
-      <c r="E20" s="61" t="n"/>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="56">
+      <c r="A21" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C21" s="57" t="inlineStr">
+      <c r="C21" s="56" t="inlineStr">
         <is>
           <t>물리 코어 수</t>
         </is>
       </c>
-      <c r="D21" s="63" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr">
         <is>
           <t>CPU 소켓 수 × 소켓당 코어 수</t>
         </is>
       </c>
-      <c r="E21" s="64">
-        <f>IF(COUNT(E19,E20)=2,E19*E20,"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="60" t="inlineStr">
+      <c r="E21" s="61">
+        <f>IF(OR(E19="",E20=""),"",IFERROR(VALUE(E19)*VALUE(E20),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="59" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="56">
+      <c r="A22" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B22" s="56" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C22" s="57" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
         <is>
           <t>논리 CPU 수</t>
         </is>
       </c>
-      <c r="D22" s="58" t="inlineStr">
+      <c r="D22" s="57" t="inlineStr">
         <is>
           <t>cat /proc/cpuinfo | grep -i '^processor' | wc -l</t>
         </is>
       </c>
-      <c r="E22" s="61" t="n"/>
-      <c r="F22" s="60" t="inlineStr">
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="56">
+      <c r="A23" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C23" s="57" t="inlineStr">
+      <c r="C23" s="56" t="inlineStr">
         <is>
           <t>하이퍼스레딩</t>
         </is>
       </c>
-      <c r="D23" s="63" t="inlineStr">
+      <c r="D23" s="60" t="inlineStr">
         <is>
           <t>논리 CPU 수 = 물리 코어 수 × 2</t>
         </is>
       </c>
-      <c r="E23" s="64">
-        <f>IF(COUNT(E21,E22)=2,IF(E22=E21*2,"사용","미사용"),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="60" t="inlineStr">
+      <c r="E23" s="61">
+        <f>IF(OR(E21="",E22=""),"",IFERROR(IF(VALUE(E22)=E21*2,"사용","미사용"),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
         <is>
           <t>수식</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56">
+      <c r="A24" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C24" s="57" t="inlineStr">
+      <c r="C24" s="56" t="inlineStr">
         <is>
           <t>OS 인식 메모리 (MiB)</t>
         </is>
       </c>
-      <c r="D24" s="58" t="inlineStr">
+      <c r="D24" s="57" t="inlineStr">
         <is>
           <t>free -m</t>
         </is>
       </c>
-      <c r="E24" s="61" t="n"/>
-      <c r="F24" s="60" t="inlineStr">
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="59" t="inlineStr">
         <is>
           <t>Mem total, 숫자만</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="56">
+      <c r="A25" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C25" s="57" t="inlineStr">
+      <c r="C25" s="56" t="inlineStr">
         <is>
           <t>물리 메모리</t>
         </is>
       </c>
-      <c r="D25" s="58" t="inlineStr">
+      <c r="D25" s="57" t="inlineStr">
         <is>
           <t>dmidecode -t memory | grep -i size | egrep -v 'No Module|Cache|Logical|Volatile'</t>
         </is>
       </c>
-      <c r="E25" s="61" t="n"/>
-      <c r="F25" s="60" t="inlineStr">
+      <c r="E25" s="58" t="n"/>
+      <c r="F25" s="59" t="inlineStr">
         <is>
           <t>물리 서버</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56">
+      <c r="A26" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t>CPU·메모리</t>
         </is>
       </c>
-      <c r="C26" s="57" t="inlineStr">
+      <c r="C26" s="56" t="inlineStr">
         <is>
           <t>GPU</t>
         </is>
       </c>
-      <c r="D26" s="58" t="inlineStr">
+      <c r="D26" s="57" t="inlineStr">
         <is>
           <t>nvidia-smi -L</t>
         </is>
       </c>
-      <c r="E26" s="61" t="n"/>
-      <c r="F26" s="60" t="inlineStr">
+      <c r="E26" s="58" t="n"/>
+      <c r="F26" s="59" t="inlineStr">
         <is>
           <t>GPU 서버</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="56">
+      <c r="A27" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="55" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C27" s="57" t="inlineStr">
+      <c r="C27" s="56" t="inlineStr">
         <is>
           <t>시간대</t>
         </is>
       </c>
-      <c r="D27" s="58" t="inlineStr">
+      <c r="D27" s="57" t="inlineStr">
         <is>
           <t>timedatectl | grep 'Time zone'</t>
         </is>
       </c>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="60" t="n"/>
+      <c r="E27" s="58" t="n"/>
+      <c r="F27" s="59" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="56">
+      <c r="A28" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C28" s="57" t="inlineStr">
+      <c r="C28" s="56" t="inlineStr">
         <is>
           <t>시간 동기화 여부</t>
         </is>
       </c>
-      <c r="D28" s="58" t="inlineStr">
+      <c r="D28" s="57" t="inlineStr">
         <is>
           <t>timedatectl | egrep 'synchronized|NTP'</t>
         </is>
       </c>
-      <c r="E28" s="59" t="n"/>
-      <c r="F28" s="60" t="n"/>
+      <c r="E28" s="58" t="n"/>
+      <c r="F28" s="59" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="56">
+      <c r="A29" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>시간</t>
         </is>
       </c>
-      <c r="C29" s="57" t="inlineStr">
+      <c r="C29" s="56" t="inlineStr">
         <is>
           <t>타임 서버 (chrony)</t>
         </is>
       </c>
-      <c r="D29" s="58" t="inlineStr">
+      <c r="D29" s="57" t="inlineStr">
         <is>
           <t>chronyc sources -v</t>
         </is>
       </c>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="60" t="inlineStr">
+      <c r="E29" s="58" t="n"/>
+      <c r="F29" s="59" t="inlineStr">
         <is>
           <t>* 표시가 동기 서버</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="56">
+      <c r="A30" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C30" s="57" t="inlineStr">
+      <c r="C30" s="56" t="inlineStr">
         <is>
           <t>IP 주소</t>
         </is>
       </c>
-      <c r="D30" s="58" t="inlineStr">
+      <c r="D30" s="57" t="inlineStr">
         <is>
           <t>ip -br addr</t>
         </is>
       </c>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="60" t="n"/>
+      <c r="E30" s="58" t="n"/>
+      <c r="F30" s="59" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="56">
+      <c r="A31" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C31" s="57" t="inlineStr">
+      <c r="C31" s="56" t="inlineStr">
         <is>
           <t>MAC 주소</t>
         </is>
       </c>
-      <c r="D31" s="58" t="inlineStr">
+      <c r="D31" s="57" t="inlineStr">
         <is>
           <t>ip -br link</t>
         </is>
       </c>
-      <c r="E31" s="61" t="n"/>
-      <c r="F31" s="60" t="n"/>
+      <c r="E31" s="58" t="n"/>
+      <c r="F31" s="59" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="56">
+      <c r="A32" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B32" s="56" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C32" s="57" t="inlineStr">
+      <c r="C32" s="56" t="inlineStr">
         <is>
           <t>MTU</t>
         </is>
       </c>
-      <c r="D32" s="58" t="inlineStr">
+      <c r="D32" s="57" t="inlineStr">
         <is>
           <t>ip link | grep mtu</t>
         </is>
       </c>
-      <c r="E32" s="61" t="n"/>
-      <c r="F32" s="60" t="n"/>
+      <c r="E32" s="58" t="n"/>
+      <c r="F32" s="59" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="56">
+      <c r="A33" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B33" s="56" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C33" s="57" t="inlineStr">
+      <c r="C33" s="56" t="inlineStr">
         <is>
           <t>본딩 상태</t>
         </is>
       </c>
-      <c r="D33" s="58" t="inlineStr">
+      <c r="D33" s="57" t="inlineStr">
         <is>
           <t>tail -v -n +1 /proc/net/bonding/*</t>
         </is>
       </c>
-      <c r="E33" s="61" t="n"/>
-      <c r="F33" s="60" t="inlineStr">
+      <c r="E33" s="58" t="n"/>
+      <c r="F33" s="59" t="inlineStr">
         <is>
           <t>본딩 사용 시</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="56">
+      <c r="A34" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B34" s="56" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C34" s="57" t="inlineStr">
+      <c r="C34" s="56" t="inlineStr">
         <is>
           <t>IPv4 경로</t>
         </is>
       </c>
-      <c r="D34" s="58" t="inlineStr">
+      <c r="D34" s="57" t="inlineStr">
         <is>
           <t>ip route</t>
         </is>
       </c>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="60" t="n"/>
+      <c r="E34" s="58" t="n"/>
+      <c r="F34" s="59" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="56">
+      <c r="A35" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C35" s="57" t="inlineStr">
+      <c r="C35" s="56" t="inlineStr">
         <is>
           <t>DNS 서버·도메인</t>
         </is>
       </c>
-      <c r="D35" s="58" t="inlineStr">
+      <c r="D35" s="57" t="inlineStr">
         <is>
           <t>cat /etc/resolv.conf</t>
         </is>
       </c>
-      <c r="E35" s="61" t="n"/>
-      <c r="F35" s="60" t="n"/>
+      <c r="E35" s="58" t="n"/>
+      <c r="F35" s="59" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="56">
+      <c r="A36" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B36" s="56" t="inlineStr">
+      <c r="B36" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C36" s="57" t="inlineStr">
+      <c r="C36" s="56" t="inlineStr">
         <is>
           <t>호스트 파일</t>
         </is>
       </c>
-      <c r="D36" s="58" t="inlineStr">
+      <c r="D36" s="57" t="inlineStr">
         <is>
           <t>cat /etc/hosts</t>
         </is>
       </c>
-      <c r="E36" s="61" t="n"/>
-      <c r="F36" s="60" t="n"/>
+      <c r="E36" s="58" t="n"/>
+      <c r="F36" s="59" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="56">
+      <c r="A37" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C37" s="57" t="inlineStr">
+      <c r="C37" s="56" t="inlineStr">
         <is>
           <t>네트워크 연결</t>
         </is>
       </c>
-      <c r="D37" s="58" t="inlineStr">
+      <c r="D37" s="57" t="inlineStr">
         <is>
           <t>nmcli connection show</t>
         </is>
       </c>
-      <c r="E37" s="61" t="n"/>
-      <c r="F37" s="60" t="n"/>
+      <c r="E37" s="58" t="n"/>
+      <c r="F37" s="59" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="56">
+      <c r="A38" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B38" s="56" t="inlineStr">
+      <c r="B38" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C38" s="57" t="inlineStr">
+      <c r="C38" s="56" t="inlineStr">
         <is>
           <t>저장된 네트워크 설정</t>
         </is>
       </c>
-      <c r="D38" s="58" t="inlineStr">
+      <c r="D38" s="57" t="inlineStr">
         <is>
           <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
-      <c r="E38" s="61" t="n"/>
-      <c r="F38" s="60" t="inlineStr">
+      <c r="E38" s="58" t="n"/>
+      <c r="F38" s="59" t="inlineStr">
         <is>
           <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="56">
+      <c r="A39" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>네트워크</t>
         </is>
       </c>
-      <c r="C39" s="57" t="inlineStr">
+      <c r="C39" s="56" t="inlineStr">
         <is>
           <t>링 버퍼 (RX/TX)</t>
         </is>
       </c>
-      <c r="D39" s="58" t="inlineStr">
+      <c r="D39" s="57" t="inlineStr">
         <is>
           <t>ethtool -g &lt;인터페이스&gt;</t>
         </is>
       </c>
-      <c r="E39" s="61" t="n"/>
-      <c r="F39" s="60" t="inlineStr">
+      <c r="E39" s="58" t="n"/>
+      <c r="F39" s="59" t="inlineStr">
         <is>
           <t>조정한 경우</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="56">
+      <c r="A40" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B40" s="56" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C40" s="57" t="inlineStr">
+      <c r="C40" s="56" t="inlineStr">
         <is>
           <t>장치와 파일시스템</t>
         </is>
       </c>
-      <c r="D40" s="58" t="inlineStr">
+      <c r="D40" s="57" t="inlineStr">
         <is>
           <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
         </is>
       </c>
-      <c r="E40" s="61" t="n"/>
-      <c r="F40" s="60" t="n"/>
+      <c r="E40" s="58" t="n"/>
+      <c r="F40" s="59" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="56">
+      <c r="A41" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B41" s="56" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C41" s="57" t="inlineStr">
+      <c r="C41" s="56" t="inlineStr">
         <is>
           <t>파일시스템 사용량</t>
         </is>
       </c>
-      <c r="D41" s="58" t="inlineStr">
+      <c r="D41" s="57" t="inlineStr">
         <is>
           <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
         </is>
       </c>
-      <c r="E41" s="61" t="n"/>
-      <c r="F41" s="60" t="n"/>
+      <c r="E41" s="58" t="n"/>
+      <c r="F41" s="59" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="56">
+      <c r="A42" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B42" s="56" t="inlineStr">
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C42" s="57" t="inlineStr">
+      <c r="C42" s="56" t="inlineStr">
         <is>
           <t>현재 마운트</t>
         </is>
       </c>
-      <c r="D42" s="58" t="inlineStr">
+      <c r="D42" s="57" t="inlineStr">
         <is>
           <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
         </is>
       </c>
-      <c r="E42" s="61" t="n"/>
-      <c r="F42" s="60" t="n"/>
+      <c r="E42" s="58" t="n"/>
+      <c r="F42" s="59" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="56">
+      <c r="A43" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B43" s="56" t="inlineStr">
+      <c r="B43" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C43" s="57" t="inlineStr">
+      <c r="C43" s="56" t="inlineStr">
         <is>
           <t>저장된 마운트</t>
         </is>
       </c>
-      <c r="D43" s="58" t="inlineStr">
+      <c r="D43" s="57" t="inlineStr">
         <is>
           <t>cat /etc/fstab</t>
         </is>
       </c>
-      <c r="E43" s="61" t="n"/>
-      <c r="F43" s="60" t="n"/>
+      <c r="E43" s="58" t="n"/>
+      <c r="F43" s="59" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="56">
+      <c r="A44" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B44" s="56" t="inlineStr">
+      <c r="B44" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C44" s="57" t="inlineStr">
+      <c r="C44" s="56" t="inlineStr">
         <is>
           <t>스왑</t>
         </is>
       </c>
-      <c r="D44" s="58" t="inlineStr">
+      <c r="D44" s="57" t="inlineStr">
         <is>
           <t>cat /proc/swaps</t>
         </is>
       </c>
-      <c r="E44" s="61" t="n"/>
-      <c r="F44" s="60" t="n"/>
+      <c r="E44" s="58" t="n"/>
+      <c r="F44" s="59" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="56">
+      <c r="A45" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B45" s="56" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C45" s="57" t="inlineStr">
+      <c r="C45" s="56" t="inlineStr">
         <is>
           <t>LVM-PV</t>
         </is>
       </c>
-      <c r="D45" s="58" t="inlineStr">
+      <c r="D45" s="57" t="inlineStr">
         <is>
           <t>pvs</t>
         </is>
       </c>
-      <c r="E45" s="61" t="n"/>
-      <c r="F45" s="60" t="inlineStr">
+      <c r="E45" s="58" t="n"/>
+      <c r="F45" s="59" t="inlineStr">
         <is>
           <t>LVM 사용 시</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="56">
+      <c r="A46" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B46" s="56" t="inlineStr">
+      <c r="B46" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C46" s="57" t="inlineStr">
+      <c r="C46" s="56" t="inlineStr">
         <is>
           <t>LVM-VG</t>
         </is>
       </c>
-      <c r="D46" s="58" t="inlineStr">
+      <c r="D46" s="57" t="inlineStr">
         <is>
           <t>vgs</t>
         </is>
       </c>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="60" t="n"/>
+      <c r="E46" s="58" t="n"/>
+      <c r="F46" s="59" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="56">
+      <c r="A47" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C47" s="57" t="inlineStr">
+      <c r="C47" s="56" t="inlineStr">
         <is>
           <t>LVM-LV</t>
         </is>
       </c>
-      <c r="D47" s="58" t="inlineStr">
+      <c r="D47" s="57" t="inlineStr">
         <is>
           <t>lvs -a -o +devices</t>
         </is>
       </c>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="60" t="n"/>
+      <c r="E47" s="58" t="n"/>
+      <c r="F47" s="59" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="56">
+      <c r="A48" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B48" s="56" t="inlineStr">
+      <c r="B48" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C48" s="57" t="inlineStr">
+      <c r="C48" s="56" t="inlineStr">
         <is>
           <t>SCSI 호스트</t>
         </is>
       </c>
-      <c r="D48" s="58" t="inlineStr">
+      <c r="D48" s="57" t="inlineStr">
         <is>
           <t>lsscsi -H</t>
         </is>
       </c>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="60" t="inlineStr">
+      <c r="E48" s="58" t="n"/>
+      <c r="F48" s="59" t="inlineStr">
         <is>
           <t>lsscsi 패키지</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="56">
+      <c r="A49" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B49" s="56" t="inlineStr">
+      <c r="B49" s="55" t="inlineStr">
         <is>
           <t>디스크</t>
         </is>
       </c>
-      <c r="C49" s="57" t="inlineStr">
+      <c r="C49" s="56" t="inlineStr">
         <is>
           <t>SCSI 장치</t>
         </is>
       </c>
-      <c r="D49" s="58" t="inlineStr">
+      <c r="D49" s="57" t="inlineStr">
         <is>
           <t>lsscsi -is</t>
         </is>
       </c>
-      <c r="E49" s="61" t="n"/>
-      <c r="F49" s="60" t="inlineStr">
+      <c r="E49" s="58" t="n"/>
+      <c r="F49" s="59" t="inlineStr">
         <is>
           <t>lsscsi 패키지</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="56">
+      <c r="A50" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B50" s="56" t="inlineStr">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C50" s="57" t="inlineStr">
+      <c r="C50" s="56" t="inlineStr">
         <is>
           <t>HBA 포트 (WWPN·상태·유형)</t>
         </is>
       </c>
-      <c r="D50" s="58" t="inlineStr">
+      <c r="D50" s="57" t="inlineStr">
         <is>
           <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
         </is>
       </c>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="60" t="inlineStr">
+      <c r="E50" s="58" t="n"/>
+      <c r="F50" s="59" t="inlineStr">
         <is>
           <t>SAN 사용 시</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="56">
+      <c r="A51" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B51" s="56" t="inlineStr">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C51" s="57" t="inlineStr">
+      <c r="C51" s="56" t="inlineStr">
         <is>
           <t>멀티패스 상태</t>
         </is>
       </c>
-      <c r="D51" s="58" t="inlineStr">
+      <c r="D51" s="57" t="inlineStr">
         <is>
           <t>multipath -ll</t>
         </is>
       </c>
-      <c r="E51" s="61" t="n"/>
-      <c r="F51" s="60" t="n"/>
+      <c r="E51" s="58" t="n"/>
+      <c r="F51" s="59" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="56">
+      <c r="A52" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B52" s="56" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C52" s="57" t="inlineStr">
+      <c r="C52" s="56" t="inlineStr">
         <is>
           <t>멀티패스 설정</t>
         </is>
       </c>
-      <c r="D52" s="58" t="inlineStr">
+      <c r="D52" s="57" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/multipath.conf</t>
         </is>
       </c>
-      <c r="E52" s="61" t="n"/>
-      <c r="F52" s="60" t="n"/>
+      <c r="E52" s="58" t="n"/>
+      <c r="F52" s="59" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="56">
+      <c r="A53" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B53" s="56" t="inlineStr">
+      <c r="B53" s="55" t="inlineStr">
         <is>
           <t>SAN</t>
         </is>
       </c>
-      <c r="C53" s="57" t="inlineStr">
+      <c r="C53" s="56" t="inlineStr">
         <is>
           <t>멀티패스 이름 매핑</t>
         </is>
       </c>
-      <c r="D53" s="58" t="inlineStr">
+      <c r="D53" s="57" t="inlineStr">
         <is>
           <t>cat /etc/multipath/bindings</t>
         </is>
       </c>
-      <c r="E53" s="61" t="n"/>
-      <c r="F53" s="60" t="n"/>
+      <c r="E53" s="58" t="n"/>
+      <c r="F53" s="59" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="56">
+      <c r="A54" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B54" s="56" t="inlineStr">
+      <c r="B54" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C54" s="57" t="inlineStr">
+      <c r="C54" s="56" t="inlineStr">
         <is>
           <t>로그인 가능 계정</t>
         </is>
       </c>
-      <c r="D54" s="58" t="inlineStr">
+      <c r="D54" s="57" t="inlineStr">
         <is>
           <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
         </is>
       </c>
-      <c r="E54" s="61" t="n"/>
-      <c r="F54" s="60" t="n"/>
+      <c r="E54" s="58" t="n"/>
+      <c r="F54" s="59" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="56">
+      <c r="A55" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B55" s="56" t="inlineStr">
+      <c r="B55" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C55" s="57" t="inlineStr">
+      <c r="C55" s="56" t="inlineStr">
         <is>
           <t>관리자 그룹</t>
         </is>
       </c>
-      <c r="D55" s="58" t="inlineStr">
+      <c r="D55" s="57" t="inlineStr">
         <is>
           <t>getent group wheel</t>
         </is>
       </c>
-      <c r="E55" s="59" t="n"/>
-      <c r="F55" s="60" t="n"/>
+      <c r="E55" s="58" t="n"/>
+      <c r="F55" s="59" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="56">
+      <c r="A56" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B56" s="56" t="inlineStr">
+      <c r="B56" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C56" s="57" t="inlineStr">
+      <c r="C56" s="56" t="inlineStr">
         <is>
           <t>SSH 설정</t>
         </is>
       </c>
-      <c r="D56" s="58" t="inlineStr">
+      <c r="D56" s="57" t="inlineStr">
         <is>
           <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
         </is>
       </c>
-      <c r="E56" s="59" t="n"/>
-      <c r="F56" s="60" t="inlineStr">
+      <c r="E56" s="58" t="n"/>
+      <c r="F56" s="59" t="inlineStr">
         <is>
           <t>allowusers 없으면 미설정</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="56">
+      <c r="A57" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B57" s="56" t="inlineStr">
+      <c r="B57" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C57" s="57" t="inlineStr">
+      <c r="C57" s="56" t="inlineStr">
         <is>
           <t>방화벽 실행</t>
         </is>
       </c>
-      <c r="D57" s="58" t="inlineStr">
+      <c r="D57" s="57" t="inlineStr">
         <is>
           <t>systemctl is-active firewalld</t>
         </is>
       </c>
-      <c r="E57" s="59" t="n"/>
-      <c r="F57" s="60" t="n"/>
+      <c r="E57" s="58" t="n"/>
+      <c r="F57" s="59" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="56">
+      <c r="A58" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B58" s="56" t="inlineStr">
+      <c r="B58" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C58" s="57" t="inlineStr">
+      <c r="C58" s="56" t="inlineStr">
         <is>
           <t>방화벽 부팅 시 시작</t>
         </is>
       </c>
-      <c r="D58" s="58" t="inlineStr">
+      <c r="D58" s="57" t="inlineStr">
         <is>
           <t>systemctl is-enabled firewalld</t>
         </is>
       </c>
-      <c r="E58" s="59" t="n"/>
-      <c r="F58" s="60" t="n"/>
+      <c r="E58" s="58" t="n"/>
+      <c r="F58" s="59" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="56">
+      <c r="A59" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B59" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C59" s="57" t="inlineStr">
+      <c r="C59" s="56" t="inlineStr">
         <is>
           <t>방화벽 응답</t>
         </is>
       </c>
-      <c r="D59" s="58" t="inlineStr">
+      <c r="D59" s="57" t="inlineStr">
         <is>
           <t>firewall-cmd --state</t>
         </is>
       </c>
-      <c r="E59" s="59" t="n"/>
-      <c r="F59" s="60" t="inlineStr">
+      <c r="E59" s="58" t="n"/>
+      <c r="F59" s="59" t="inlineStr">
         <is>
           <t>not running이면 미사용</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="56">
+      <c r="A60" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B60" s="56" t="inlineStr">
+      <c r="B60" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C60" s="57" t="inlineStr">
+      <c r="C60" s="56" t="inlineStr">
         <is>
           <t>방화벽 영역</t>
         </is>
       </c>
-      <c r="D60" s="58" t="inlineStr">
+      <c r="D60" s="57" t="inlineStr">
         <is>
           <t>firewall-cmd --get-active-zones</t>
         </is>
       </c>
-      <c r="E60" s="59" t="n"/>
-      <c r="F60" s="60" t="n"/>
+      <c r="E60" s="58" t="n"/>
+      <c r="F60" s="59" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="56">
+      <c r="A61" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B61" s="56" t="inlineStr">
+      <c r="B61" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C61" s="57" t="inlineStr">
+      <c r="C61" s="56" t="inlineStr">
         <is>
           <t>방화벽 규칙</t>
         </is>
       </c>
-      <c r="D61" s="58" t="inlineStr">
+      <c r="D61" s="57" t="inlineStr">
         <is>
           <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
-      <c r="E61" s="61" t="n"/>
-      <c r="F61" s="60" t="inlineStr">
+      <c r="E61" s="58" t="n"/>
+      <c r="F61" s="59" t="inlineStr">
         <is>
           <t>활성 영역마다</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="56">
+      <c r="A62" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B62" s="56" t="inlineStr">
+      <c r="B62" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C62" s="57" t="inlineStr">
+      <c r="C62" s="56" t="inlineStr">
         <is>
           <t>방화벽 저장 규칙</t>
         </is>
       </c>
-      <c r="D62" s="58" t="inlineStr">
+      <c r="D62" s="57" t="inlineStr">
         <is>
           <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
-      <c r="E62" s="61" t="n"/>
-      <c r="F62" s="60" t="inlineStr">
+      <c r="E62" s="58" t="n"/>
+      <c r="F62" s="59" t="inlineStr">
         <is>
           <t>규칙과 다르면 표시</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="56">
+      <c r="A63" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B63" s="56" t="inlineStr">
+      <c r="B63" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C63" s="57" t="inlineStr">
+      <c r="C63" s="56" t="inlineStr">
         <is>
           <t>보안 모듈 (SELinux)</t>
         </is>
       </c>
-      <c r="D63" s="58" t="inlineStr">
+      <c r="D63" s="57" t="inlineStr">
         <is>
           <t>getenforce</t>
         </is>
       </c>
-      <c r="E63" s="59" t="n"/>
-      <c r="F63" s="60" t="n"/>
+      <c r="E63" s="58" t="n"/>
+      <c r="F63" s="59" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="56">
+      <c r="A64" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B64" s="56" t="inlineStr">
+      <c r="B64" s="55" t="inlineStr">
         <is>
           <t>계정·접근</t>
         </is>
       </c>
-      <c r="C64" s="57" t="inlineStr">
+      <c r="C64" s="56" t="inlineStr">
         <is>
           <t>보안 모듈 부팅 설정</t>
         </is>
       </c>
-      <c r="D64" s="58" t="inlineStr">
+      <c r="D64" s="57" t="inlineStr">
         <is>
           <t>grep ^SELINUX= /etc/selinux/config</t>
         </is>
       </c>
-      <c r="E64" s="59" t="n"/>
-      <c r="F64" s="60" t="n"/>
+      <c r="E64" s="58" t="n"/>
+      <c r="F64" s="59" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="56">
+      <c r="A65" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B65" s="56" t="inlineStr">
+      <c r="B65" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C65" s="57" t="inlineStr">
+      <c r="C65" s="56" t="inlineStr">
         <is>
           <t>주요 패키지</t>
         </is>
       </c>
-      <c r="D65" s="58" t="inlineStr">
+      <c r="D65" s="57" t="inlineStr">
         <is>
           <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
         </is>
       </c>
-      <c r="E65" s="61" t="n"/>
-      <c r="F65" s="60" t="n"/>
+      <c r="E65" s="58" t="n"/>
+      <c r="F65" s="59" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="56">
+      <c r="A66" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B66" s="56" t="inlineStr">
+      <c r="B66" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C66" s="57" t="inlineStr">
+      <c r="C66" s="56" t="inlineStr">
         <is>
           <t>전체 패키지</t>
         </is>
       </c>
-      <c r="D66" s="58" t="inlineStr">
+      <c r="D66" s="57" t="inlineStr">
         <is>
           <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
         </is>
       </c>
-      <c r="E66" s="59" t="inlineStr">
+      <c r="E66" s="58" t="inlineStr">
         <is>
           <t>패키지 시트 참고</t>
         </is>
       </c>
-      <c r="F66" s="60" t="n"/>
+      <c r="F66" s="59" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="56">
+      <c r="A67" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B67" s="56" t="inlineStr">
+      <c r="B67" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C67" s="57" t="inlineStr">
+      <c r="C67" s="56" t="inlineStr">
         <is>
           <t>최근 패치일</t>
         </is>
       </c>
-      <c r="D67" s="58" t="inlineStr">
+      <c r="D67" s="57" t="inlineStr">
         <is>
           <t>dnf history</t>
         </is>
       </c>
-      <c r="E67" s="61" t="n"/>
-      <c r="F67" s="60" t="inlineStr">
+      <c r="E67" s="58" t="n"/>
+      <c r="F67" s="59" t="inlineStr">
         <is>
           <t>Action(s)에 U가 든 줄</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="56">
+      <c r="A68" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B68" s="56" t="inlineStr">
+      <c r="B68" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C68" s="57" t="inlineStr">
+      <c r="C68" s="56" t="inlineStr">
         <is>
           <t>자동 업데이트 설정</t>
         </is>
       </c>
-      <c r="D68" s="58" t="inlineStr">
+      <c r="D68" s="57" t="inlineStr">
         <is>
           <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
         </is>
       </c>
-      <c r="E68" s="61" t="n"/>
-      <c r="F68" s="60" t="inlineStr">
+      <c r="E68" s="58" t="n"/>
+      <c r="F68" s="59" t="inlineStr">
         <is>
           <t>파일 없으면 미설치</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="56">
+      <c r="A69" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B69" s="56" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C69" s="57" t="inlineStr">
+      <c r="C69" s="56" t="inlineStr">
         <is>
           <t>자동 업데이트 예약</t>
         </is>
       </c>
-      <c r="D69" s="58" t="inlineStr">
+      <c r="D69" s="57" t="inlineStr">
         <is>
           <t>systemctl list-unit-files 'dnf-automatic*'</t>
         </is>
       </c>
-      <c r="E69" s="61" t="n"/>
-      <c r="F69" s="60" t="inlineStr">
+      <c r="E69" s="58" t="n"/>
+      <c r="F69" s="59" t="inlineStr">
         <is>
           <t>enabled면 사용</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="56">
+      <c r="A70" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B70" s="56" t="inlineStr">
+      <c r="B70" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C70" s="57" t="inlineStr">
+      <c r="C70" s="56" t="inlineStr">
         <is>
           <t>저장소 목록</t>
         </is>
       </c>
-      <c r="D70" s="58" t="inlineStr">
+      <c r="D70" s="57" t="inlineStr">
         <is>
           <t>dnf repolist</t>
         </is>
       </c>
-      <c r="E70" s="61" t="n"/>
-      <c r="F70" s="60" t="n"/>
+      <c r="E70" s="58" t="n"/>
+      <c r="F70" s="59" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="56">
+      <c r="A71" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B71" s="56" t="inlineStr">
+      <c r="B71" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C71" s="57" t="inlineStr">
+      <c r="C71" s="56" t="inlineStr">
         <is>
           <t>저장소 파일</t>
         </is>
       </c>
-      <c r="D71" s="58" t="inlineStr">
+      <c r="D71" s="57" t="inlineStr">
         <is>
           <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
-      <c r="E71" s="61" t="n"/>
-      <c r="F71" s="60" t="n"/>
+      <c r="E71" s="58" t="n"/>
+      <c r="F71" s="59" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="56">
+      <c r="A72" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B72" s="56" t="inlineStr">
+      <c r="B72" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C72" s="57" t="inlineStr">
+      <c r="C72" s="56" t="inlineStr">
         <is>
           <t>구독 등록 여부</t>
         </is>
       </c>
-      <c r="D72" s="58" t="inlineStr">
+      <c r="D72" s="57" t="inlineStr">
         <is>
           <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
-      <c r="E72" s="59" t="n"/>
-      <c r="F72" s="60" t="inlineStr">
+      <c r="E72" s="58" t="n"/>
+      <c r="F72" s="59" t="inlineStr">
         <is>
           <t>파일 없으면 미등록</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="56">
+      <c r="A73" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B73" s="56" t="inlineStr">
+      <c r="B73" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C73" s="57" t="inlineStr">
+      <c r="C73" s="56" t="inlineStr">
         <is>
           <t>구독 (RHSM)</t>
         </is>
       </c>
-      <c r="D73" s="58" t="inlineStr">
-        <is>
-          <t>subscription-manager status | grep :</t>
-        </is>
-      </c>
-      <c r="E73" s="61" t="n"/>
-      <c r="F73" s="60" t="inlineStr">
+      <c r="D73" s="57" t="inlineStr">
+        <is>
+          <t>subscription-manager status</t>
+        </is>
+      </c>
+      <c r="E73" s="58" t="n"/>
+      <c r="F73" s="59" t="inlineStr">
         <is>
           <t>RHEL</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="56">
+      <c r="A74" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B74" s="56" t="inlineStr">
+      <c r="B74" s="55" t="inlineStr">
         <is>
           <t>업데이트·패키지</t>
         </is>
       </c>
-      <c r="C74" s="57" t="inlineStr">
+      <c r="C74" s="56" t="inlineStr">
         <is>
           <t>릴리스 고정</t>
         </is>
       </c>
-      <c r="D74" s="58" t="inlineStr">
+      <c r="D74" s="57" t="inlineStr">
         <is>
           <t>subscription-manager release --show</t>
         </is>
       </c>
-      <c r="E74" s="59" t="n"/>
-      <c r="F74" s="60" t="inlineStr">
+      <c r="E74" s="58" t="n"/>
+      <c r="F74" s="59" t="inlineStr">
         <is>
           <t>Release not set이면 미고정</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="56">
+      <c r="A75" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B75" s="56" t="inlineStr">
+      <c r="B75" s="55" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C75" s="57" t="inlineStr">
+      <c r="C75" s="56" t="inlineStr">
         <is>
           <t>sysctl</t>
         </is>
       </c>
-      <c r="D75" s="58" t="inlineStr">
+      <c r="D75" s="57" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
         </is>
       </c>
-      <c r="E75" s="61" t="n"/>
-      <c r="F75" s="60" t="inlineStr">
+      <c r="E75" s="58" t="n"/>
+      <c r="F75" s="59" t="inlineStr">
         <is>
           <t>99-sysctl.conf 줄은 중복</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="56">
+      <c r="A76" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B76" s="56" t="inlineStr">
+      <c r="B76" s="55" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C76" s="57" t="inlineStr">
+      <c r="C76" s="56" t="inlineStr">
         <is>
           <t>자원 제한 (limits)</t>
         </is>
       </c>
-      <c r="D76" s="58" t="inlineStr">
+      <c r="D76" s="57" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
-      <c r="E76" s="61" t="n"/>
-      <c r="F76" s="60" t="n"/>
+      <c r="E76" s="58" t="n"/>
+      <c r="F76" s="59" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="56">
+      <c r="A77" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B77" s="56" t="inlineStr">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C77" s="57" t="inlineStr">
+      <c r="C77" s="56" t="inlineStr">
         <is>
           <t>kdump 설정</t>
         </is>
       </c>
-      <c r="D77" s="58" t="inlineStr">
+      <c r="D77" s="57" t="inlineStr">
         <is>
           <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
-      <c r="E77" s="61" t="n"/>
-      <c r="F77" s="60" t="n"/>
+      <c r="E77" s="58" t="n"/>
+      <c r="F77" s="59" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="56">
+      <c r="A78" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B78" s="56" t="inlineStr">
+      <c r="B78" s="55" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C78" s="57" t="inlineStr">
+      <c r="C78" s="56" t="inlineStr">
         <is>
           <t>kdump 실행</t>
         </is>
       </c>
-      <c r="D78" s="58" t="inlineStr">
+      <c r="D78" s="57" t="inlineStr">
         <is>
           <t>systemctl is-active kdump</t>
         </is>
       </c>
-      <c r="E78" s="59" t="n"/>
-      <c r="F78" s="60" t="n"/>
+      <c r="E78" s="58" t="n"/>
+      <c r="F78" s="59" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="56">
+      <c r="A79" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B79" s="56" t="inlineStr">
+      <c r="B79" s="55" t="inlineStr">
         <is>
           <t>커널 설정</t>
         </is>
       </c>
-      <c r="C79" s="57" t="inlineStr">
+      <c r="C79" s="56" t="inlineStr">
         <is>
           <t>kdump 부팅 시 시작</t>
         </is>
       </c>
-      <c r="D79" s="58" t="inlineStr">
+      <c r="D79" s="57" t="inlineStr">
         <is>
           <t>systemctl is-enabled kdump</t>
         </is>
       </c>
-      <c r="E79" s="59" t="n"/>
-      <c r="F79" s="60" t="n"/>
+      <c r="E79" s="58" t="n"/>
+      <c r="F79" s="59" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="56">
+      <c r="A80" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B80" s="56" t="inlineStr">
+      <c r="B80" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C80" s="57" t="inlineStr">
+      <c r="C80" s="56" t="inlineStr">
         <is>
           <t>실행 중인 서비스</t>
         </is>
       </c>
-      <c r="D80" s="58" t="inlineStr">
+      <c r="D80" s="57" t="inlineStr">
         <is>
           <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
-      <c r="E80" s="61" t="n"/>
-      <c r="F80" s="60" t="n"/>
+      <c r="E80" s="58" t="n"/>
+      <c r="F80" s="59" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="56">
+      <c r="A81" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B81" s="56" t="inlineStr">
+      <c r="B81" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C81" s="57" t="inlineStr">
+      <c r="C81" s="56" t="inlineStr">
         <is>
           <t>자동 시작 서비스</t>
         </is>
       </c>
-      <c r="D81" s="58" t="inlineStr">
+      <c r="D81" s="57" t="inlineStr">
         <is>
           <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
-      <c r="E81" s="61" t="n"/>
-      <c r="F81" s="60" t="n"/>
+      <c r="E81" s="58" t="n"/>
+      <c r="F81" s="59" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="56">
+      <c r="A82" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B82" s="56" t="inlineStr">
+      <c r="B82" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C82" s="57" t="inlineStr">
+      <c r="C82" s="56" t="inlineStr">
         <is>
           <t>열린 포트</t>
         </is>
       </c>
-      <c r="D82" s="58" t="inlineStr">
+      <c r="D82" s="57" t="inlineStr">
         <is>
           <t>ss -tulnp</t>
         </is>
       </c>
-      <c r="E82" s="61" t="n"/>
-      <c r="F82" s="60" t="n"/>
+      <c r="E82" s="58" t="n"/>
+      <c r="F82" s="59" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="56">
+      <c r="A83" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B83" s="56" t="inlineStr">
+      <c r="B83" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C83" s="57" t="inlineStr">
+      <c r="C83" s="56" t="inlineStr">
         <is>
           <t>예약 작업 (타이머)</t>
         </is>
       </c>
-      <c r="D83" s="58" t="inlineStr">
+      <c r="D83" s="57" t="inlineStr">
         <is>
           <t>systemctl list-timers --all --no-pager</t>
         </is>
       </c>
-      <c r="E83" s="61" t="n"/>
-      <c r="F83" s="60" t="n"/>
+      <c r="E83" s="58" t="n"/>
+      <c r="F83" s="59" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="56">
+      <c r="A84" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B84" s="56" t="inlineStr">
+      <c r="B84" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C84" s="57" t="inlineStr">
+      <c r="C84" s="56" t="inlineStr">
         <is>
           <t>예약 작업 (crontab)</t>
         </is>
       </c>
-      <c r="D84" s="58" t="inlineStr">
+      <c r="D84" s="57" t="inlineStr">
         <is>
           <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
-      <c r="E84" s="61" t="n"/>
-      <c r="F84" s="60" t="inlineStr">
+      <c r="E84" s="58" t="n"/>
+      <c r="F84" s="59" t="inlineStr">
         <is>
           <t>파일명이 계정명</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="56">
+      <c r="A85" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B85" s="56" t="inlineStr">
+      <c r="B85" s="55" t="inlineStr">
         <is>
           <t>서비스·예약</t>
         </is>
       </c>
-      <c r="C85" s="57" t="inlineStr">
+      <c r="C85" s="56" t="inlineStr">
         <is>
           <t>예약 작업 (cron.d)</t>
         </is>
       </c>
-      <c r="D85" s="58" t="inlineStr">
+      <c r="D85" s="57" t="inlineStr">
         <is>
           <t>ls /etc/cron.d</t>
         </is>
       </c>
-      <c r="E85" s="61" t="n"/>
-      <c r="F85" s="60" t="n"/>
+      <c r="E85" s="58" t="n"/>
+      <c r="F85" s="59" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="56">
+      <c r="A86" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B86" s="56" t="inlineStr">
+      <c r="B86" s="55" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C86" s="57" t="inlineStr">
+      <c r="C86" s="56" t="inlineStr">
         <is>
           <t>모니터링 에이전트</t>
         </is>
       </c>
-      <c r="D86" s="58" t="inlineStr">
+      <c r="D86" s="57" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E86" s="61" t="n"/>
-      <c r="F86" s="60" t="inlineStr">
+      <c r="E86" s="58" t="n"/>
+      <c r="F86" s="59" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="56">
+      <c r="A87" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B87" s="56" t="inlineStr">
+      <c r="B87" s="55" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C87" s="57" t="inlineStr">
+      <c r="C87" s="56" t="inlineStr">
         <is>
           <t>보안 에이전트</t>
         </is>
       </c>
-      <c r="D87" s="58" t="inlineStr">
+      <c r="D87" s="57" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E87" s="61" t="n"/>
-      <c r="F87" s="60" t="inlineStr">
+      <c r="E87" s="58" t="n"/>
+      <c r="F87" s="59" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="56">
+      <c r="A88" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B88" s="56" t="inlineStr">
+      <c r="B88" s="55" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C88" s="57" t="inlineStr">
+      <c r="C88" s="56" t="inlineStr">
         <is>
           <t>백신</t>
         </is>
       </c>
-      <c r="D88" s="58" t="inlineStr">
+      <c r="D88" s="57" t="inlineStr">
         <is>
           <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
-      <c r="E88" s="61" t="n"/>
-      <c r="F88" s="60" t="inlineStr">
+      <c r="E88" s="58" t="n"/>
+      <c r="F88" s="59" t="inlineStr">
         <is>
           <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="56">
+      <c r="A89" s="55">
         <f>ROW()-5</f>
         <v/>
       </c>
-      <c r="B89" s="56" t="inlineStr">
+      <c r="B89" s="55" t="inlineStr">
         <is>
           <t>에이전트·백업</t>
         </is>
       </c>
-      <c r="C89" s="57" t="inlineStr">
+      <c r="C89" s="56" t="inlineStr">
         <is>
           <t>설정 백업</t>
         </is>
       </c>
-      <c r="D89" s="58" t="inlineStr">
+      <c r="D89" s="57" t="inlineStr">
         <is>
           <t>백업 위치, 마지막 백업 날짜</t>
         </is>
       </c>
-      <c r="E89" s="59" t="n"/>
-      <c r="F89" s="60" t="inlineStr">
+      <c r="E89" s="58" t="n"/>
+      <c r="F89" s="59" t="inlineStr">
         <is>
           <t>직접 입력</t>
         </is>
@@ -3370,7 +3361,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3380,55 +3371,55 @@
           <t>원문</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="65" t="inlineStr">
+      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="E3" s="65" t="inlineStr">
+      <c r="E3" s="62" t="inlineStr">
         <is>
           <t>릴리스</t>
         </is>
       </c>
-      <c r="F3" s="65" t="inlineStr">
+      <c r="F3" s="62" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="G3" s="65" t="inlineStr">
+      <c r="G3" s="62" t="inlineStr">
         <is>
           <t>설치 일시</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66">
+      <c r="A4" s="63">
         <f>IF(Packages[[#This Row],[원문]]="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B4" s="67" t="n"/>
-      <c r="C4" s="66">
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="63">
         <f>IF(Packages[[#This Row],[원문]]="","",IFERROR(LEFT(Packages[[#This Row],[원문]],FIND(" ",Packages[[#This Row],[원문]])-1),""))</f>
         <v/>
       </c>
-      <c r="D4" s="66">
+      <c r="D4" s="63">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))-1),""))</f>
         <v/>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="63">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-1),""))</f>
         <v/>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="63">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-1),""))</f>
         <v/>
       </c>
-      <c r="G4" s="68">
+      <c r="G4" s="65">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(VALUE(TRIM(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))+1,20)))/86400+25569+9/24,""))</f>
         <v/>
       </c>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D25" s="57" t="inlineStr">
         <is>
-          <t>dmidecode -t memory | grep -i size | egrep -v 'No Module|Cache|Logical|Volatile'</t>
+          <t>dmidecode -t memory | grep '^.Size: [0-9]' | cut -f2</t>
         </is>
       </c>
       <c r="E25" s="58" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D14" s="57" t="inlineStr">
         <is>
-          <t>who -b</t>
+          <t>uptime -s</t>
         </is>
       </c>
       <c r="E14" s="58" t="n"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D25" s="57" t="inlineStr">
         <is>
-          <t>dmidecode -t memory | grep '^.Size: [0-9]' | cut -f2</t>
+          <t>dmidecode -t memory | grep '^.Size: [0-9]' | cut -d' ' -f2-</t>
         </is>
       </c>
       <c r="E25" s="58" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D18" s="57" t="inlineStr">
         <is>
-          <t>cat /proc/cpuinfo | grep -i 'model name' | uniq</t>
+          <t>grep -i 'model name' /proc/cpuinfo | uniq</t>
         </is>
       </c>
       <c r="E18" s="58" t="n"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="D19" s="57" t="inlineStr">
         <is>
-          <t>cat /proc/cpuinfo | grep 'physical id' | sort -u | wc -l</t>
+          <t>grep -i 'physical id' /proc/cpuinfo | sort -u | wc -l</t>
         </is>
       </c>
       <c r="E19" s="58" t="n"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D20" s="57" t="inlineStr">
         <is>
-          <t>cat /proc/cpuinfo | grep -i 'cpu cores' | uniq</t>
+          <t>grep -i 'cpu cores' /proc/cpuinfo | uniq</t>
         </is>
       </c>
       <c r="E20" s="58" t="n"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D22" s="57" t="inlineStr">
         <is>
-          <t>cat /proc/cpuinfo | grep -i '^processor' | wc -l</t>
+          <t>grep -i '^processor' /proc/cpuinfo | wc -l</t>
         </is>
       </c>
       <c r="E22" s="58" t="n"/>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -352,6 +352,9 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1567,7 +1570,7 @@
           <t>grep -i 'physical id' /proc/cpuinfo | sort -u | wc -l</t>
         </is>
       </c>
-      <c r="E19" s="58" t="n"/>
+      <c r="E19" s="60" t="n"/>
       <c r="F19" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
@@ -1594,7 +1597,7 @@
           <t>grep -i 'cpu cores' /proc/cpuinfo | uniq</t>
         </is>
       </c>
-      <c r="E20" s="58" t="n"/>
+      <c r="E20" s="60" t="n"/>
       <c r="F20" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
@@ -1616,12 +1619,12 @@
           <t>물리 코어 수</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr">
         <is>
           <t>CPU 소켓 수 × 소켓당 코어 수</t>
         </is>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="62">
         <f>IF(OR(E19="",E20=""),"",IFERROR(VALUE(E19)*VALUE(E20),""))</f>
         <v/>
       </c>
@@ -1651,7 +1654,7 @@
           <t>grep -i '^processor' /proc/cpuinfo | wc -l</t>
         </is>
       </c>
-      <c r="E22" s="58" t="n"/>
+      <c r="E22" s="60" t="n"/>
       <c r="F22" s="59" t="inlineStr">
         <is>
           <t>숫자만</t>
@@ -1673,12 +1676,12 @@
           <t>하이퍼스레딩</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr">
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>논리 CPU 수 = 물리 코어 수 × 2</t>
         </is>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="62">
         <f>IF(OR(E21="",E22=""),"",IFERROR(IF(VALUE(E22)=E21*2,"사용","미사용"),""))</f>
         <v/>
       </c>
@@ -3361,7 +3364,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3371,55 +3374,55 @@
           <t>원문</t>
         </is>
       </c>
-      <c r="C3" s="62" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="62" t="inlineStr">
+      <c r="D3" s="63" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="E3" s="62" t="inlineStr">
+      <c r="E3" s="63" t="inlineStr">
         <is>
           <t>릴리스</t>
         </is>
       </c>
-      <c r="F3" s="62" t="inlineStr">
+      <c r="F3" s="63" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="G3" s="62" t="inlineStr">
+      <c r="G3" s="63" t="inlineStr">
         <is>
           <t>설치 일시</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63">
+      <c r="A4" s="64">
         <f>IF(Packages[[#This Row],[원문]]="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B4" s="64" t="n"/>
-      <c r="C4" s="63">
+      <c r="B4" s="65" t="n"/>
+      <c r="C4" s="64">
         <f>IF(Packages[[#This Row],[원문]]="","",IFERROR(LEFT(Packages[[#This Row],[원문]],FIND(" ",Packages[[#This Row],[원문]])-1),""))</f>
         <v/>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="64">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",1))-1),""))</f>
         <v/>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="64">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",2))-1),""))</f>
         <v/>
       </c>
-      <c r="F4" s="63">
+      <c r="F4" s="64">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))+1,FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))-FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",3))-1),""))</f>
         <v/>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="66">
         <f>IF(Packages[[#This Row],[이름]]="","",IFERROR(VALUE(TRIM(MID(Packages[[#This Row],[원문]],FIND("|",SUBSTITUTE(Packages[[#This Row],[원문]]," ","|",4))+1,20)))/86400+25569+9/24,""))</f>
         <v/>
       </c>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -1752,25 +1752,21 @@
       </c>
       <c r="B26" s="55" t="inlineStr">
         <is>
-          <t>CPU·메모리</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="C26" s="56" t="inlineStr">
         <is>
-          <t>GPU</t>
+          <t>시간대</t>
         </is>
       </c>
       <c r="D26" s="57" t="inlineStr">
         <is>
-          <t>nvidia-smi -L</t>
+          <t>timedatectl | grep 'Time zone'</t>
         </is>
       </c>
       <c r="E26" s="58" t="n"/>
-      <c r="F26" s="59" t="inlineStr">
-        <is>
-          <t>GPU 서버</t>
-        </is>
-      </c>
+      <c r="F26" s="59" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="55">
@@ -1784,12 +1780,12 @@
       </c>
       <c r="C27" s="56" t="inlineStr">
         <is>
-          <t>시간대</t>
+          <t>시간 동기화 여부</t>
         </is>
       </c>
       <c r="D27" s="57" t="inlineStr">
         <is>
-          <t>timedatectl | grep 'Time zone'</t>
+          <t>timedatectl | egrep 'synchronized|NTP'</t>
         </is>
       </c>
       <c r="E27" s="58" t="n"/>
@@ -1807,16 +1803,20 @@
       </c>
       <c r="C28" s="56" t="inlineStr">
         <is>
-          <t>시간 동기화 여부</t>
+          <t>타임 서버 (chrony)</t>
         </is>
       </c>
       <c r="D28" s="57" t="inlineStr">
         <is>
-          <t>timedatectl | egrep 'synchronized|NTP'</t>
+          <t>chronyc sources -v</t>
         </is>
       </c>
       <c r="E28" s="58" t="n"/>
-      <c r="F28" s="59" t="n"/>
+      <c r="F28" s="59" t="inlineStr">
+        <is>
+          <t>* 표시가 동기 서버</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="55">
@@ -1825,25 +1825,21 @@
       </c>
       <c r="B29" s="55" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="C29" s="56" t="inlineStr">
         <is>
-          <t>타임 서버 (chrony)</t>
+          <t>IP 주소</t>
         </is>
       </c>
       <c r="D29" s="57" t="inlineStr">
         <is>
-          <t>chronyc sources -v</t>
+          <t>ip -br addr</t>
         </is>
       </c>
       <c r="E29" s="58" t="n"/>
-      <c r="F29" s="59" t="inlineStr">
-        <is>
-          <t>* 표시가 동기 서버</t>
-        </is>
-      </c>
+      <c r="F29" s="59" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="55">
@@ -1857,12 +1853,12 @@
       </c>
       <c r="C30" s="56" t="inlineStr">
         <is>
-          <t>IP 주소</t>
+          <t>MAC 주소</t>
         </is>
       </c>
       <c r="D30" s="57" t="inlineStr">
         <is>
-          <t>ip -br addr</t>
+          <t>ip -br link</t>
         </is>
       </c>
       <c r="E30" s="58" t="n"/>
@@ -1880,12 +1876,12 @@
       </c>
       <c r="C31" s="56" t="inlineStr">
         <is>
-          <t>MAC 주소</t>
+          <t>MTU</t>
         </is>
       </c>
       <c r="D31" s="57" t="inlineStr">
         <is>
-          <t>ip -br link</t>
+          <t>ip link | grep mtu</t>
         </is>
       </c>
       <c r="E31" s="58" t="n"/>
@@ -1903,16 +1899,20 @@
       </c>
       <c r="C32" s="56" t="inlineStr">
         <is>
-          <t>MTU</t>
+          <t>본딩 상태</t>
         </is>
       </c>
       <c r="D32" s="57" t="inlineStr">
         <is>
-          <t>ip link | grep mtu</t>
+          <t>tail -v -n +1 /proc/net/bonding/*</t>
         </is>
       </c>
       <c r="E32" s="58" t="n"/>
-      <c r="F32" s="59" t="n"/>
+      <c r="F32" s="59" t="inlineStr">
+        <is>
+          <t>본딩 사용 시</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="55">
@@ -1926,20 +1926,16 @@
       </c>
       <c r="C33" s="56" t="inlineStr">
         <is>
-          <t>본딩 상태</t>
+          <t>IPv4 경로</t>
         </is>
       </c>
       <c r="D33" s="57" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /proc/net/bonding/*</t>
+          <t>ip route</t>
         </is>
       </c>
       <c r="E33" s="58" t="n"/>
-      <c r="F33" s="59" t="inlineStr">
-        <is>
-          <t>본딩 사용 시</t>
-        </is>
-      </c>
+      <c r="F33" s="59" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="55">
@@ -1953,12 +1949,12 @@
       </c>
       <c r="C34" s="56" t="inlineStr">
         <is>
-          <t>IPv4 경로</t>
+          <t>DNS 서버·도메인</t>
         </is>
       </c>
       <c r="D34" s="57" t="inlineStr">
         <is>
-          <t>ip route</t>
+          <t>cat /etc/resolv.conf</t>
         </is>
       </c>
       <c r="E34" s="58" t="n"/>
@@ -1976,12 +1972,12 @@
       </c>
       <c r="C35" s="56" t="inlineStr">
         <is>
-          <t>DNS 서버·도메인</t>
+          <t>호스트 파일</t>
         </is>
       </c>
       <c r="D35" s="57" t="inlineStr">
         <is>
-          <t>cat /etc/resolv.conf</t>
+          <t>cat /etc/hosts</t>
         </is>
       </c>
       <c r="E35" s="58" t="n"/>
@@ -1999,12 +1995,12 @@
       </c>
       <c r="C36" s="56" t="inlineStr">
         <is>
-          <t>호스트 파일</t>
+          <t>네트워크 연결</t>
         </is>
       </c>
       <c r="D36" s="57" t="inlineStr">
         <is>
-          <t>cat /etc/hosts</t>
+          <t>nmcli connection show</t>
         </is>
       </c>
       <c r="E36" s="58" t="n"/>
@@ -2022,16 +2018,20 @@
       </c>
       <c r="C37" s="56" t="inlineStr">
         <is>
-          <t>네트워크 연결</t>
+          <t>저장된 네트워크 설정</t>
         </is>
       </c>
       <c r="D37" s="57" t="inlineStr">
         <is>
-          <t>nmcli connection show</t>
+          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
       <c r="E37" s="58" t="n"/>
-      <c r="F37" s="59" t="n"/>
+      <c r="F37" s="59" t="inlineStr">
+        <is>
+          <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="55">
@@ -2045,18 +2045,18 @@
       </c>
       <c r="C38" s="56" t="inlineStr">
         <is>
-          <t>저장된 네트워크 설정</t>
+          <t>링 버퍼 (RX/TX)</t>
         </is>
       </c>
       <c r="D38" s="57" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
+          <t>ethtool -g &lt;인터페이스&gt;</t>
         </is>
       </c>
       <c r="E38" s="58" t="n"/>
       <c r="F38" s="59" t="inlineStr">
         <is>
-          <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
+          <t>조정한 경우</t>
         </is>
       </c>
     </row>
@@ -2067,25 +2067,21 @@
       </c>
       <c r="B39" s="55" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>디스크</t>
         </is>
       </c>
       <c r="C39" s="56" t="inlineStr">
         <is>
-          <t>링 버퍼 (RX/TX)</t>
+          <t>장치와 파일시스템</t>
         </is>
       </c>
       <c r="D39" s="57" t="inlineStr">
         <is>
-          <t>ethtool -g &lt;인터페이스&gt;</t>
+          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
         </is>
       </c>
       <c r="E39" s="58" t="n"/>
-      <c r="F39" s="59" t="inlineStr">
-        <is>
-          <t>조정한 경우</t>
-        </is>
-      </c>
+      <c r="F39" s="59" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="55">
@@ -2099,12 +2095,12 @@
       </c>
       <c r="C40" s="56" t="inlineStr">
         <is>
-          <t>장치와 파일시스템</t>
+          <t>파일시스템 사용량</t>
         </is>
       </c>
       <c r="D40" s="57" t="inlineStr">
         <is>
-          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
+          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
         </is>
       </c>
       <c r="E40" s="58" t="n"/>
@@ -2122,12 +2118,12 @@
       </c>
       <c r="C41" s="56" t="inlineStr">
         <is>
-          <t>파일시스템 사용량</t>
+          <t>현재 마운트</t>
         </is>
       </c>
       <c r="D41" s="57" t="inlineStr">
         <is>
-          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
+          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
         </is>
       </c>
       <c r="E41" s="58" t="n"/>
@@ -2145,12 +2141,12 @@
       </c>
       <c r="C42" s="56" t="inlineStr">
         <is>
-          <t>현재 마운트</t>
+          <t>저장된 마운트</t>
         </is>
       </c>
       <c r="D42" s="57" t="inlineStr">
         <is>
-          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
+          <t>cat /etc/fstab</t>
         </is>
       </c>
       <c r="E42" s="58" t="n"/>
@@ -2168,12 +2164,12 @@
       </c>
       <c r="C43" s="56" t="inlineStr">
         <is>
-          <t>저장된 마운트</t>
+          <t>스왑</t>
         </is>
       </c>
       <c r="D43" s="57" t="inlineStr">
         <is>
-          <t>cat /etc/fstab</t>
+          <t>cat /proc/swaps</t>
         </is>
       </c>
       <c r="E43" s="58" t="n"/>
@@ -2191,16 +2187,20 @@
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>스왑</t>
+          <t>LVM-PV</t>
         </is>
       </c>
       <c r="D44" s="57" t="inlineStr">
         <is>
-          <t>cat /proc/swaps</t>
+          <t>pvs</t>
         </is>
       </c>
       <c r="E44" s="58" t="n"/>
-      <c r="F44" s="59" t="n"/>
+      <c r="F44" s="59" t="inlineStr">
+        <is>
+          <t>LVM 사용 시</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="55">
@@ -2214,20 +2214,16 @@
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>LVM-PV</t>
+          <t>LVM-VG</t>
         </is>
       </c>
       <c r="D45" s="57" t="inlineStr">
         <is>
-          <t>pvs</t>
+          <t>vgs</t>
         </is>
       </c>
       <c r="E45" s="58" t="n"/>
-      <c r="F45" s="59" t="inlineStr">
-        <is>
-          <t>LVM 사용 시</t>
-        </is>
-      </c>
+      <c r="F45" s="59" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="55">
@@ -2241,12 +2237,12 @@
       </c>
       <c r="C46" s="56" t="inlineStr">
         <is>
-          <t>LVM-VG</t>
+          <t>LVM-LV</t>
         </is>
       </c>
       <c r="D46" s="57" t="inlineStr">
         <is>
-          <t>vgs</t>
+          <t>lvs -a -o +devices</t>
         </is>
       </c>
       <c r="E46" s="58" t="n"/>
@@ -2264,16 +2260,20 @@
       </c>
       <c r="C47" s="56" t="inlineStr">
         <is>
-          <t>LVM-LV</t>
+          <t>SCSI 호스트</t>
         </is>
       </c>
       <c r="D47" s="57" t="inlineStr">
         <is>
-          <t>lvs -a -o +devices</t>
+          <t>lsscsi -H</t>
         </is>
       </c>
       <c r="E47" s="58" t="n"/>
-      <c r="F47" s="59" t="n"/>
+      <c r="F47" s="59" t="inlineStr">
+        <is>
+          <t>lsscsi 패키지</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="55">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="C48" s="56" t="inlineStr">
         <is>
-          <t>SCSI 호스트</t>
+          <t>SCSI 장치</t>
         </is>
       </c>
       <c r="D48" s="57" t="inlineStr">
         <is>
-          <t>lsscsi -H</t>
+          <t>lsscsi -is</t>
         </is>
       </c>
       <c r="E48" s="58" t="n"/>
@@ -2309,23 +2309,23 @@
       </c>
       <c r="B49" s="55" t="inlineStr">
         <is>
-          <t>디스크</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C49" s="56" t="inlineStr">
         <is>
-          <t>SCSI 장치</t>
+          <t>HBA 포트 (WWPN·상태·유형)</t>
         </is>
       </c>
       <c r="D49" s="57" t="inlineStr">
         <is>
-          <t>lsscsi -is</t>
+          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
         </is>
       </c>
       <c r="E49" s="58" t="n"/>
       <c r="F49" s="59" t="inlineStr">
         <is>
-          <t>lsscsi 패키지</t>
+          <t>SAN 사용 시</t>
         </is>
       </c>
     </row>
@@ -2341,20 +2341,16 @@
       </c>
       <c r="C50" s="56" t="inlineStr">
         <is>
-          <t>HBA 포트 (WWPN·상태·유형)</t>
+          <t>멀티패스 상태</t>
         </is>
       </c>
       <c r="D50" s="57" t="inlineStr">
         <is>
-          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
+          <t>multipath -ll</t>
         </is>
       </c>
       <c r="E50" s="58" t="n"/>
-      <c r="F50" s="59" t="inlineStr">
-        <is>
-          <t>SAN 사용 시</t>
-        </is>
-      </c>
+      <c r="F50" s="59" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="55">
@@ -2368,12 +2364,12 @@
       </c>
       <c r="C51" s="56" t="inlineStr">
         <is>
-          <t>멀티패스 상태</t>
+          <t>멀티패스 설정</t>
         </is>
       </c>
       <c r="D51" s="57" t="inlineStr">
         <is>
-          <t>multipath -ll</t>
+          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
         </is>
       </c>
       <c r="E51" s="58" t="n"/>
@@ -2391,12 +2387,12 @@
       </c>
       <c r="C52" s="56" t="inlineStr">
         <is>
-          <t>멀티패스 설정</t>
+          <t>멀티패스 이름 매핑</t>
         </is>
       </c>
       <c r="D52" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
+          <t>cat /etc/multipath/bindings</t>
         </is>
       </c>
       <c r="E52" s="58" t="n"/>
@@ -2409,17 +2405,17 @@
       </c>
       <c r="B53" s="55" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>계정·접근</t>
         </is>
       </c>
       <c r="C53" s="56" t="inlineStr">
         <is>
-          <t>멀티패스 이름 매핑</t>
+          <t>로그인 가능 계정</t>
         </is>
       </c>
       <c r="D53" s="57" t="inlineStr">
         <is>
-          <t>cat /etc/multipath/bindings</t>
+          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
         </is>
       </c>
       <c r="E53" s="58" t="n"/>
@@ -2437,12 +2433,12 @@
       </c>
       <c r="C54" s="56" t="inlineStr">
         <is>
-          <t>로그인 가능 계정</t>
+          <t>관리자 그룹</t>
         </is>
       </c>
       <c r="D54" s="57" t="inlineStr">
         <is>
-          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
+          <t>getent group wheel</t>
         </is>
       </c>
       <c r="E54" s="58" t="n"/>
@@ -2460,16 +2456,20 @@
       </c>
       <c r="C55" s="56" t="inlineStr">
         <is>
-          <t>관리자 그룹</t>
+          <t>SSH 설정</t>
         </is>
       </c>
       <c r="D55" s="57" t="inlineStr">
         <is>
-          <t>getent group wheel</t>
+          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
         </is>
       </c>
       <c r="E55" s="58" t="n"/>
-      <c r="F55" s="59" t="n"/>
+      <c r="F55" s="59" t="inlineStr">
+        <is>
+          <t>allowusers 없으면 미설정</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="55">
@@ -2483,20 +2483,16 @@
       </c>
       <c r="C56" s="56" t="inlineStr">
         <is>
-          <t>SSH 설정</t>
+          <t>방화벽 실행</t>
         </is>
       </c>
       <c r="D56" s="57" t="inlineStr">
         <is>
-          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+          <t>systemctl is-active firewalld</t>
         </is>
       </c>
       <c r="E56" s="58" t="n"/>
-      <c r="F56" s="59" t="inlineStr">
-        <is>
-          <t>allowusers 없으면 미설정</t>
-        </is>
-      </c>
+      <c r="F56" s="59" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="55">
@@ -2510,12 +2506,12 @@
       </c>
       <c r="C57" s="56" t="inlineStr">
         <is>
-          <t>방화벽 실행</t>
+          <t>방화벽 부팅 시 시작</t>
         </is>
       </c>
       <c r="D57" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-active firewalld</t>
+          <t>systemctl is-enabled firewalld</t>
         </is>
       </c>
       <c r="E57" s="58" t="n"/>
@@ -2533,16 +2529,20 @@
       </c>
       <c r="C58" s="56" t="inlineStr">
         <is>
-          <t>방화벽 부팅 시 시작</t>
+          <t>방화벽 응답</t>
         </is>
       </c>
       <c r="D58" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-enabled firewalld</t>
+          <t>firewall-cmd --state</t>
         </is>
       </c>
       <c r="E58" s="58" t="n"/>
-      <c r="F58" s="59" t="n"/>
+      <c r="F58" s="59" t="inlineStr">
+        <is>
+          <t>not running이면 미사용</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="55">
@@ -2556,20 +2556,16 @@
       </c>
       <c r="C59" s="56" t="inlineStr">
         <is>
-          <t>방화벽 응답</t>
+          <t>방화벽 영역</t>
         </is>
       </c>
       <c r="D59" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --state</t>
+          <t>firewall-cmd --get-active-zones</t>
         </is>
       </c>
       <c r="E59" s="58" t="n"/>
-      <c r="F59" s="59" t="inlineStr">
-        <is>
-          <t>not running이면 미사용</t>
-        </is>
-      </c>
+      <c r="F59" s="59" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="55">
@@ -2583,16 +2579,20 @@
       </c>
       <c r="C60" s="56" t="inlineStr">
         <is>
-          <t>방화벽 영역</t>
+          <t>방화벽 규칙</t>
         </is>
       </c>
       <c r="D60" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --get-active-zones</t>
+          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E60" s="58" t="n"/>
-      <c r="F60" s="59" t="n"/>
+      <c r="F60" s="59" t="inlineStr">
+        <is>
+          <t>활성 영역마다</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="55">
@@ -2606,18 +2606,18 @@
       </c>
       <c r="C61" s="56" t="inlineStr">
         <is>
-          <t>방화벽 규칙</t>
+          <t>방화벽 저장 규칙</t>
         </is>
       </c>
       <c r="D61" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
+          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E61" s="58" t="n"/>
       <c r="F61" s="59" t="inlineStr">
         <is>
-          <t>활성 영역마다</t>
+          <t>규칙과 다르면 표시</t>
         </is>
       </c>
     </row>
@@ -2633,20 +2633,16 @@
       </c>
       <c r="C62" s="56" t="inlineStr">
         <is>
-          <t>방화벽 저장 규칙</t>
+          <t>보안 모듈 (SELinux)</t>
         </is>
       </c>
       <c r="D62" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
+          <t>getenforce</t>
         </is>
       </c>
       <c r="E62" s="58" t="n"/>
-      <c r="F62" s="59" t="inlineStr">
-        <is>
-          <t>규칙과 다르면 표시</t>
-        </is>
-      </c>
+      <c r="F62" s="59" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="55">
@@ -2660,12 +2656,12 @@
       </c>
       <c r="C63" s="56" t="inlineStr">
         <is>
-          <t>보안 모듈 (SELinux)</t>
+          <t>보안 모듈 부팅 설정</t>
         </is>
       </c>
       <c r="D63" s="57" t="inlineStr">
         <is>
-          <t>getenforce</t>
+          <t>grep ^SELINUX= /etc/selinux/config</t>
         </is>
       </c>
       <c r="E63" s="58" t="n"/>
@@ -2678,17 +2674,17 @@
       </c>
       <c r="B64" s="55" t="inlineStr">
         <is>
-          <t>계정·접근</t>
+          <t>업데이트·패키지</t>
         </is>
       </c>
       <c r="C64" s="56" t="inlineStr">
         <is>
-          <t>보안 모듈 부팅 설정</t>
+          <t>주요 패키지</t>
         </is>
       </c>
       <c r="D64" s="57" t="inlineStr">
         <is>
-          <t>grep ^SELINUX= /etc/selinux/config</t>
+          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
         </is>
       </c>
       <c r="E64" s="58" t="n"/>
@@ -2706,15 +2702,19 @@
       </c>
       <c r="C65" s="56" t="inlineStr">
         <is>
-          <t>주요 패키지</t>
+          <t>전체 패키지</t>
         </is>
       </c>
       <c r="D65" s="57" t="inlineStr">
         <is>
-          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
-        </is>
-      </c>
-      <c r="E65" s="58" t="n"/>
+          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
+        </is>
+      </c>
+      <c r="E65" s="58" t="inlineStr">
+        <is>
+          <t>패키지 시트 참고</t>
+        </is>
+      </c>
       <c r="F65" s="59" t="n"/>
     </row>
     <row r="66">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C66" s="56" t="inlineStr">
         <is>
-          <t>전체 패키지</t>
+          <t>최근 패치일</t>
         </is>
       </c>
       <c r="D66" s="57" t="inlineStr">
         <is>
-          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
-        </is>
-      </c>
-      <c r="E66" s="58" t="inlineStr">
-        <is>
-          <t>패키지 시트 참고</t>
-        </is>
-      </c>
-      <c r="F66" s="59" t="n"/>
+          <t>dnf history</t>
+        </is>
+      </c>
+      <c r="E66" s="58" t="n"/>
+      <c r="F66" s="59" t="inlineStr">
+        <is>
+          <t>Action(s)에 U가 든 줄</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="55">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="C67" s="56" t="inlineStr">
         <is>
-          <t>최근 패치일</t>
+          <t>자동 업데이트 설정</t>
         </is>
       </c>
       <c r="D67" s="57" t="inlineStr">
         <is>
-          <t>dnf history</t>
+          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
         </is>
       </c>
       <c r="E67" s="58" t="n"/>
       <c r="F67" s="59" t="inlineStr">
         <is>
-          <t>Action(s)에 U가 든 줄</t>
+          <t>파일 없으면 미설치</t>
         </is>
       </c>
     </row>
@@ -2783,18 +2783,18 @@
       </c>
       <c r="C68" s="56" t="inlineStr">
         <is>
-          <t>자동 업데이트 설정</t>
+          <t>자동 업데이트 예약</t>
         </is>
       </c>
       <c r="D68" s="57" t="inlineStr">
         <is>
-          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
+          <t>systemctl list-unit-files 'dnf-automatic*'</t>
         </is>
       </c>
       <c r="E68" s="58" t="n"/>
       <c r="F68" s="59" t="inlineStr">
         <is>
-          <t>파일 없으면 미설치</t>
+          <t>enabled면 사용</t>
         </is>
       </c>
     </row>
@@ -2810,20 +2810,16 @@
       </c>
       <c r="C69" s="56" t="inlineStr">
         <is>
-          <t>자동 업데이트 예약</t>
+          <t>저장소 목록</t>
         </is>
       </c>
       <c r="D69" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files 'dnf-automatic*'</t>
+          <t>dnf repolist</t>
         </is>
       </c>
       <c r="E69" s="58" t="n"/>
-      <c r="F69" s="59" t="inlineStr">
-        <is>
-          <t>enabled면 사용</t>
-        </is>
-      </c>
+      <c r="F69" s="59" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="55">
@@ -2837,12 +2833,12 @@
       </c>
       <c r="C70" s="56" t="inlineStr">
         <is>
-          <t>저장소 목록</t>
+          <t>저장소 파일</t>
         </is>
       </c>
       <c r="D70" s="57" t="inlineStr">
         <is>
-          <t>dnf repolist</t>
+          <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
       <c r="E70" s="58" t="n"/>
@@ -2860,16 +2856,20 @@
       </c>
       <c r="C71" s="56" t="inlineStr">
         <is>
-          <t>저장소 파일</t>
+          <t>구독 등록 여부</t>
         </is>
       </c>
       <c r="D71" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/yum.repos.d/</t>
+          <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
       <c r="E71" s="58" t="n"/>
-      <c r="F71" s="59" t="n"/>
+      <c r="F71" s="59" t="inlineStr">
+        <is>
+          <t>파일 없으면 미등록</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="55">
@@ -2883,18 +2883,18 @@
       </c>
       <c r="C72" s="56" t="inlineStr">
         <is>
-          <t>구독 등록 여부</t>
+          <t>구독 (RHSM)</t>
         </is>
       </c>
       <c r="D72" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/pki/consumer/cert.pem</t>
+          <t>subscription-manager status</t>
         </is>
       </c>
       <c r="E72" s="58" t="n"/>
       <c r="F72" s="59" t="inlineStr">
         <is>
-          <t>파일 없으면 미등록</t>
+          <t>RHEL</t>
         </is>
       </c>
     </row>
@@ -2910,18 +2910,18 @@
       </c>
       <c r="C73" s="56" t="inlineStr">
         <is>
-          <t>구독 (RHSM)</t>
+          <t>릴리스 고정</t>
         </is>
       </c>
       <c r="D73" s="57" t="inlineStr">
         <is>
-          <t>subscription-manager status</t>
+          <t>subscription-manager release --show</t>
         </is>
       </c>
       <c r="E73" s="58" t="n"/>
       <c r="F73" s="59" t="inlineStr">
         <is>
-          <t>RHEL</t>
+          <t>Release not set이면 미고정</t>
         </is>
       </c>
     </row>
@@ -2932,23 +2932,23 @@
       </c>
       <c r="B74" s="55" t="inlineStr">
         <is>
-          <t>업데이트·패키지</t>
+          <t>커널 설정</t>
         </is>
       </c>
       <c r="C74" s="56" t="inlineStr">
         <is>
-          <t>릴리스 고정</t>
+          <t>sysctl</t>
         </is>
       </c>
       <c r="D74" s="57" t="inlineStr">
         <is>
-          <t>subscription-manager release --show</t>
+          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
         </is>
       </c>
       <c r="E74" s="58" t="n"/>
       <c r="F74" s="59" t="inlineStr">
         <is>
-          <t>Release not set이면 미고정</t>
+          <t>99-sysctl.conf 줄은 중복</t>
         </is>
       </c>
     </row>
@@ -2964,20 +2964,16 @@
       </c>
       <c r="C75" s="56" t="inlineStr">
         <is>
-          <t>sysctl</t>
+          <t>자원 제한 (limits)</t>
         </is>
       </c>
       <c r="D75" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
       <c r="E75" s="58" t="n"/>
-      <c r="F75" s="59" t="inlineStr">
-        <is>
-          <t>99-sysctl.conf 줄은 중복</t>
-        </is>
-      </c>
+      <c r="F75" s="59" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="55">
@@ -2991,12 +2987,12 @@
       </c>
       <c r="C76" s="56" t="inlineStr">
         <is>
-          <t>자원 제한 (limits)</t>
+          <t>kdump 설정</t>
         </is>
       </c>
       <c r="D76" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
+          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
       <c r="E76" s="58" t="n"/>
@@ -3014,12 +3010,12 @@
       </c>
       <c r="C77" s="56" t="inlineStr">
         <is>
-          <t>kdump 설정</t>
+          <t>kdump 실행</t>
         </is>
       </c>
       <c r="D77" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
+          <t>systemctl is-active kdump</t>
         </is>
       </c>
       <c r="E77" s="58" t="n"/>
@@ -3037,12 +3033,12 @@
       </c>
       <c r="C78" s="56" t="inlineStr">
         <is>
-          <t>kdump 실행</t>
+          <t>kdump 부팅 시 시작</t>
         </is>
       </c>
       <c r="D78" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-active kdump</t>
+          <t>systemctl is-enabled kdump</t>
         </is>
       </c>
       <c r="E78" s="58" t="n"/>
@@ -3055,17 +3051,17 @@
       </c>
       <c r="B79" s="55" t="inlineStr">
         <is>
-          <t>커널 설정</t>
+          <t>서비스·예약</t>
         </is>
       </c>
       <c r="C79" s="56" t="inlineStr">
         <is>
-          <t>kdump 부팅 시 시작</t>
+          <t>실행 중인 서비스</t>
         </is>
       </c>
       <c r="D79" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-enabled kdump</t>
+          <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
       <c r="E79" s="58" t="n"/>
@@ -3083,12 +3079,12 @@
       </c>
       <c r="C80" s="56" t="inlineStr">
         <is>
-          <t>실행 중인 서비스</t>
+          <t>자동 시작 서비스</t>
         </is>
       </c>
       <c r="D80" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-units --type=service --state=running --no-pager</t>
+          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
       <c r="E80" s="58" t="n"/>
@@ -3106,12 +3102,12 @@
       </c>
       <c r="C81" s="56" t="inlineStr">
         <is>
-          <t>자동 시작 서비스</t>
+          <t>열린 포트</t>
         </is>
       </c>
       <c r="D81" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
+          <t>ss -tulnp</t>
         </is>
       </c>
       <c r="E81" s="58" t="n"/>
@@ -3129,12 +3125,12 @@
       </c>
       <c r="C82" s="56" t="inlineStr">
         <is>
-          <t>열린 포트</t>
+          <t>예약 작업 (타이머)</t>
         </is>
       </c>
       <c r="D82" s="57" t="inlineStr">
         <is>
-          <t>ss -tulnp</t>
+          <t>systemctl list-timers --all --no-pager</t>
         </is>
       </c>
       <c r="E82" s="58" t="n"/>
@@ -3152,16 +3148,20 @@
       </c>
       <c r="C83" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (타이머)</t>
+          <t>예약 작업 (crontab)</t>
         </is>
       </c>
       <c r="D83" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-timers --all --no-pager</t>
+          <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E83" s="58" t="n"/>
-      <c r="F83" s="59" t="n"/>
+      <c r="F83" s="59" t="inlineStr">
+        <is>
+          <t>파일명이 계정명</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="55">
@@ -3175,20 +3175,16 @@
       </c>
       <c r="C84" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (crontab)</t>
+          <t>예약 작업 (cron.d)</t>
         </is>
       </c>
       <c r="D84" s="57" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /var/spool/cron/*</t>
+          <t>ls /etc/cron.d</t>
         </is>
       </c>
       <c r="E84" s="58" t="n"/>
-      <c r="F84" s="59" t="inlineStr">
-        <is>
-          <t>파일명이 계정명</t>
-        </is>
-      </c>
+      <c r="F84" s="59" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="55">
@@ -3197,21 +3193,25 @@
       </c>
       <c r="B85" s="55" t="inlineStr">
         <is>
-          <t>서비스·예약</t>
+          <t>에이전트·백업</t>
         </is>
       </c>
       <c r="C85" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (cron.d)</t>
+          <t>모니터링 에이전트</t>
         </is>
       </c>
       <c r="D85" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/cron.d</t>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
       <c r="E85" s="58" t="n"/>
-      <c r="F85" s="59" t="n"/>
+      <c r="F85" s="59" t="inlineStr">
+        <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="55">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="C86" s="56" t="inlineStr">
         <is>
-          <t>모니터링 에이전트</t>
+          <t>보안 에이전트</t>
         </is>
       </c>
       <c r="D86" s="57" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="C87" s="56" t="inlineStr">
         <is>
-          <t>보안 에이전트</t>
+          <t>백신</t>
         </is>
       </c>
       <c r="D87" s="57" t="inlineStr">
@@ -3279,18 +3279,18 @@
       </c>
       <c r="C88" s="56" t="inlineStr">
         <is>
-          <t>백신</t>
+          <t>설정 백업</t>
         </is>
       </c>
       <c r="D88" s="57" t="inlineStr">
         <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+          <t>백업 위치, 마지막 백업 날짜</t>
         </is>
       </c>
       <c r="E88" s="58" t="n"/>
       <c r="F88" s="59" t="inlineStr">
         <is>
-          <t>출력 없으면 미실행</t>
+          <t>직접 입력</t>
         </is>
       </c>
     </row>
@@ -3301,23 +3301,23 @@
       </c>
       <c r="B89" s="55" t="inlineStr">
         <is>
-          <t>에이전트·백업</t>
+          <t>특수 구성</t>
         </is>
       </c>
       <c r="C89" s="56" t="inlineStr">
         <is>
-          <t>설정 백업</t>
+          <t>GPU</t>
         </is>
       </c>
       <c r="D89" s="57" t="inlineStr">
         <is>
-          <t>백업 위치, 마지막 백업 날짜</t>
+          <t>nvidia-smi -L</t>
         </is>
       </c>
       <c r="E89" s="58" t="n"/>
       <c r="F89" s="59" t="inlineStr">
         <is>
-          <t>직접 입력</t>
+          <t>GPU 서버</t>
         </is>
       </c>
     </row>

--- a/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
+++ b/04_RHEL_구성표/RHEL_계열_9_구성표.xlsx
@@ -522,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Checks" displayName="Checks" ref="A5:F89" headerRowCount="1">
-  <autoFilter ref="A5:F89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Checks" displayName="Checks" ref="A5:F90" headerRowCount="1">
+  <autoFilter ref="A5:F90"/>
   <tableColumns count="6">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="구분"/>
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1958,7 +1958,11 @@
         </is>
       </c>
       <c r="E34" s="58" t="n"/>
-      <c r="F34" s="59" t="n"/>
+      <c r="F34" s="59" t="inlineStr">
+        <is>
+          <t>파일 없으면 DNS 미사용</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="55">
@@ -2456,20 +2460,16 @@
       </c>
       <c r="C55" s="56" t="inlineStr">
         <is>
-          <t>SSH 설정</t>
+          <t>sudo 권한</t>
         </is>
       </c>
       <c r="D55" s="57" t="inlineStr">
         <is>
-          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+          <t>egrep -v '^#|^$' /etc/sudoers /etc/sudoers.d/*</t>
         </is>
       </c>
       <c r="E55" s="58" t="n"/>
-      <c r="F55" s="59" t="inlineStr">
-        <is>
-          <t>allowusers 없으면 미설정</t>
-        </is>
-      </c>
+      <c r="F55" s="59" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="55">
@@ -2483,16 +2483,20 @@
       </c>
       <c r="C56" s="56" t="inlineStr">
         <is>
-          <t>방화벽 실행</t>
+          <t>SSH 설정</t>
         </is>
       </c>
       <c r="D56" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-active firewalld</t>
+          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
         </is>
       </c>
       <c r="E56" s="58" t="n"/>
-      <c r="F56" s="59" t="n"/>
+      <c r="F56" s="59" t="inlineStr">
+        <is>
+          <t>allowusers 없으면 미설정</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="55">
@@ -2506,12 +2510,12 @@
       </c>
       <c r="C57" s="56" t="inlineStr">
         <is>
-          <t>방화벽 부팅 시 시작</t>
+          <t>방화벽 실행</t>
         </is>
       </c>
       <c r="D57" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-enabled firewalld</t>
+          <t>systemctl is-active firewalld</t>
         </is>
       </c>
       <c r="E57" s="58" t="n"/>
@@ -2529,20 +2533,16 @@
       </c>
       <c r="C58" s="56" t="inlineStr">
         <is>
-          <t>방화벽 응답</t>
+          <t>방화벽 부팅 시 시작</t>
         </is>
       </c>
       <c r="D58" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --state</t>
+          <t>systemctl is-enabled firewalld</t>
         </is>
       </c>
       <c r="E58" s="58" t="n"/>
-      <c r="F58" s="59" t="inlineStr">
-        <is>
-          <t>not running이면 미사용</t>
-        </is>
-      </c>
+      <c r="F58" s="59" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="55">
@@ -2556,16 +2556,20 @@
       </c>
       <c r="C59" s="56" t="inlineStr">
         <is>
-          <t>방화벽 영역</t>
+          <t>방화벽 응답</t>
         </is>
       </c>
       <c r="D59" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --get-active-zones</t>
+          <t>firewall-cmd --state</t>
         </is>
       </c>
       <c r="E59" s="58" t="n"/>
-      <c r="F59" s="59" t="n"/>
+      <c r="F59" s="59" t="inlineStr">
+        <is>
+          <t>not running이면 미사용</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="55">
@@ -2579,20 +2583,16 @@
       </c>
       <c r="C60" s="56" t="inlineStr">
         <is>
-          <t>방화벽 규칙</t>
+          <t>방화벽 영역</t>
         </is>
       </c>
       <c r="D60" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
+          <t>firewall-cmd --get-active-zones</t>
         </is>
       </c>
       <c r="E60" s="58" t="n"/>
-      <c r="F60" s="59" t="inlineStr">
-        <is>
-          <t>활성 영역마다</t>
-        </is>
-      </c>
+      <c r="F60" s="59" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="55">
@@ -2606,18 +2606,18 @@
       </c>
       <c r="C61" s="56" t="inlineStr">
         <is>
-          <t>방화벽 저장 규칙</t>
+          <t>방화벽 규칙</t>
         </is>
       </c>
       <c r="D61" s="57" t="inlineStr">
         <is>
-          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
+          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E61" s="58" t="n"/>
       <c r="F61" s="59" t="inlineStr">
         <is>
-          <t>규칙과 다르면 표시</t>
+          <t>활성 영역마다</t>
         </is>
       </c>
     </row>
@@ -2633,16 +2633,20 @@
       </c>
       <c r="C62" s="56" t="inlineStr">
         <is>
-          <t>보안 모듈 (SELinux)</t>
+          <t>방화벽 저장 규칙</t>
         </is>
       </c>
       <c r="D62" s="57" t="inlineStr">
         <is>
-          <t>getenforce</t>
+          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E62" s="58" t="n"/>
-      <c r="F62" s="59" t="n"/>
+      <c r="F62" s="59" t="inlineStr">
+        <is>
+          <t>규칙과 다르면 표시</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="55">
@@ -2656,12 +2660,12 @@
       </c>
       <c r="C63" s="56" t="inlineStr">
         <is>
-          <t>보안 모듈 부팅 설정</t>
+          <t>보안 모듈 (SELinux)</t>
         </is>
       </c>
       <c r="D63" s="57" t="inlineStr">
         <is>
-          <t>grep ^SELINUX= /etc/selinux/config</t>
+          <t>getenforce</t>
         </is>
       </c>
       <c r="E63" s="58" t="n"/>
@@ -2674,17 +2678,17 @@
       </c>
       <c r="B64" s="55" t="inlineStr">
         <is>
-          <t>업데이트·패키지</t>
+          <t>계정·접근</t>
         </is>
       </c>
       <c r="C64" s="56" t="inlineStr">
         <is>
-          <t>주요 패키지</t>
+          <t>보안 모듈 부팅 설정</t>
         </is>
       </c>
       <c r="D64" s="57" t="inlineStr">
         <is>
-          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
+          <t>grep ^SELINUX= /etc/selinux/config</t>
         </is>
       </c>
       <c r="E64" s="58" t="n"/>
@@ -2702,19 +2706,15 @@
       </c>
       <c r="C65" s="56" t="inlineStr">
         <is>
-          <t>전체 패키지</t>
+          <t>주요 패키지</t>
         </is>
       </c>
       <c r="D65" s="57" t="inlineStr">
         <is>
-          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
-        </is>
-      </c>
-      <c r="E65" s="58" t="inlineStr">
-        <is>
-          <t>패키지 시트 참고</t>
-        </is>
-      </c>
+          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
+        </is>
+      </c>
+      <c r="E65" s="58" t="n"/>
       <c r="F65" s="59" t="n"/>
     </row>
     <row r="66">
@@ -2729,20 +2729,20 @@
       </c>
       <c r="C66" s="56" t="inlineStr">
         <is>
-          <t>최근 패치일</t>
+          <t>전체 패키지</t>
         </is>
       </c>
       <c r="D66" s="57" t="inlineStr">
         <is>
-          <t>dnf history</t>
-        </is>
-      </c>
-      <c r="E66" s="58" t="n"/>
-      <c r="F66" s="59" t="inlineStr">
-        <is>
-          <t>Action(s)에 U가 든 줄</t>
-        </is>
-      </c>
+          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
+        </is>
+      </c>
+      <c r="E66" s="58" t="inlineStr">
+        <is>
+          <t>패키지 시트 참고</t>
+        </is>
+      </c>
+      <c r="F66" s="59" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="55">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="C67" s="56" t="inlineStr">
         <is>
-          <t>자동 업데이트 설정</t>
+          <t>최근 패치일</t>
         </is>
       </c>
       <c r="D67" s="57" t="inlineStr">
         <is>
-          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
+          <t>dnf history</t>
         </is>
       </c>
       <c r="E67" s="58" t="n"/>
       <c r="F67" s="59" t="inlineStr">
         <is>
-          <t>파일 없으면 미설치</t>
+          <t>Action(s)에 U가 든 줄</t>
         </is>
       </c>
     </row>
@@ -2783,18 +2783,18 @@
       </c>
       <c r="C68" s="56" t="inlineStr">
         <is>
-          <t>자동 업데이트 예약</t>
+          <t>자동 업데이트 설정</t>
         </is>
       </c>
       <c r="D68" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files 'dnf-automatic*'</t>
+          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
         </is>
       </c>
       <c r="E68" s="58" t="n"/>
       <c r="F68" s="59" t="inlineStr">
         <is>
-          <t>enabled면 사용</t>
+          <t>파일 없으면 미설치</t>
         </is>
       </c>
     </row>
@@ -2810,16 +2810,20 @@
       </c>
       <c r="C69" s="56" t="inlineStr">
         <is>
-          <t>저장소 목록</t>
+          <t>자동 업데이트 예약</t>
         </is>
       </c>
       <c r="D69" s="57" t="inlineStr">
         <is>
-          <t>dnf repolist</t>
+          <t>systemctl list-unit-files 'dnf-automatic*'</t>
         </is>
       </c>
       <c r="E69" s="58" t="n"/>
-      <c r="F69" s="59" t="n"/>
+      <c r="F69" s="59" t="inlineStr">
+        <is>
+          <t>enabled면 사용</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="55">
@@ -2833,12 +2837,12 @@
       </c>
       <c r="C70" s="56" t="inlineStr">
         <is>
-          <t>저장소 파일</t>
+          <t>저장소 목록</t>
         </is>
       </c>
       <c r="D70" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/yum.repos.d/</t>
+          <t>dnf repolist</t>
         </is>
       </c>
       <c r="E70" s="58" t="n"/>
@@ -2856,20 +2860,16 @@
       </c>
       <c r="C71" s="56" t="inlineStr">
         <is>
-          <t>구독 등록 여부</t>
+          <t>저장소 파일</t>
         </is>
       </c>
       <c r="D71" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/pki/consumer/cert.pem</t>
+          <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
       <c r="E71" s="58" t="n"/>
-      <c r="F71" s="59" t="inlineStr">
-        <is>
-          <t>파일 없으면 미등록</t>
-        </is>
-      </c>
+      <c r="F71" s="59" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="55">
@@ -2883,18 +2883,18 @@
       </c>
       <c r="C72" s="56" t="inlineStr">
         <is>
-          <t>구독 (RHSM)</t>
+          <t>구독 등록 여부</t>
         </is>
       </c>
       <c r="D72" s="57" t="inlineStr">
         <is>
-          <t>subscription-manager status</t>
+          <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
       <c r="E72" s="58" t="n"/>
       <c r="F72" s="59" t="inlineStr">
         <is>
-          <t>RHEL</t>
+          <t>파일 없으면 미등록</t>
         </is>
       </c>
     </row>
@@ -2910,18 +2910,18 @@
       </c>
       <c r="C73" s="56" t="inlineStr">
         <is>
-          <t>릴리스 고정</t>
+          <t>구독 (RHSM)</t>
         </is>
       </c>
       <c r="D73" s="57" t="inlineStr">
         <is>
-          <t>subscription-manager release --show</t>
+          <t>subscription-manager status</t>
         </is>
       </c>
       <c r="E73" s="58" t="n"/>
       <c r="F73" s="59" t="inlineStr">
         <is>
-          <t>Release not set이면 미고정</t>
+          <t>RHEL</t>
         </is>
       </c>
     </row>
@@ -2932,23 +2932,23 @@
       </c>
       <c r="B74" s="55" t="inlineStr">
         <is>
-          <t>커널 설정</t>
+          <t>업데이트·패키지</t>
         </is>
       </c>
       <c r="C74" s="56" t="inlineStr">
         <is>
-          <t>sysctl</t>
+          <t>릴리스 고정</t>
         </is>
       </c>
       <c r="D74" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+          <t>subscription-manager release --show</t>
         </is>
       </c>
       <c r="E74" s="58" t="n"/>
       <c r="F74" s="59" t="inlineStr">
         <is>
-          <t>99-sysctl.conf 줄은 중복</t>
+          <t>Release not set이면 미고정</t>
         </is>
       </c>
     </row>
@@ -2964,16 +2964,20 @@
       </c>
       <c r="C75" s="56" t="inlineStr">
         <is>
-          <t>자원 제한 (limits)</t>
+          <t>sysctl</t>
         </is>
       </c>
       <c r="D75" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
+          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
         </is>
       </c>
       <c r="E75" s="58" t="n"/>
-      <c r="F75" s="59" t="n"/>
+      <c r="F75" s="59" t="inlineStr">
+        <is>
+          <t>99-sysctl.conf 줄은 중복</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="55">
@@ -2987,12 +2991,12 @@
       </c>
       <c r="C76" s="56" t="inlineStr">
         <is>
-          <t>kdump 설정</t>
+          <t>자원 제한 (limits)</t>
         </is>
       </c>
       <c r="D76" s="57" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
+          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
       <c r="E76" s="58" t="n"/>
@@ -3010,12 +3014,12 @@
       </c>
       <c r="C77" s="56" t="inlineStr">
         <is>
-          <t>kdump 실행</t>
+          <t>kdump 설정</t>
         </is>
       </c>
       <c r="D77" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-active kdump</t>
+          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
       <c r="E77" s="58" t="n"/>
@@ -3033,12 +3037,12 @@
       </c>
       <c r="C78" s="56" t="inlineStr">
         <is>
-          <t>kdump 부팅 시 시작</t>
+          <t>kdump 실행</t>
         </is>
       </c>
       <c r="D78" s="57" t="inlineStr">
         <is>
-          <t>systemctl is-enabled kdump</t>
+          <t>systemctl is-active kdump</t>
         </is>
       </c>
       <c r="E78" s="58" t="n"/>
@@ -3051,17 +3055,17 @@
       </c>
       <c r="B79" s="55" t="inlineStr">
         <is>
-          <t>서비스·예약</t>
+          <t>커널 설정</t>
         </is>
       </c>
       <c r="C79" s="56" t="inlineStr">
         <is>
-          <t>실행 중인 서비스</t>
+          <t>kdump 부팅 시 시작</t>
         </is>
       </c>
       <c r="D79" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-units --type=service --state=running --no-pager</t>
+          <t>systemctl is-enabled kdump</t>
         </is>
       </c>
       <c r="E79" s="58" t="n"/>
@@ -3079,12 +3083,12 @@
       </c>
       <c r="C80" s="56" t="inlineStr">
         <is>
-          <t>자동 시작 서비스</t>
+          <t>실행 중인 서비스</t>
         </is>
       </c>
       <c r="D80" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
+          <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
       <c r="E80" s="58" t="n"/>
@@ -3102,12 +3106,12 @@
       </c>
       <c r="C81" s="56" t="inlineStr">
         <is>
-          <t>열린 포트</t>
+          <t>자동 시작 서비스</t>
         </is>
       </c>
       <c r="D81" s="57" t="inlineStr">
         <is>
-          <t>ss -tulnp</t>
+          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
       <c r="E81" s="58" t="n"/>
@@ -3125,12 +3129,12 @@
       </c>
       <c r="C82" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (타이머)</t>
+          <t>열린 포트</t>
         </is>
       </c>
       <c r="D82" s="57" t="inlineStr">
         <is>
-          <t>systemctl list-timers --all --no-pager</t>
+          <t>ss -tulnp</t>
         </is>
       </c>
       <c r="E82" s="58" t="n"/>
@@ -3148,20 +3152,16 @@
       </c>
       <c r="C83" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (crontab)</t>
+          <t>예약 작업 (타이머)</t>
         </is>
       </c>
       <c r="D83" s="57" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /var/spool/cron/*</t>
+          <t>systemctl list-timers --all --no-pager</t>
         </is>
       </c>
       <c r="E83" s="58" t="n"/>
-      <c r="F83" s="59" t="inlineStr">
-        <is>
-          <t>파일명이 계정명</t>
-        </is>
-      </c>
+      <c r="F83" s="59" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="55">
@@ -3175,16 +3175,20 @@
       </c>
       <c r="C84" s="56" t="inlineStr">
         <is>
-          <t>예약 작업 (cron.d)</t>
+          <t>예약 작업 (crontab)</t>
         </is>
       </c>
       <c r="D84" s="57" t="inlineStr">
         <is>
-          <t>ls /etc/cron.d</t>
+          <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
       <c r="E84" s="58" t="n"/>
-      <c r="F84" s="59" t="n"/>
+      <c r="F84" s="59" t="inlineStr">
+        <is>
+          <t>파일명이 계정명</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="55">
@@ -3193,25 +3197,21 @@
       </c>
       <c r="B85" s="55" t="inlineStr">
         <is>
-          <t>에이전트·백업</t>
+          <t>서비스·예약</t>
         </is>
       </c>
       <c r="C85" s="56" t="inlineStr">
         <is>
-          <t>모니터링 에이전트</t>
+          <t>예약 작업 (cron.d)</t>
         </is>
       </c>
       <c r="D85" s="57" t="inlineStr">
         <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+          <t>ls /etc/cron.d</t>
         </is>
       </c>
       <c r="E85" s="58" t="n"/>
-      <c r="F85" s="59" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
+      <c r="F85" s="59" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="55">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="C86" s="56" t="inlineStr">
         <is>
-          <t>보안 에이전트</t>
+          <t>모니터링 에이전트</t>
         </is>
       </c>
       <c r="D86" s="57" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="C87" s="56" t="inlineStr">
         <is>
-          <t>백신</t>
+          <t>보안 에이전트</t>
         </is>
       </c>
       <c r="D87" s="57" t="inlineStr">
@@ -3279,18 +3279,18 @@
       </c>
       <c r="C88" s="56" t="inlineStr">
         <is>
-          <t>설정 백업</t>
+          <t>백신</t>
         </is>
       </c>
       <c r="D88" s="57" t="inlineStr">
         <is>
-          <t>백업 위치, 마지막 백업 날짜</t>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
         </is>
       </c>
       <c r="E88" s="58" t="n"/>
       <c r="F88" s="59" t="inlineStr">
         <is>
-          <t>직접 입력</t>
+          <t>출력 없으면 미실행</t>
         </is>
       </c>
     </row>
@@ -3301,21 +3301,48 @@
       </c>
       <c r="B89" s="55" t="inlineStr">
         <is>
-          <t>특수 구성</t>
+          <t>에이전트·백업</t>
         </is>
       </c>
       <c r="C89" s="56" t="inlineStr">
         <is>
-          <t>GPU</t>
+          <t>설정 백업</t>
         </is>
       </c>
       <c r="D89" s="57" t="inlineStr">
         <is>
-          <t>nvidia-smi -L</t>
+          <t>백업 위치, 마지막 백업 날짜</t>
         </is>
       </c>
       <c r="E89" s="58" t="n"/>
       <c r="F89" s="59" t="inlineStr">
+        <is>
+          <t>직접 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="55">
+        <f>ROW()-5</f>
+        <v/>
+      </c>
+      <c r="B90" s="55" t="inlineStr">
+        <is>
+          <t>특수 구성</t>
+        </is>
+      </c>
+      <c r="C90" s="56" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D90" s="57" t="inlineStr">
+        <is>
+          <t>nvidia-smi -L</t>
+        </is>
+      </c>
+      <c r="E90" s="58" t="n"/>
+      <c r="F90" s="59" t="inlineStr">
         <is>
           <t>GPU 서버</t>
         </is>
